--- a/research/traditional_assets/database/data/poland/poland_aerospace_defense.xlsx
+++ b/research/traditional_assets/database/data/poland/poland_aerospace_defense.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="wse_lbw" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -351,7 +353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +581,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,28 +590,28 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.00336</v>
+        <v>0.0513</v>
       </c>
       <c r="E2">
-        <v>0.275</v>
+        <v>0.224</v>
       </c>
       <c r="G2">
-        <v>0.237315875613748</v>
+        <v>0.1517904416887279</v>
       </c>
       <c r="H2">
-        <v>0.237315875613748</v>
+        <v>0.1471506200362268</v>
       </c>
       <c r="I2">
-        <v>0.1243862520458265</v>
+        <v>0.08360039013515395</v>
       </c>
       <c r="J2">
-        <v>0.1030530635898341</v>
+        <v>0.07593906405971829</v>
       </c>
       <c r="K2">
-        <v>5.98</v>
+        <v>4.61</v>
       </c>
       <c r="L2">
-        <v>0.09787234042553192</v>
+        <v>0.06423296642050996</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -633,70 +635,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>1.68</v>
+        <v>6.738</v>
       </c>
       <c r="V2">
-        <v>0.0417910447761194</v>
+        <v>0.05247663551401869</v>
       </c>
       <c r="W2">
-        <v>0.0860431654676259</v>
+        <v>-0.06972663507989596</v>
       </c>
       <c r="X2">
-        <v>0.08028404810152097</v>
+        <v>0.1210753446079734</v>
       </c>
       <c r="Y2">
-        <v>0.005759117366104932</v>
+        <v>-0.1908019796878694</v>
       </c>
       <c r="Z2">
-        <v>0.7628917467848672</v>
+        <v>0.8398572348019429</v>
       </c>
       <c r="AA2">
-        <v>0.07861833169358054</v>
+        <v>-0.1923805960054602</v>
       </c>
       <c r="AB2">
-        <v>0.06955858799740432</v>
+        <v>0.1171148720170407</v>
       </c>
       <c r="AC2">
-        <v>0.009059743696176223</v>
+        <v>-0.3094954680225009</v>
       </c>
       <c r="AD2">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AG2">
-        <v>8.82</v>
+        <v>2.861999999999999</v>
       </c>
       <c r="AH2">
-        <v>0.2071005917159763</v>
+        <v>0.06956521739130435</v>
       </c>
       <c r="AI2">
-        <v>0.1244075829383886</v>
+        <v>0.1134751773049645</v>
       </c>
       <c r="AJ2">
-        <v>0.1799265605875153</v>
+        <v>0.02180372080266946</v>
       </c>
       <c r="AK2">
-        <v>0.1066247582205029</v>
+        <v>0.03675733990906988</v>
       </c>
       <c r="AL2">
-        <v>0</v>
+        <v>0.6789999999999999</v>
       </c>
       <c r="AM2">
-        <v>-0.467</v>
+        <v>0.6349999999999999</v>
       </c>
       <c r="AN2">
-        <v>0.9722222222222222</v>
+        <v>1.059251903343264</v>
+      </c>
+      <c r="AO2">
+        <v>8.836524300441827</v>
       </c>
       <c r="AP2">
-        <v>0.8166666666666667</v>
+        <v>0.3157894736842104</v>
       </c>
       <c r="AQ2">
-        <v>-16.27408993576017</v>
+        <v>9.448818897637796</v>
       </c>
     </row>
     <row r="3">
@@ -716,28 +721,28 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.00336</v>
+        <v>0.0513</v>
       </c>
       <c r="E3">
-        <v>0.275</v>
+        <v>0.224</v>
       </c>
       <c r="G3">
-        <v>0.237315875613748</v>
+        <v>0.1579160419790105</v>
       </c>
       <c r="H3">
-        <v>0.237315875613748</v>
+        <v>0.1529235382308845</v>
       </c>
       <c r="I3">
-        <v>0.1243862520458265</v>
+        <v>0.1107946026986507</v>
       </c>
       <c r="J3">
-        <v>0.1030530635898341</v>
+        <v>0.09048767405153728</v>
       </c>
       <c r="K3">
-        <v>5.98</v>
+        <v>5.62</v>
       </c>
       <c r="L3">
-        <v>0.09787234042553192</v>
+        <v>0.08425787106446776</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -761,70 +766,8910 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>1.68</v>
+        <v>0.588</v>
       </c>
       <c r="V3">
-        <v>0.0417910447761194</v>
+        <v>0.007646293888166449</v>
       </c>
       <c r="W3">
-        <v>0.0860431654676259</v>
+        <v>0.07635869565217392</v>
       </c>
       <c r="X3">
-        <v>0.08028404810152097</v>
+        <v>0.1243922705849377</v>
       </c>
       <c r="Y3">
-        <v>0.005759117366104932</v>
+        <v>-0.04803357493276375</v>
       </c>
       <c r="Z3">
-        <v>0.7628917467848672</v>
+        <v>0.8092695947585539</v>
       </c>
       <c r="AA3">
-        <v>0.07861833169358054</v>
+        <v>0.07322892331033168</v>
       </c>
       <c r="AB3">
-        <v>0.06955858799740432</v>
+        <v>0.1172424185774482</v>
       </c>
       <c r="AC3">
-        <v>0.009059743696176223</v>
+        <v>-0.04401349526711648</v>
       </c>
       <c r="AD3">
-        <v>10.5</v>
+        <v>8.98</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>10.5</v>
+        <v>8.98</v>
       </c>
       <c r="AG3">
-        <v>8.82</v>
+        <v>8.392000000000001</v>
       </c>
       <c r="AH3">
-        <v>0.2071005917159763</v>
+        <v>0.1045645086166744</v>
       </c>
       <c r="AI3">
-        <v>0.1244075829383886</v>
+        <v>0.1218783930510315</v>
       </c>
       <c r="AJ3">
-        <v>0.1799265605875153</v>
+        <v>0.09839140833841394</v>
       </c>
       <c r="AK3">
-        <v>0.1066247582205029</v>
+        <v>0.1148142067531331</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>0.601</v>
       </c>
       <c r="AM3">
-        <v>-0.467</v>
+        <v>0.601</v>
       </c>
       <c r="AN3">
-        <v>0.9722222222222222</v>
+        <v>0.9200819672131149</v>
+      </c>
+      <c r="AO3">
+        <v>12.29617304492512</v>
       </c>
       <c r="AP3">
-        <v>0.8166666666666667</v>
+        <v>0.8598360655737707</v>
       </c>
       <c r="AQ3">
-        <v>-16.27408993576017</v>
+        <v>12.29617304492512</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Creotech Instruments S.A. (WSE:CRI)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Aerospace/Defense</t>
+        </is>
+      </c>
+      <c r="G4">
+        <v>0.07120315581854043</v>
+      </c>
+      <c r="H4">
+        <v>0.07120315581854043</v>
+      </c>
+      <c r="I4">
+        <v>-0.2741617357001972</v>
+      </c>
+      <c r="J4">
+        <v>-0.2741617357001972</v>
+      </c>
+      <c r="K4">
+        <v>-1.01</v>
+      </c>
+      <c r="L4">
+        <v>-0.1992110453648915</v>
+      </c>
+      <c r="M4">
+        <v>-0</v>
+      </c>
+      <c r="N4">
+        <v>-0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>-0</v>
+      </c>
+      <c r="Q4">
+        <v>-0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>6.15</v>
+      </c>
+      <c r="V4">
+        <v>0.1194174757281554</v>
+      </c>
+      <c r="W4">
+        <v>-0.2158119658119658</v>
+      </c>
+      <c r="X4">
+        <v>0.1177584186310092</v>
+      </c>
+      <c r="Y4">
+        <v>-0.333570384442975</v>
+      </c>
+      <c r="Z4">
+        <v>1.670510708401977</v>
+      </c>
+      <c r="AA4">
+        <v>-0.4579901153212521</v>
+      </c>
+      <c r="AB4">
+        <v>0.1169873254566333</v>
+      </c>
+      <c r="AC4">
+        <v>-0.5749774407778854</v>
+      </c>
+      <c r="AD4">
+        <v>0.62</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>0.62</v>
+      </c>
+      <c r="AG4">
+        <v>-5.53</v>
+      </c>
+      <c r="AH4">
+        <v>0.01189562547966232</v>
+      </c>
+      <c r="AI4">
+        <v>0.05677655677655678</v>
+      </c>
+      <c r="AJ4">
+        <v>-0.1202958451163803</v>
+      </c>
+      <c r="AK4">
+        <v>-1.159329140461216</v>
+      </c>
+      <c r="AL4">
+        <v>0.078</v>
+      </c>
+      <c r="AM4">
+        <v>0.034</v>
+      </c>
+      <c r="AN4">
+        <v>-0.8895265423242468</v>
+      </c>
+      <c r="AO4">
+        <v>-17.82051282051282</v>
+      </c>
+      <c r="AP4">
+        <v>7.93400286944046</v>
+      </c>
+      <c r="AQ4">
+        <v>-40.88235294117646</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_capital</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>actual_equity_value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>actual_enterprise_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_capital</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_rating</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>actual_beta</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Lubawa S.A. (WSE:LBW)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>WSE:LBW</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Aerospace/Defense</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.104564508616674</v>
+      </c>
+      <c r="F2">
+        <v>0.34</v>
+      </c>
+      <c r="G2">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="H2">
+        <v>60.4774905067256</v>
+      </c>
+      <c r="I2">
+        <v>85.292</v>
+      </c>
+      <c r="J2">
+        <v>89.0886905067256</v>
+      </c>
+      <c r="K2">
+        <v>8.98</v>
+      </c>
+      <c r="L2">
+        <v>29.1992</v>
+      </c>
+      <c r="M2">
+        <v>0.117242418577448</v>
+      </c>
+      <c r="N2">
+        <v>0.113899439976645</v>
+      </c>
+      <c r="O2">
+        <v>0.0560148440366973</v>
+      </c>
+      <c r="P2">
+        <v>0.04455</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="S2">
+        <v>0.124392270584938</v>
+      </c>
+      <c r="T2">
+        <v>0.149624909055522</v>
+      </c>
+      <c r="U2">
+        <v>1.16060162251071</v>
+      </c>
+      <c r="V2">
+        <v>1.50274748391914</v>
+      </c>
+      <c r="W2">
+        <v>4.601620467808582</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0.0388</v>
+      </c>
+      <c r="AA2">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="AB2">
+        <v>0.07374819139040771</v>
+      </c>
+      <c r="AC2">
+        <v>0.06915412844036697</v>
+      </c>
+      <c r="AD2">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>9.76</v>
+      </c>
+      <c r="AH2">
+        <v>2.37</v>
+      </c>
+      <c r="AI2">
+        <v>6.210000000000001</v>
+      </c>
+      <c r="AJ2">
+        <v>8.98</v>
+      </c>
+      <c r="AK2">
+        <v>8.98</v>
+      </c>
+      <c r="AL2">
+        <v>0.601</v>
+      </c>
+      <c r="AM2">
+        <v>8.98</v>
+      </c>
+      <c r="AN2">
+        <v>0.588</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.1169958947793934</v>
+      </c>
+      <c r="C2">
+        <v>86.14889528974642</v>
+      </c>
+      <c r="D2">
+        <v>85.56089528974643</v>
+      </c>
+      <c r="E2">
+        <v>-8.98</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0.588</v>
+      </c>
+      <c r="H2">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>9.76</v>
+      </c>
+      <c r="K2">
+        <v>2.37</v>
+      </c>
+      <c r="L2">
+        <v>7.39</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>7.39</v>
+      </c>
+      <c r="O2">
+        <v>1.404099999999999</v>
+      </c>
+      <c r="P2">
+        <v>5.9859</v>
+      </c>
+      <c r="Q2">
+        <v>8.3559</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.1169958947793934</v>
+      </c>
+      <c r="T2">
+        <v>1.060309321559365</v>
+      </c>
+      <c r="U2">
+        <v>0.0457</v>
+      </c>
+      <c r="V2">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W2">
+        <v>0.03701700000000001</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.1168294925793126</v>
+      </c>
+      <c r="C3">
+        <v>85.47255862183368</v>
+      </c>
+      <c r="D3">
+        <v>85.74335862183369</v>
+      </c>
+      <c r="E3">
+        <v>-8.1212</v>
+      </c>
+      <c r="F3">
+        <v>0.8588000000000001</v>
+      </c>
+      <c r="G3">
+        <v>0.588</v>
+      </c>
+      <c r="H3">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>9.76</v>
+      </c>
+      <c r="K3">
+        <v>2.37</v>
+      </c>
+      <c r="L3">
+        <v>7.39</v>
+      </c>
+      <c r="M3">
+        <v>0.03924716000000001</v>
+      </c>
+      <c r="N3">
+        <v>7.350752839999999</v>
+      </c>
+      <c r="O3">
+        <v>1.3966430396</v>
+      </c>
+      <c r="P3">
+        <v>5.954109800399999</v>
+      </c>
+      <c r="Q3">
+        <v>8.324109800399999</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.117635679373043</v>
+      </c>
+      <c r="T3">
+        <v>1.068984579644851</v>
+      </c>
+      <c r="U3">
+        <v>0.0457</v>
+      </c>
+      <c r="V3">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W3">
+        <v>0.03701700000000001</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>188.2938790985131</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.1166630903792317</v>
+      </c>
+      <c r="C4">
+        <v>84.79700184333313</v>
+      </c>
+      <c r="D4">
+        <v>85.92660184333315</v>
+      </c>
+      <c r="E4">
+        <v>-7.2624</v>
+      </c>
+      <c r="F4">
+        <v>1.7176</v>
+      </c>
+      <c r="G4">
+        <v>0.588</v>
+      </c>
+      <c r="H4">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>9.76</v>
+      </c>
+      <c r="K4">
+        <v>2.37</v>
+      </c>
+      <c r="L4">
+        <v>7.39</v>
+      </c>
+      <c r="M4">
+        <v>0.07849432000000002</v>
+      </c>
+      <c r="N4">
+        <v>7.31150568</v>
+      </c>
+      <c r="O4">
+        <v>1.389186079199999</v>
+      </c>
+      <c r="P4">
+        <v>5.9223196008</v>
+      </c>
+      <c r="Q4">
+        <v>8.292319600799999</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.1182885207951344</v>
+      </c>
+      <c r="T4">
+        <v>1.077836883813714</v>
+      </c>
+      <c r="U4">
+        <v>0.0457</v>
+      </c>
+      <c r="V4">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W4">
+        <v>0.03701700000000001</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>94.14693954925653</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.1164966881791509</v>
+      </c>
+      <c r="C5">
+        <v>84.12222996508825</v>
+      </c>
+      <c r="D5">
+        <v>86.11062996508826</v>
+      </c>
+      <c r="E5">
+        <v>-6.403600000000001</v>
+      </c>
+      <c r="F5">
+        <v>2.5764</v>
+      </c>
+      <c r="G5">
+        <v>0.588</v>
+      </c>
+      <c r="H5">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>9.76</v>
+      </c>
+      <c r="K5">
+        <v>2.37</v>
+      </c>
+      <c r="L5">
+        <v>7.39</v>
+      </c>
+      <c r="M5">
+        <v>0.11774148</v>
+      </c>
+      <c r="N5">
+        <v>7.272258519999999</v>
+      </c>
+      <c r="O5">
+        <v>1.3817291188</v>
+      </c>
+      <c r="P5">
+        <v>5.8905294012</v>
+      </c>
+      <c r="Q5">
+        <v>8.260529401199999</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.118954822865104</v>
+      </c>
+      <c r="T5">
+        <v>1.086871709718018</v>
+      </c>
+      <c r="U5">
+        <v>0.0457</v>
+      </c>
+      <c r="V5">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W5">
+        <v>0.03701700000000001</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>62.76462636617103</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.11633028597907</v>
+      </c>
+      <c r="C6">
+        <v>83.44824804096132</v>
+      </c>
+      <c r="D6">
+        <v>86.29544804096132</v>
+      </c>
+      <c r="E6">
+        <v>-5.5448</v>
+      </c>
+      <c r="F6">
+        <v>3.4352</v>
+      </c>
+      <c r="G6">
+        <v>0.588</v>
+      </c>
+      <c r="H6">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>9.76</v>
+      </c>
+      <c r="K6">
+        <v>2.37</v>
+      </c>
+      <c r="L6">
+        <v>7.39</v>
+      </c>
+      <c r="M6">
+        <v>0.15698864</v>
+      </c>
+      <c r="N6">
+        <v>7.23301136</v>
+      </c>
+      <c r="O6">
+        <v>1.374272158399999</v>
+      </c>
+      <c r="P6">
+        <v>5.858739201600001</v>
+      </c>
+      <c r="Q6">
+        <v>8.2287392016</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.1196350062281979</v>
+      </c>
+      <c r="T6">
+        <v>1.096094761161994</v>
+      </c>
+      <c r="U6">
+        <v>0.0457</v>
+      </c>
+      <c r="V6">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W6">
+        <v>0.03701700000000001</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>47.07346977462826</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.1161638837789892</v>
+      </c>
+      <c r="C7">
+        <v>82.77506116829606</v>
+      </c>
+      <c r="D7">
+        <v>86.48106116829607</v>
+      </c>
+      <c r="E7">
+        <v>-4.686</v>
+      </c>
+      <c r="F7">
+        <v>4.294</v>
+      </c>
+      <c r="G7">
+        <v>0.588</v>
+      </c>
+      <c r="H7">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>9.76</v>
+      </c>
+      <c r="K7">
+        <v>2.37</v>
+      </c>
+      <c r="L7">
+        <v>7.39</v>
+      </c>
+      <c r="M7">
+        <v>0.1962358</v>
+      </c>
+      <c r="N7">
+        <v>7.193764199999999</v>
+      </c>
+      <c r="O7">
+        <v>1.366815198</v>
+      </c>
+      <c r="P7">
+        <v>5.826949002</v>
+      </c>
+      <c r="Q7">
+        <v>8.196949002</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.1203295092410412</v>
+      </c>
+      <c r="T7">
+        <v>1.105511982110054</v>
+      </c>
+      <c r="U7">
+        <v>0.0457</v>
+      </c>
+      <c r="V7">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W7">
+        <v>0.03701700000000001</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>37.65877581970261</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.1159974815789083</v>
+      </c>
+      <c r="C8">
+        <v>82.1026744883863</v>
+      </c>
+      <c r="D8">
+        <v>86.6674744883863</v>
+      </c>
+      <c r="E8">
+        <v>-3.8272</v>
+      </c>
+      <c r="F8">
+        <v>5.1528</v>
+      </c>
+      <c r="G8">
+        <v>0.588</v>
+      </c>
+      <c r="H8">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>9.76</v>
+      </c>
+      <c r="K8">
+        <v>2.37</v>
+      </c>
+      <c r="L8">
+        <v>7.39</v>
+      </c>
+      <c r="M8">
+        <v>0.23548296</v>
+      </c>
+      <c r="N8">
+        <v>7.15451704</v>
+      </c>
+      <c r="O8">
+        <v>1.3593582376</v>
+      </c>
+      <c r="P8">
+        <v>5.7951588024</v>
+      </c>
+      <c r="Q8">
+        <v>8.165158802400001</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.1210387889137323</v>
+      </c>
+      <c r="T8">
+        <v>1.115129569461264</v>
+      </c>
+      <c r="U8">
+        <v>0.0457</v>
+      </c>
+      <c r="V8">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W8">
+        <v>0.03701700000000001</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>31.38231318308552</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.1158310793788275</v>
+      </c>
+      <c r="C9">
+        <v>81.43109318695072</v>
+      </c>
+      <c r="D9">
+        <v>86.85469318695073</v>
+      </c>
+      <c r="E9">
+        <v>-2.968399999999999</v>
+      </c>
+      <c r="F9">
+        <v>6.011600000000001</v>
+      </c>
+      <c r="G9">
+        <v>0.588</v>
+      </c>
+      <c r="H9">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>9.76</v>
+      </c>
+      <c r="K9">
+        <v>2.37</v>
+      </c>
+      <c r="L9">
+        <v>7.39</v>
+      </c>
+      <c r="M9">
+        <v>0.2747301200000001</v>
+      </c>
+      <c r="N9">
+        <v>7.11526988</v>
+      </c>
+      <c r="O9">
+        <v>1.3519012772</v>
+      </c>
+      <c r="P9">
+        <v>5.7633686028</v>
+      </c>
+      <c r="Q9">
+        <v>8.133368602800001</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.1217633219127177</v>
+      </c>
+      <c r="T9">
+        <v>1.124953986647985</v>
+      </c>
+      <c r="U9">
+        <v>0.0457</v>
+      </c>
+      <c r="V9">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W9">
+        <v>0.03701700000000001</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>26.89912558550186</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.1156646771787466</v>
+      </c>
+      <c r="C10">
+        <v>80.76032249461367</v>
+      </c>
+      <c r="D10">
+        <v>87.04272249461368</v>
+      </c>
+      <c r="E10">
+        <v>-2.109599999999999</v>
+      </c>
+      <c r="F10">
+        <v>6.870400000000001</v>
+      </c>
+      <c r="G10">
+        <v>0.588</v>
+      </c>
+      <c r="H10">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>9.76</v>
+      </c>
+      <c r="K10">
+        <v>2.37</v>
+      </c>
+      <c r="L10">
+        <v>7.39</v>
+      </c>
+      <c r="M10">
+        <v>0.3139772800000001</v>
+      </c>
+      <c r="N10">
+        <v>7.076022719999999</v>
+      </c>
+      <c r="O10">
+        <v>1.3444443168</v>
+      </c>
+      <c r="P10">
+        <v>5.731578403199999</v>
+      </c>
+      <c r="Q10">
+        <v>8.1015784032</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.1225036056290724</v>
+      </c>
+      <c r="T10">
+        <v>1.134991978121373</v>
+      </c>
+      <c r="U10">
+        <v>0.0457</v>
+      </c>
+      <c r="V10">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W10">
+        <v>0.03701700000000001</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>23.53673488731413</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.1154982749786658</v>
+      </c>
+      <c r="C11">
+        <v>80.09036768739226</v>
+      </c>
+      <c r="D11">
+        <v>87.23156768739227</v>
+      </c>
+      <c r="E11">
+        <v>-1.2508</v>
+      </c>
+      <c r="F11">
+        <v>7.729200000000001</v>
+      </c>
+      <c r="G11">
+        <v>0.588</v>
+      </c>
+      <c r="H11">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>9.76</v>
+      </c>
+      <c r="K11">
+        <v>2.37</v>
+      </c>
+      <c r="L11">
+        <v>7.39</v>
+      </c>
+      <c r="M11">
+        <v>0.3532244400000001</v>
+      </c>
+      <c r="N11">
+        <v>7.03677556</v>
+      </c>
+      <c r="O11">
+        <v>1.3369873564</v>
+      </c>
+      <c r="P11">
+        <v>5.6997882036</v>
+      </c>
+      <c r="Q11">
+        <v>8.0697882036</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.1232601593172152</v>
+      </c>
+      <c r="T11">
+        <v>1.145250584791978</v>
+      </c>
+      <c r="U11">
+        <v>0.0457</v>
+      </c>
+      <c r="V11">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W11">
+        <v>0.03701700000000001</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>20.92154212205701</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.1153318727785849</v>
+      </c>
+      <c r="C12">
+        <v>79.42123408718987</v>
+      </c>
+      <c r="D12">
+        <v>87.42123408718987</v>
+      </c>
+      <c r="E12">
+        <v>-0.3919999999999995</v>
+      </c>
+      <c r="F12">
+        <v>8.588000000000001</v>
+      </c>
+      <c r="G12">
+        <v>0.588</v>
+      </c>
+      <c r="H12">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>9.76</v>
+      </c>
+      <c r="K12">
+        <v>2.37</v>
+      </c>
+      <c r="L12">
+        <v>7.39</v>
+      </c>
+      <c r="M12">
+        <v>0.3924716000000001</v>
+      </c>
+      <c r="N12">
+        <v>6.997528399999999</v>
+      </c>
+      <c r="O12">
+        <v>1.329530396</v>
+      </c>
+      <c r="P12">
+        <v>5.667998003999999</v>
+      </c>
+      <c r="Q12">
+        <v>8.037998003999999</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.1240335253095388</v>
+      </c>
+      <c r="T12">
+        <v>1.155737160499708</v>
+      </c>
+      <c r="U12">
+        <v>0.0457</v>
+      </c>
+      <c r="V12">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W12">
+        <v>0.03701700000000001</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>18.82938790985131</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.1151654705785041</v>
+      </c>
+      <c r="C13">
+        <v>78.75292706229617</v>
+      </c>
+      <c r="D13">
+        <v>87.61172706229617</v>
+      </c>
+      <c r="E13">
+        <v>0.466800000000001</v>
+      </c>
+      <c r="F13">
+        <v>9.446800000000001</v>
+      </c>
+      <c r="G13">
+        <v>0.588</v>
+      </c>
+      <c r="H13">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>9.76</v>
+      </c>
+      <c r="K13">
+        <v>2.37</v>
+      </c>
+      <c r="L13">
+        <v>7.39</v>
+      </c>
+      <c r="M13">
+        <v>0.4317187600000001</v>
+      </c>
+      <c r="N13">
+        <v>6.95828124</v>
+      </c>
+      <c r="O13">
+        <v>1.3220734356</v>
+      </c>
+      <c r="P13">
+        <v>5.6362078044</v>
+      </c>
+      <c r="Q13">
+        <v>8.006207804399999</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.124824270312926</v>
+      </c>
+      <c r="T13">
+        <v>1.166459389594129</v>
+      </c>
+      <c r="U13">
+        <v>0.0457</v>
+      </c>
+      <c r="V13">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W13">
+        <v>0.03701700000000001</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>17.1176253725921</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.1149990683784232</v>
+      </c>
+      <c r="C14">
+        <v>78.0854520278935</v>
+      </c>
+      <c r="D14">
+        <v>87.8030520278935</v>
+      </c>
+      <c r="E14">
+        <v>1.3256</v>
+      </c>
+      <c r="F14">
+        <v>10.3056</v>
+      </c>
+      <c r="G14">
+        <v>0.588</v>
+      </c>
+      <c r="H14">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>9.76</v>
+      </c>
+      <c r="K14">
+        <v>2.37</v>
+      </c>
+      <c r="L14">
+        <v>7.39</v>
+      </c>
+      <c r="M14">
+        <v>0.47096592</v>
+      </c>
+      <c r="N14">
+        <v>6.919034079999999</v>
+      </c>
+      <c r="O14">
+        <v>1.3146164752</v>
+      </c>
+      <c r="P14">
+        <v>5.6044176048</v>
+      </c>
+      <c r="Q14">
+        <v>7.9744176048</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.1256329867936628</v>
+      </c>
+      <c r="T14">
+        <v>1.177425305713422</v>
+      </c>
+      <c r="U14">
+        <v>0.0457</v>
+      </c>
+      <c r="V14">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W14">
+        <v>0.03701700000000001</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>15.69115659154276</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.1148326661783424</v>
+      </c>
+      <c r="C15">
+        <v>77.41881444657</v>
+      </c>
+      <c r="D15">
+        <v>87.99521444657</v>
+      </c>
+      <c r="E15">
+        <v>2.184400000000002</v>
+      </c>
+      <c r="F15">
+        <v>11.1644</v>
+      </c>
+      <c r="G15">
+        <v>0.588</v>
+      </c>
+      <c r="H15">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>9.76</v>
+      </c>
+      <c r="K15">
+        <v>2.37</v>
+      </c>
+      <c r="L15">
+        <v>7.39</v>
+      </c>
+      <c r="M15">
+        <v>0.5102130800000002</v>
+      </c>
+      <c r="N15">
+        <v>6.879786919999999</v>
+      </c>
+      <c r="O15">
+        <v>1.307159514799999</v>
+      </c>
+      <c r="P15">
+        <v>5.5726274052</v>
+      </c>
+      <c r="Q15">
+        <v>7.9426274052</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.1264602944578648</v>
+      </c>
+      <c r="T15">
+        <v>1.188643311858447</v>
+      </c>
+      <c r="U15">
+        <v>0.0457</v>
+      </c>
+      <c r="V15">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W15">
+        <v>0.03701700000000001</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>14.48414454603946</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.1146662639782616</v>
+      </c>
+      <c r="C16">
+        <v>76.75301982883964</v>
+      </c>
+      <c r="D16">
+        <v>88.18821982883965</v>
+      </c>
+      <c r="E16">
+        <v>3.043200000000002</v>
+      </c>
+      <c r="F16">
+        <v>12.0232</v>
+      </c>
+      <c r="G16">
+        <v>0.588</v>
+      </c>
+      <c r="H16">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>9.76</v>
+      </c>
+      <c r="K16">
+        <v>2.37</v>
+      </c>
+      <c r="L16">
+        <v>7.39</v>
+      </c>
+      <c r="M16">
+        <v>0.5494602400000002</v>
+      </c>
+      <c r="N16">
+        <v>6.84053976</v>
+      </c>
+      <c r="O16">
+        <v>1.2997025544</v>
+      </c>
+      <c r="P16">
+        <v>5.5408372056</v>
+      </c>
+      <c r="Q16">
+        <v>7.9108372056</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.1273068418351879</v>
+      </c>
+      <c r="T16">
+        <v>1.20012220186731</v>
+      </c>
+      <c r="U16">
+        <v>0.0457</v>
+      </c>
+      <c r="V16">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W16">
+        <v>0.03701700000000001</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>13.44956279275093</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.1146942617781807</v>
+      </c>
+      <c r="C17">
+        <v>75.86168672190713</v>
+      </c>
+      <c r="D17">
+        <v>88.15568672190714</v>
+      </c>
+      <c r="E17">
+        <v>3.902000000000001</v>
+      </c>
+      <c r="F17">
+        <v>12.882</v>
+      </c>
+      <c r="G17">
+        <v>0.588</v>
+      </c>
+      <c r="H17">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>9.76</v>
+      </c>
+      <c r="K17">
+        <v>2.37</v>
+      </c>
+      <c r="L17">
+        <v>7.39</v>
+      </c>
+      <c r="M17">
+        <v>0.6093186</v>
+      </c>
+      <c r="N17">
+        <v>6.7806814</v>
+      </c>
+      <c r="O17">
+        <v>1.288329466</v>
+      </c>
+      <c r="P17">
+        <v>5.492351934</v>
+      </c>
+      <c r="Q17">
+        <v>7.862351934</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.1281733079743302</v>
+      </c>
+      <c r="T17">
+        <v>1.211871183405792</v>
+      </c>
+      <c r="U17">
+        <v>0.0473</v>
+      </c>
+      <c r="V17">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W17">
+        <v>0.03831300000000001</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>12.12830200817766</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.1145408195780999</v>
+      </c>
+      <c r="C18">
+        <v>75.18148001671955</v>
+      </c>
+      <c r="D18">
+        <v>88.33428001671956</v>
+      </c>
+      <c r="E18">
+        <v>4.760800000000001</v>
+      </c>
+      <c r="F18">
+        <v>13.7408</v>
+      </c>
+      <c r="G18">
+        <v>0.588</v>
+      </c>
+      <c r="H18">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>9.76</v>
+      </c>
+      <c r="K18">
+        <v>2.37</v>
+      </c>
+      <c r="L18">
+        <v>7.39</v>
+      </c>
+      <c r="M18">
+        <v>0.6499398400000002</v>
+      </c>
+      <c r="N18">
+        <v>6.74006016</v>
+      </c>
+      <c r="O18">
+        <v>1.2806114304</v>
+      </c>
+      <c r="P18">
+        <v>5.4594487296</v>
+      </c>
+      <c r="Q18">
+        <v>7.8294487296</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.1290604042596427</v>
+      </c>
+      <c r="T18">
+        <v>1.223899902599953</v>
+      </c>
+      <c r="U18">
+        <v>0.0473</v>
+      </c>
+      <c r="V18">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W18">
+        <v>0.03831300000000001</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>11.37028313266655</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.114387377378019</v>
+      </c>
+      <c r="C19">
+        <v>74.50199839947726</v>
+      </c>
+      <c r="D19">
+        <v>88.51359839947726</v>
+      </c>
+      <c r="E19">
+        <v>5.619600000000002</v>
+      </c>
+      <c r="F19">
+        <v>14.5996</v>
+      </c>
+      <c r="G19">
+        <v>0.588</v>
+      </c>
+      <c r="H19">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>9.76</v>
+      </c>
+      <c r="K19">
+        <v>2.37</v>
+      </c>
+      <c r="L19">
+        <v>7.39</v>
+      </c>
+      <c r="M19">
+        <v>0.6905610800000002</v>
+      </c>
+      <c r="N19">
+        <v>6.69943892</v>
+      </c>
+      <c r="O19">
+        <v>1.2728933948</v>
+      </c>
+      <c r="P19">
+        <v>5.4265455252</v>
+      </c>
+      <c r="Q19">
+        <v>7.7965455252</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.1299688763590591</v>
+      </c>
+      <c r="T19">
+        <v>1.236218470449395</v>
+      </c>
+      <c r="U19">
+        <v>0.0473</v>
+      </c>
+      <c r="V19">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W19">
+        <v>0.03831300000000001</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>10.70144294839205</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.1147879751779382</v>
+      </c>
+      <c r="C20">
+        <v>73.1765672950331</v>
+      </c>
+      <c r="D20">
+        <v>88.0469672950331</v>
+      </c>
+      <c r="E20">
+        <v>6.478400000000001</v>
+      </c>
+      <c r="F20">
+        <v>15.4584</v>
+      </c>
+      <c r="G20">
+        <v>0.588</v>
+      </c>
+      <c r="H20">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>9.76</v>
+      </c>
+      <c r="K20">
+        <v>2.37</v>
+      </c>
+      <c r="L20">
+        <v>7.39</v>
+      </c>
+      <c r="M20">
+        <v>0.7899242400000001</v>
+      </c>
+      <c r="N20">
+        <v>6.600075759999999</v>
+      </c>
+      <c r="O20">
+        <v>1.2540143944</v>
+      </c>
+      <c r="P20">
+        <v>5.3460613656</v>
+      </c>
+      <c r="Q20">
+        <v>7.7160613656</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.1308995063145587</v>
+      </c>
+      <c r="T20">
+        <v>1.248837491173213</v>
+      </c>
+      <c r="U20">
+        <v>0.0511</v>
+      </c>
+      <c r="V20">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W20">
+        <v>0.041391</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>9.355327543816099</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1146653129778573</v>
+      </c>
+      <c r="C21">
+        <v>72.46012530154402</v>
+      </c>
+      <c r="D21">
+        <v>88.18932530154403</v>
+      </c>
+      <c r="E21">
+        <v>7.337200000000003</v>
+      </c>
+      <c r="F21">
+        <v>16.3172</v>
+      </c>
+      <c r="G21">
+        <v>0.588</v>
+      </c>
+      <c r="H21">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>9.76</v>
+      </c>
+      <c r="K21">
+        <v>2.37</v>
+      </c>
+      <c r="L21">
+        <v>7.39</v>
+      </c>
+      <c r="M21">
+        <v>0.8338089200000002</v>
+      </c>
+      <c r="N21">
+        <v>6.55619108</v>
+      </c>
+      <c r="O21">
+        <v>1.2456763052</v>
+      </c>
+      <c r="P21">
+        <v>5.3105147748</v>
+      </c>
+      <c r="Q21">
+        <v>7.6805147748</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.1318531147874782</v>
+      </c>
+      <c r="T21">
+        <v>1.261768092655645</v>
+      </c>
+      <c r="U21">
+        <v>0.0511</v>
+      </c>
+      <c r="V21">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W21">
+        <v>0.041391</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>8.862941883615251</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1145426507777765</v>
+      </c>
+      <c r="C22">
+        <v>71.74414439427514</v>
+      </c>
+      <c r="D22">
+        <v>88.33214439427515</v>
+      </c>
+      <c r="E22">
+        <v>8.196000000000002</v>
+      </c>
+      <c r="F22">
+        <v>17.176</v>
+      </c>
+      <c r="G22">
+        <v>0.588</v>
+      </c>
+      <c r="H22">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>9.76</v>
+      </c>
+      <c r="K22">
+        <v>2.37</v>
+      </c>
+      <c r="L22">
+        <v>7.39</v>
+      </c>
+      <c r="M22">
+        <v>0.8776936000000001</v>
+      </c>
+      <c r="N22">
+        <v>6.5123064</v>
+      </c>
+      <c r="O22">
+        <v>1.237338216</v>
+      </c>
+      <c r="P22">
+        <v>5.274968184</v>
+      </c>
+      <c r="Q22">
+        <v>7.644968184000001</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.1328305634722206</v>
+      </c>
+      <c r="T22">
+        <v>1.275021959175137</v>
+      </c>
+      <c r="U22">
+        <v>0.0511</v>
+      </c>
+      <c r="V22">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W22">
+        <v>0.041391</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>8.419794789434491</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1144199885776956</v>
+      </c>
+      <c r="C23">
+        <v>71.02862681699237</v>
+      </c>
+      <c r="D23">
+        <v>88.47542681699238</v>
+      </c>
+      <c r="E23">
+        <v>9.0548</v>
+      </c>
+      <c r="F23">
+        <v>18.0348</v>
+      </c>
+      <c r="G23">
+        <v>0.588</v>
+      </c>
+      <c r="H23">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>9.76</v>
+      </c>
+      <c r="K23">
+        <v>2.37</v>
+      </c>
+      <c r="L23">
+        <v>7.39</v>
+      </c>
+      <c r="M23">
+        <v>0.92157828</v>
+      </c>
+      <c r="N23">
+        <v>6.468421719999999</v>
+      </c>
+      <c r="O23">
+        <v>1.229000126799999</v>
+      </c>
+      <c r="P23">
+        <v>5.239421593199999</v>
+      </c>
+      <c r="Q23">
+        <v>7.6094215932</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.1338327576932856</v>
+      </c>
+      <c r="T23">
+        <v>1.288611366619173</v>
+      </c>
+      <c r="U23">
+        <v>0.0511</v>
+      </c>
+      <c r="V23">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W23">
+        <v>0.041391</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>8.0188521804138</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.1146359063776148</v>
+      </c>
+      <c r="C24">
+        <v>69.91792213993728</v>
+      </c>
+      <c r="D24">
+        <v>88.22352213993729</v>
+      </c>
+      <c r="E24">
+        <v>9.913600000000002</v>
+      </c>
+      <c r="F24">
+        <v>18.8936</v>
+      </c>
+      <c r="G24">
+        <v>0.588</v>
+      </c>
+      <c r="H24">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>9.76</v>
+      </c>
+      <c r="K24">
+        <v>2.37</v>
+      </c>
+      <c r="L24">
+        <v>7.39</v>
+      </c>
+      <c r="M24">
+        <v>1.0013608</v>
+      </c>
+      <c r="N24">
+        <v>6.388639199999999</v>
+      </c>
+      <c r="O24">
+        <v>1.213841447999999</v>
+      </c>
+      <c r="P24">
+        <v>5.174797752</v>
+      </c>
+      <c r="Q24">
+        <v>7.544797752</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.1348606492020702</v>
+      </c>
+      <c r="T24">
+        <v>1.302549220407928</v>
+      </c>
+      <c r="U24">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V24">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W24">
+        <v>0.04293000000000001</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>7.37995735403263</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.114528634177534</v>
+      </c>
+      <c r="C25">
+        <v>69.18409377611709</v>
+      </c>
+      <c r="D25">
+        <v>88.34849377611711</v>
+      </c>
+      <c r="E25">
+        <v>10.7724</v>
+      </c>
+      <c r="F25">
+        <v>19.7524</v>
+      </c>
+      <c r="G25">
+        <v>0.588</v>
+      </c>
+      <c r="H25">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>9.76</v>
+      </c>
+      <c r="K25">
+        <v>2.37</v>
+      </c>
+      <c r="L25">
+        <v>7.39</v>
+      </c>
+      <c r="M25">
+        <v>1.0468772</v>
+      </c>
+      <c r="N25">
+        <v>6.3431228</v>
+      </c>
+      <c r="O25">
+        <v>1.205193332</v>
+      </c>
+      <c r="P25">
+        <v>5.137929468</v>
+      </c>
+      <c r="Q25">
+        <v>7.507929468</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.1359152391916025</v>
+      </c>
+      <c r="T25">
+        <v>1.316849096373014</v>
+      </c>
+      <c r="U25">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V25">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W25">
+        <v>0.04293000000000001</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>7.059089642987734</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.1144213619774531</v>
+      </c>
+      <c r="C26">
+        <v>68.45061996772978</v>
+      </c>
+      <c r="D26">
+        <v>88.47381996772978</v>
+      </c>
+      <c r="E26">
+        <v>11.6312</v>
+      </c>
+      <c r="F26">
+        <v>20.6112</v>
+      </c>
+      <c r="G26">
+        <v>0.588</v>
+      </c>
+      <c r="H26">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>9.76</v>
+      </c>
+      <c r="K26">
+        <v>2.37</v>
+      </c>
+      <c r="L26">
+        <v>7.39</v>
+      </c>
+      <c r="M26">
+        <v>1.0923936</v>
+      </c>
+      <c r="N26">
+        <v>6.297606399999999</v>
+      </c>
+      <c r="O26">
+        <v>1.196545216</v>
+      </c>
+      <c r="P26">
+        <v>5.101061184</v>
+      </c>
+      <c r="Q26">
+        <v>7.471061184</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.1369975815492804</v>
+      </c>
+      <c r="T26">
+        <v>1.331525284863498</v>
+      </c>
+      <c r="U26">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V26">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W26">
+        <v>0.04293000000000001</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>6.764960907863245</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.1143140897773722</v>
+      </c>
+      <c r="C27">
+        <v>67.71750222577559</v>
+      </c>
+      <c r="D27">
+        <v>88.59950222577559</v>
+      </c>
+      <c r="E27">
+        <v>12.49</v>
+      </c>
+      <c r="F27">
+        <v>21.47</v>
+      </c>
+      <c r="G27">
+        <v>0.588</v>
+      </c>
+      <c r="H27">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>9.76</v>
+      </c>
+      <c r="K27">
+        <v>2.37</v>
+      </c>
+      <c r="L27">
+        <v>7.39</v>
+      </c>
+      <c r="M27">
+        <v>1.13791</v>
+      </c>
+      <c r="N27">
+        <v>6.252089999999999</v>
+      </c>
+      <c r="O27">
+        <v>1.187897099999999</v>
+      </c>
+      <c r="P27">
+        <v>5.0641929</v>
+      </c>
+      <c r="Q27">
+        <v>7.4341929</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.1381087863698297</v>
+      </c>
+      <c r="T27">
+        <v>1.346592838380394</v>
+      </c>
+      <c r="U27">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V27">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W27">
+        <v>0.04293000000000001</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>6.494362471548714</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.1142068175772914</v>
+      </c>
+      <c r="C28">
+        <v>66.98474206985316</v>
+      </c>
+      <c r="D28">
+        <v>88.72554206985316</v>
+      </c>
+      <c r="E28">
+        <v>13.3488</v>
+      </c>
+      <c r="F28">
+        <v>22.3288</v>
+      </c>
+      <c r="G28">
+        <v>0.588</v>
+      </c>
+      <c r="H28">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>9.76</v>
+      </c>
+      <c r="K28">
+        <v>2.37</v>
+      </c>
+      <c r="L28">
+        <v>7.39</v>
+      </c>
+      <c r="M28">
+        <v>1.1834264</v>
+      </c>
+      <c r="N28">
+        <v>6.2065736</v>
+      </c>
+      <c r="O28">
+        <v>1.179248984</v>
+      </c>
+      <c r="P28">
+        <v>5.027324616</v>
+      </c>
+      <c r="Q28">
+        <v>7.397324616</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.1392500237530965</v>
+      </c>
+      <c r="T28">
+        <v>1.362067623073423</v>
+      </c>
+      <c r="U28">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V28">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W28">
+        <v>0.04293000000000001</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>6.244579299566071</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.1145369453772105</v>
+      </c>
+      <c r="C29">
+        <v>65.73919861387837</v>
+      </c>
+      <c r="D29">
+        <v>88.33879861387838</v>
+      </c>
+      <c r="E29">
+        <v>14.2076</v>
+      </c>
+      <c r="F29">
+        <v>23.1876</v>
+      </c>
+      <c r="G29">
+        <v>0.588</v>
+      </c>
+      <c r="H29">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>9.76</v>
+      </c>
+      <c r="K29">
+        <v>2.37</v>
+      </c>
+      <c r="L29">
+        <v>7.39</v>
+      </c>
+      <c r="M29">
+        <v>1.275318</v>
+      </c>
+      <c r="N29">
+        <v>6.114681999999999</v>
+      </c>
+      <c r="O29">
+        <v>1.16178958</v>
+      </c>
+      <c r="P29">
+        <v>4.95289242</v>
+      </c>
+      <c r="Q29">
+        <v>7.32289242</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.140422527913987</v>
+      </c>
+      <c r="T29">
+        <v>1.37796637447037</v>
+      </c>
+      <c r="U29">
+        <v>0.055</v>
+      </c>
+      <c r="V29">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W29">
+        <v>0.04455000000000001</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>5.794633181684881</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1144458731771297</v>
+      </c>
+      <c r="C30">
+        <v>64.98675218485808</v>
+      </c>
+      <c r="D30">
+        <v>88.44515218485809</v>
+      </c>
+      <c r="E30">
+        <v>15.06640000000001</v>
+      </c>
+      <c r="F30">
+        <v>24.04640000000001</v>
+      </c>
+      <c r="G30">
+        <v>0.588</v>
+      </c>
+      <c r="H30">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>9.76</v>
+      </c>
+      <c r="K30">
+        <v>2.37</v>
+      </c>
+      <c r="L30">
+        <v>7.39</v>
+      </c>
+      <c r="M30">
+        <v>1.322552</v>
+      </c>
+      <c r="N30">
+        <v>6.067447999999999</v>
+      </c>
+      <c r="O30">
+        <v>1.152815119999999</v>
+      </c>
+      <c r="P30">
+        <v>4.914632879999999</v>
+      </c>
+      <c r="Q30">
+        <v>7.284632879999999</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.1416276016349023</v>
+      </c>
+      <c r="T30">
+        <v>1.394306757850565</v>
+      </c>
+      <c r="U30">
+        <v>0.055</v>
+      </c>
+      <c r="V30">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W30">
+        <v>0.04455000000000001</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>5.587681996624705</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1143548009770488</v>
+      </c>
+      <c r="C31">
+        <v>64.23456214864328</v>
+      </c>
+      <c r="D31">
+        <v>88.55176214864328</v>
+      </c>
+      <c r="E31">
+        <v>15.9252</v>
+      </c>
+      <c r="F31">
+        <v>24.9052</v>
+      </c>
+      <c r="G31">
+        <v>0.588</v>
+      </c>
+      <c r="H31">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>9.76</v>
+      </c>
+      <c r="K31">
+        <v>2.37</v>
+      </c>
+      <c r="L31">
+        <v>7.39</v>
+      </c>
+      <c r="M31">
+        <v>1.369786</v>
+      </c>
+      <c r="N31">
+        <v>6.020213999999999</v>
+      </c>
+      <c r="O31">
+        <v>1.14384066</v>
+      </c>
+      <c r="P31">
+        <v>4.87637334</v>
+      </c>
+      <c r="Q31">
+        <v>7.24637334</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.142866621094435</v>
+      </c>
+      <c r="T31">
+        <v>1.411107433720344</v>
+      </c>
+      <c r="U31">
+        <v>0.055</v>
+      </c>
+      <c r="V31">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W31">
+        <v>0.04455000000000001</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>5.395003307085924</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.114263728776968</v>
+      </c>
+      <c r="C32">
+        <v>63.48262943350468</v>
+      </c>
+      <c r="D32">
+        <v>88.65862943350469</v>
+      </c>
+      <c r="E32">
+        <v>16.784</v>
+      </c>
+      <c r="F32">
+        <v>25.764</v>
+      </c>
+      <c r="G32">
+        <v>0.588</v>
+      </c>
+      <c r="H32">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>9.76</v>
+      </c>
+      <c r="K32">
+        <v>2.37</v>
+      </c>
+      <c r="L32">
+        <v>7.39</v>
+      </c>
+      <c r="M32">
+        <v>1.41702</v>
+      </c>
+      <c r="N32">
+        <v>5.97298</v>
+      </c>
+      <c r="O32">
+        <v>1.1348662</v>
+      </c>
+      <c r="P32">
+        <v>4.8381138</v>
+      </c>
+      <c r="Q32">
+        <v>7.2081138</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1441410411099543</v>
+      </c>
+      <c r="T32">
+        <v>1.428388128900688</v>
+      </c>
+      <c r="U32">
+        <v>0.055</v>
+      </c>
+      <c r="V32">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W32">
+        <v>0.04455000000000001</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>5.215169863516393</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.1141726565768872</v>
+      </c>
+      <c r="C33">
+        <v>62.73095497219954</v>
+      </c>
+      <c r="D33">
+        <v>88.76575497219955</v>
+      </c>
+      <c r="E33">
+        <v>17.6428</v>
+      </c>
+      <c r="F33">
+        <v>26.6228</v>
+      </c>
+      <c r="G33">
+        <v>0.588</v>
+      </c>
+      <c r="H33">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>9.76</v>
+      </c>
+      <c r="K33">
+        <v>2.37</v>
+      </c>
+      <c r="L33">
+        <v>7.39</v>
+      </c>
+      <c r="M33">
+        <v>1.464254</v>
+      </c>
+      <c r="N33">
+        <v>5.925745999999999</v>
+      </c>
+      <c r="O33">
+        <v>1.125891739999999</v>
+      </c>
+      <c r="P33">
+        <v>4.79985426</v>
+      </c>
+      <c r="Q33">
+        <v>7.16985426</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1454524008360684</v>
+      </c>
+      <c r="T33">
+        <v>1.446169713796404</v>
+      </c>
+      <c r="U33">
+        <v>0.055</v>
+      </c>
+      <c r="V33">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W33">
+        <v>0.04455000000000001</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>5.046938577596509</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.1140815843768063</v>
+      </c>
+      <c r="C34">
+        <v>61.97953970199868</v>
+      </c>
+      <c r="D34">
+        <v>88.87313970199868</v>
+      </c>
+      <c r="E34">
+        <v>18.5016</v>
+      </c>
+      <c r="F34">
+        <v>27.4816</v>
+      </c>
+      <c r="G34">
+        <v>0.588</v>
+      </c>
+      <c r="H34">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>9.76</v>
+      </c>
+      <c r="K34">
+        <v>2.37</v>
+      </c>
+      <c r="L34">
+        <v>7.39</v>
+      </c>
+      <c r="M34">
+        <v>1.511488</v>
+      </c>
+      <c r="N34">
+        <v>5.878512</v>
+      </c>
+      <c r="O34">
+        <v>1.11691728</v>
+      </c>
+      <c r="P34">
+        <v>4.76159472</v>
+      </c>
+      <c r="Q34">
+        <v>7.13159472</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1468023299658917</v>
+      </c>
+      <c r="T34">
+        <v>1.464474286483171</v>
+      </c>
+      <c r="U34">
+        <v>0.055</v>
+      </c>
+      <c r="V34">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W34">
+        <v>0.04455000000000001</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>4.889221747046618</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.1139905121767254</v>
+      </c>
+      <c r="C35">
+        <v>61.22838456471396</v>
+      </c>
+      <c r="D35">
+        <v>88.98078456471397</v>
+      </c>
+      <c r="E35">
+        <v>19.36040000000001</v>
+      </c>
+      <c r="F35">
+        <v>28.34040000000001</v>
+      </c>
+      <c r="G35">
+        <v>0.588</v>
+      </c>
+      <c r="H35">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>9.76</v>
+      </c>
+      <c r="K35">
+        <v>2.37</v>
+      </c>
+      <c r="L35">
+        <v>7.39</v>
+      </c>
+      <c r="M35">
+        <v>1.558722</v>
+      </c>
+      <c r="N35">
+        <v>5.831277999999999</v>
+      </c>
+      <c r="O35">
+        <v>1.10794282</v>
+      </c>
+      <c r="P35">
+        <v>4.723335179999999</v>
+      </c>
+      <c r="Q35">
+        <v>7.09333518</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1481925554876499</v>
+      </c>
+      <c r="T35">
+        <v>1.483325264324766</v>
+      </c>
+      <c r="U35">
+        <v>0.055</v>
+      </c>
+      <c r="V35">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W35">
+        <v>0.04455000000000001</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>4.74106351228763</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.1138994399766446</v>
+      </c>
+      <c r="C36">
+        <v>60.47749050672559</v>
+      </c>
+      <c r="D36">
+        <v>89.0886905067256</v>
+      </c>
+      <c r="E36">
+        <v>20.2192</v>
+      </c>
+      <c r="F36">
+        <v>29.1992</v>
+      </c>
+      <c r="G36">
+        <v>0.588</v>
+      </c>
+      <c r="H36">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>9.76</v>
+      </c>
+      <c r="K36">
+        <v>2.37</v>
+      </c>
+      <c r="L36">
+        <v>7.39</v>
+      </c>
+      <c r="M36">
+        <v>1.605956</v>
+      </c>
+      <c r="N36">
+        <v>5.784044</v>
+      </c>
+      <c r="O36">
+        <v>1.09896836</v>
+      </c>
+      <c r="P36">
+        <v>4.68507564</v>
+      </c>
+      <c r="Q36">
+        <v>7.05507564</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1496249090555222</v>
+      </c>
+      <c r="T36">
+        <v>1.502747483919137</v>
+      </c>
+      <c r="U36">
+        <v>0.055</v>
+      </c>
+      <c r="V36">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W36">
+        <v>0.04455000000000001</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>4.601620467808582</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.1148856677765638</v>
+      </c>
+      <c r="C37">
+        <v>58.46391660772871</v>
+      </c>
+      <c r="D37">
+        <v>87.93391660772872</v>
+      </c>
+      <c r="E37">
+        <v>21.07800000000001</v>
+      </c>
+      <c r="F37">
+        <v>30.05800000000001</v>
+      </c>
+      <c r="G37">
+        <v>0.588</v>
+      </c>
+      <c r="H37">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>9.76</v>
+      </c>
+      <c r="K37">
+        <v>2.37</v>
+      </c>
+      <c r="L37">
+        <v>7.39</v>
+      </c>
+      <c r="M37">
+        <v>1.767410400000001</v>
+      </c>
+      <c r="N37">
+        <v>5.6225896</v>
+      </c>
+      <c r="O37">
+        <v>1.068292024</v>
+      </c>
+      <c r="P37">
+        <v>4.554297576</v>
+      </c>
+      <c r="Q37">
+        <v>6.924297576</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1511013350408673</v>
+      </c>
+      <c r="T37">
+        <v>1.522767310270258</v>
+      </c>
+      <c r="U37">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="V37">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W37">
+        <v>0.04762800000000001</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>4.181258636930052</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.1148253755764829</v>
+      </c>
+      <c r="C38">
+        <v>57.67485291950361</v>
+      </c>
+      <c r="D38">
+        <v>88.00365291950362</v>
+      </c>
+      <c r="E38">
+        <v>21.9368</v>
+      </c>
+      <c r="F38">
+        <v>30.9168</v>
+      </c>
+      <c r="G38">
+        <v>0.588</v>
+      </c>
+      <c r="H38">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>9.76</v>
+      </c>
+      <c r="K38">
+        <v>2.37</v>
+      </c>
+      <c r="L38">
+        <v>7.39</v>
+      </c>
+      <c r="M38">
+        <v>1.81790784</v>
+      </c>
+      <c r="N38">
+        <v>5.57209216</v>
+      </c>
+      <c r="O38">
+        <v>1.0586975104</v>
+      </c>
+      <c r="P38">
+        <v>4.5133946496</v>
+      </c>
+      <c r="Q38">
+        <v>6.8833946496</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1526238993382545</v>
+      </c>
+      <c r="T38">
+        <v>1.543412756194851</v>
+      </c>
+      <c r="U38">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="V38">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W38">
+        <v>0.04762800000000001</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>4.065112563681995</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.1160238233764021</v>
+      </c>
+      <c r="C39">
+        <v>55.45031136961737</v>
+      </c>
+      <c r="D39">
+        <v>86.63791136961738</v>
+      </c>
+      <c r="E39">
+        <v>22.7956</v>
+      </c>
+      <c r="F39">
+        <v>31.7756</v>
+      </c>
+      <c r="G39">
+        <v>0.588</v>
+      </c>
+      <c r="H39">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>9.76</v>
+      </c>
+      <c r="K39">
+        <v>2.37</v>
+      </c>
+      <c r="L39">
+        <v>7.39</v>
+      </c>
+      <c r="M39">
+        <v>2.0018628</v>
+      </c>
+      <c r="N39">
+        <v>5.388137199999999</v>
+      </c>
+      <c r="O39">
+        <v>1.023746067999999</v>
+      </c>
+      <c r="P39">
+        <v>4.364391132</v>
+      </c>
+      <c r="Q39">
+        <v>6.734391132</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.154194799010162</v>
+      </c>
+      <c r="T39">
+        <v>1.564713613101178</v>
+      </c>
+      <c r="U39">
+        <v>0.063</v>
+      </c>
+      <c r="V39">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W39">
+        <v>0.05103000000000001</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>3.691561679451758</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.1159975511763212</v>
+      </c>
+      <c r="C40">
+        <v>54.62099635336885</v>
+      </c>
+      <c r="D40">
+        <v>86.66739635336886</v>
+      </c>
+      <c r="E40">
+        <v>23.65440000000001</v>
+      </c>
+      <c r="F40">
+        <v>32.63440000000001</v>
+      </c>
+      <c r="G40">
+        <v>0.588</v>
+      </c>
+      <c r="H40">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>9.76</v>
+      </c>
+      <c r="K40">
+        <v>2.37</v>
+      </c>
+      <c r="L40">
+        <v>7.39</v>
+      </c>
+      <c r="M40">
+        <v>2.0559672</v>
+      </c>
+      <c r="N40">
+        <v>5.334032799999999</v>
+      </c>
+      <c r="O40">
+        <v>1.013466232</v>
+      </c>
+      <c r="P40">
+        <v>4.320566567999999</v>
+      </c>
+      <c r="Q40">
+        <v>6.690566567999999</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1558163728650342</v>
+      </c>
+      <c r="T40">
+        <v>1.586701594423837</v>
+      </c>
+      <c r="U40">
+        <v>0.063</v>
+      </c>
+      <c r="V40">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W40">
+        <v>0.05103000000000001</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>3.594415319466185</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.1159712789762404</v>
+      </c>
+      <c r="C41">
+        <v>53.79170141286365</v>
+      </c>
+      <c r="D41">
+        <v>86.69690141286365</v>
+      </c>
+      <c r="E41">
+        <v>24.5132</v>
+      </c>
+      <c r="F41">
+        <v>33.4932</v>
+      </c>
+      <c r="G41">
+        <v>0.588</v>
+      </c>
+      <c r="H41">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>9.76</v>
+      </c>
+      <c r="K41">
+        <v>2.37</v>
+      </c>
+      <c r="L41">
+        <v>7.39</v>
+      </c>
+      <c r="M41">
+        <v>2.1100716</v>
+      </c>
+      <c r="N41">
+        <v>5.279928399999999</v>
+      </c>
+      <c r="O41">
+        <v>1.003186396</v>
+      </c>
+      <c r="P41">
+        <v>4.276742004</v>
+      </c>
+      <c r="Q41">
+        <v>6.646742004</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1574911130758039</v>
+      </c>
+      <c r="T41">
+        <v>1.609410493166912</v>
+      </c>
+      <c r="U41">
+        <v>0.063</v>
+      </c>
+      <c r="V41">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W41">
+        <v>0.05103000000000001</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>3.502250824095258</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.1182454067761595</v>
+      </c>
+      <c r="C42">
+        <v>50.45119930231435</v>
+      </c>
+      <c r="D42">
+        <v>84.21519930231436</v>
+      </c>
+      <c r="E42">
+        <v>25.372</v>
+      </c>
+      <c r="F42">
+        <v>34.352</v>
+      </c>
+      <c r="G42">
+        <v>0.588</v>
+      </c>
+      <c r="H42">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>9.76</v>
+      </c>
+      <c r="K42">
+        <v>2.37</v>
+      </c>
+      <c r="L42">
+        <v>7.39</v>
+      </c>
+      <c r="M42">
+        <v>2.4080752</v>
+      </c>
+      <c r="N42">
+        <v>4.9819248</v>
+      </c>
+      <c r="O42">
+        <v>0.9465657119999997</v>
+      </c>
+      <c r="P42">
+        <v>4.035359088</v>
+      </c>
+      <c r="Q42">
+        <v>6.405359088</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1592216779602659</v>
+      </c>
+      <c r="T42">
+        <v>1.632876355201423</v>
+      </c>
+      <c r="U42">
+        <v>0.0701</v>
+      </c>
+      <c r="V42">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W42">
+        <v>0.056781</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>3.068841039515709</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.1253503745760787</v>
+      </c>
+      <c r="C43">
+        <v>42.67912732356902</v>
+      </c>
+      <c r="D43">
+        <v>77.30192732356903</v>
+      </c>
+      <c r="E43">
+        <v>26.23080000000001</v>
+      </c>
+      <c r="F43">
+        <v>35.21080000000001</v>
+      </c>
+      <c r="G43">
+        <v>0.588</v>
+      </c>
+      <c r="H43">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>9.76</v>
+      </c>
+      <c r="K43">
+        <v>2.37</v>
+      </c>
+      <c r="L43">
+        <v>7.39</v>
+      </c>
+      <c r="M43">
+        <v>3.218267120000001</v>
+      </c>
+      <c r="N43">
+        <v>4.171732879999999</v>
+      </c>
+      <c r="O43">
+        <v>0.7926292471999995</v>
+      </c>
+      <c r="P43">
+        <v>3.379103632799999</v>
+      </c>
+      <c r="Q43">
+        <v>5.749103632799999</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1610109060611503</v>
+      </c>
+      <c r="T43">
+        <v>1.657137670186255</v>
+      </c>
+      <c r="U43">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V43">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W43">
+        <v>0.07403400000000002</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>2.29626681827455</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.1255541423759979</v>
+      </c>
+      <c r="C44">
+        <v>41.63876085044354</v>
+      </c>
+      <c r="D44">
+        <v>77.12036085044355</v>
+      </c>
+      <c r="E44">
+        <v>27.0896</v>
+      </c>
+      <c r="F44">
+        <v>36.0696</v>
+      </c>
+      <c r="G44">
+        <v>0.588</v>
+      </c>
+      <c r="H44">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>9.76</v>
+      </c>
+      <c r="K44">
+        <v>2.37</v>
+      </c>
+      <c r="L44">
+        <v>7.39</v>
+      </c>
+      <c r="M44">
+        <v>3.29676144</v>
+      </c>
+      <c r="N44">
+        <v>4.09323856</v>
+      </c>
+      <c r="O44">
+        <v>0.7777153263999997</v>
+      </c>
+      <c r="P44">
+        <v>3.3155232336</v>
+      </c>
+      <c r="Q44">
+        <v>5.6855232336</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1628618316827549</v>
+      </c>
+      <c r="T44">
+        <v>1.682235582239531</v>
+      </c>
+      <c r="U44">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V44">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W44">
+        <v>0.07403400000000002</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>2.241593798791822</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.125757910175917</v>
+      </c>
+      <c r="C45">
+        <v>40.59924530394897</v>
+      </c>
+      <c r="D45">
+        <v>76.93964530394898</v>
+      </c>
+      <c r="E45">
+        <v>27.9484</v>
+      </c>
+      <c r="F45">
+        <v>36.9284</v>
+      </c>
+      <c r="G45">
+        <v>0.588</v>
+      </c>
+      <c r="H45">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>9.76</v>
+      </c>
+      <c r="K45">
+        <v>2.37</v>
+      </c>
+      <c r="L45">
+        <v>7.39</v>
+      </c>
+      <c r="M45">
+        <v>3.375255760000001</v>
+      </c>
+      <c r="N45">
+        <v>4.014744239999999</v>
+      </c>
+      <c r="O45">
+        <v>0.7628014055999995</v>
+      </c>
+      <c r="P45">
+        <v>3.251942834399999</v>
+      </c>
+      <c r="Q45">
+        <v>5.6219428344</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1647777020630123</v>
+      </c>
+      <c r="T45">
+        <v>1.708214122785904</v>
+      </c>
+      <c r="U45">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V45">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W45">
+        <v>0.07403400000000002</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>2.189463710447826</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.1259616779758362</v>
+      </c>
+      <c r="C46">
+        <v>39.56057471616047</v>
+      </c>
+      <c r="D46">
+        <v>76.75977471616048</v>
+      </c>
+      <c r="E46">
+        <v>28.80720000000001</v>
+      </c>
+      <c r="F46">
+        <v>37.78720000000001</v>
+      </c>
+      <c r="G46">
+        <v>0.588</v>
+      </c>
+      <c r="H46">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>9.76</v>
+      </c>
+      <c r="K46">
+        <v>2.37</v>
+      </c>
+      <c r="L46">
+        <v>7.39</v>
+      </c>
+      <c r="M46">
+        <v>3.453750080000001</v>
+      </c>
+      <c r="N46">
+        <v>3.936249919999999</v>
+      </c>
+      <c r="O46">
+        <v>0.7478874847999996</v>
+      </c>
+      <c r="P46">
+        <v>3.188362435199999</v>
+      </c>
+      <c r="Q46">
+        <v>5.558362435199999</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1667619963854217</v>
+      </c>
+      <c r="T46">
+        <v>1.73512046835179</v>
+      </c>
+      <c r="U46">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V46">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W46">
+        <v>0.07403400000000002</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>2.139703171574012</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.1261654457757553</v>
+      </c>
+      <c r="C47">
+        <v>38.52274317483064</v>
+      </c>
+      <c r="D47">
+        <v>76.58074317483066</v>
+      </c>
+      <c r="E47">
+        <v>29.66600000000001</v>
+      </c>
+      <c r="F47">
+        <v>38.64600000000001</v>
+      </c>
+      <c r="G47">
+        <v>0.588</v>
+      </c>
+      <c r="H47">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>9.76</v>
+      </c>
+      <c r="K47">
+        <v>2.37</v>
+      </c>
+      <c r="L47">
+        <v>7.39</v>
+      </c>
+      <c r="M47">
+        <v>3.532244400000001</v>
+      </c>
+      <c r="N47">
+        <v>3.857755599999999</v>
+      </c>
+      <c r="O47">
+        <v>0.7329735639999996</v>
+      </c>
+      <c r="P47">
+        <v>3.124782035999999</v>
+      </c>
+      <c r="Q47">
+        <v>5.494782035999999</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1688184468650096</v>
+      </c>
+      <c r="T47">
+        <v>1.763005226483708</v>
+      </c>
+      <c r="U47">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V47">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W47">
+        <v>0.07403400000000002</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>2.092154212205701</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.1263692135756744</v>
+      </c>
+      <c r="C48">
+        <v>37.48574482274172</v>
+      </c>
+      <c r="D48">
+        <v>76.40254482274173</v>
+      </c>
+      <c r="E48">
+        <v>30.5248</v>
+      </c>
+      <c r="F48">
+        <v>39.5048</v>
+      </c>
+      <c r="G48">
+        <v>0.588</v>
+      </c>
+      <c r="H48">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>9.76</v>
+      </c>
+      <c r="K48">
+        <v>2.37</v>
+      </c>
+      <c r="L48">
+        <v>7.39</v>
+      </c>
+      <c r="M48">
+        <v>3.610738720000001</v>
+      </c>
+      <c r="N48">
+        <v>3.779261279999999</v>
+      </c>
+      <c r="O48">
+        <v>0.7180596431999996</v>
+      </c>
+      <c r="P48">
+        <v>3.061201636799999</v>
+      </c>
+      <c r="Q48">
+        <v>5.431201636799999</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.1709510621771749</v>
+      </c>
+      <c r="T48">
+        <v>1.791922753435327</v>
+      </c>
+      <c r="U48">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V48">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W48">
+        <v>0.07403400000000002</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>2.046672598896881</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.1265729813755936</v>
+      </c>
+      <c r="C49">
+        <v>36.44957385706678</v>
+      </c>
+      <c r="D49">
+        <v>76.22517385706679</v>
+      </c>
+      <c r="E49">
+        <v>31.3836</v>
+      </c>
+      <c r="F49">
+        <v>40.36360000000001</v>
+      </c>
+      <c r="G49">
+        <v>0.588</v>
+      </c>
+      <c r="H49">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>9.76</v>
+      </c>
+      <c r="K49">
+        <v>2.37</v>
+      </c>
+      <c r="L49">
+        <v>7.39</v>
+      </c>
+      <c r="M49">
+        <v>3.689233040000001</v>
+      </c>
+      <c r="N49">
+        <v>3.700766959999999</v>
+      </c>
+      <c r="O49">
+        <v>0.7031457223999996</v>
+      </c>
+      <c r="P49">
+        <v>2.997621237599999</v>
+      </c>
+      <c r="Q49">
+        <v>5.3676212376</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1731641535388558</v>
+      </c>
+      <c r="T49">
+        <v>1.821931507819083</v>
+      </c>
+      <c r="U49">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V49">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W49">
+        <v>0.07403400000000002</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>2.003126373388437</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.1349804291755127</v>
+      </c>
+      <c r="C50">
+        <v>28.92768058812754</v>
+      </c>
+      <c r="D50">
+        <v>69.56208058812754</v>
+      </c>
+      <c r="E50">
+        <v>32.2424</v>
+      </c>
+      <c r="F50">
+        <v>41.2224</v>
+      </c>
+      <c r="G50">
+        <v>0.588</v>
+      </c>
+      <c r="H50">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>9.76</v>
+      </c>
+      <c r="K50">
+        <v>2.37</v>
+      </c>
+      <c r="L50">
+        <v>7.39</v>
+      </c>
+      <c r="M50">
+        <v>4.63752</v>
+      </c>
+      <c r="N50">
+        <v>2.752479999999999</v>
+      </c>
+      <c r="O50">
+        <v>0.5229711999999997</v>
+      </c>
+      <c r="P50">
+        <v>2.2295088</v>
+      </c>
+      <c r="Q50">
+        <v>4.5995088</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.175462363799063</v>
+      </c>
+      <c r="T50">
+        <v>1.853094445063752</v>
+      </c>
+      <c r="U50">
+        <v>0.1125</v>
+      </c>
+      <c r="V50">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W50">
+        <v>0.09112500000000001</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>1.593524124963342</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.1353551069754319</v>
+      </c>
+      <c r="C51">
+        <v>27.79894802703377</v>
+      </c>
+      <c r="D51">
+        <v>69.29214802703378</v>
+      </c>
+      <c r="E51">
+        <v>33.10120000000001</v>
+      </c>
+      <c r="F51">
+        <v>42.0812</v>
+      </c>
+      <c r="G51">
+        <v>0.588</v>
+      </c>
+      <c r="H51">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>9.76</v>
+      </c>
+      <c r="K51">
+        <v>2.37</v>
+      </c>
+      <c r="L51">
+        <v>7.39</v>
+      </c>
+      <c r="M51">
+        <v>4.734135</v>
+      </c>
+      <c r="N51">
+        <v>2.655864999999999</v>
+      </c>
+      <c r="O51">
+        <v>0.5046143499999998</v>
+      </c>
+      <c r="P51">
+        <v>2.15125065</v>
+      </c>
+      <c r="Q51">
+        <v>4.52125065</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.1778506999518273</v>
+      </c>
+      <c r="T51">
+        <v>1.885479458278801</v>
+      </c>
+      <c r="U51">
+        <v>0.1125</v>
+      </c>
+      <c r="V51">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W51">
+        <v>0.09112500000000001</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>1.561003224453887</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.1357297847753511</v>
+      </c>
+      <c r="C52">
+        <v>26.67230229071431</v>
+      </c>
+      <c r="D52">
+        <v>69.02430229071432</v>
+      </c>
+      <c r="E52">
+        <v>33.96000000000001</v>
+      </c>
+      <c r="F52">
+        <v>42.94</v>
+      </c>
+      <c r="G52">
+        <v>0.588</v>
+      </c>
+      <c r="H52">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>9.76</v>
+      </c>
+      <c r="K52">
+        <v>2.37</v>
+      </c>
+      <c r="L52">
+        <v>7.39</v>
+      </c>
+      <c r="M52">
+        <v>4.830750000000001</v>
+      </c>
+      <c r="N52">
+        <v>2.559249999999999</v>
+      </c>
+      <c r="O52">
+        <v>0.4862574999999996</v>
+      </c>
+      <c r="P52">
+        <v>2.072992499999999</v>
+      </c>
+      <c r="Q52">
+        <v>4.442992499999999</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.1803345695507021</v>
+      </c>
+      <c r="T52">
+        <v>1.919159872022451</v>
+      </c>
+      <c r="U52">
+        <v>0.1125</v>
+      </c>
+      <c r="V52">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W52">
+        <v>0.09112500000000001</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>1.529783159964808</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.1746214467196824</v>
+      </c>
+      <c r="C53">
+        <v>6.048804627213578</v>
+      </c>
+      <c r="D53">
+        <v>49.25960462721358</v>
+      </c>
+      <c r="E53">
+        <v>34.81880000000001</v>
+      </c>
+      <c r="F53">
+        <v>43.79880000000001</v>
+      </c>
+      <c r="G53">
+        <v>0.588</v>
+      </c>
+      <c r="H53">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>9.76</v>
+      </c>
+      <c r="K53">
+        <v>2.37</v>
+      </c>
+      <c r="L53">
+        <v>7.39</v>
+      </c>
+      <c r="M53">
+        <v>8.610844080000001</v>
+      </c>
+      <c r="N53">
+        <v>-1.220844080000002</v>
+      </c>
+      <c r="O53">
+        <v>-0.2319603752000003</v>
+      </c>
+      <c r="P53">
+        <v>-0.9888837048000015</v>
+      </c>
+      <c r="Q53">
+        <v>1.381116295199999</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.1851122535547066</v>
+      </c>
+      <c r="T53">
+        <v>1.983943616734406</v>
+      </c>
+      <c r="U53">
+        <v>0.1966</v>
+      </c>
+      <c r="V53">
+        <v>0.16306183075144</v>
+      </c>
+      <c r="W53">
+        <v>0.1645420440742669</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>0.8582201618496845</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.1761994467196824</v>
+      </c>
+      <c r="C54">
+        <v>4.624269771961011</v>
+      </c>
+      <c r="D54">
+        <v>48.69386977196102</v>
+      </c>
+      <c r="E54">
+        <v>35.67760000000001</v>
+      </c>
+      <c r="F54">
+        <v>44.65760000000001</v>
+      </c>
+      <c r="G54">
+        <v>0.588</v>
+      </c>
+      <c r="H54">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>9.76</v>
+      </c>
+      <c r="K54">
+        <v>2.37</v>
+      </c>
+      <c r="L54">
+        <v>7.39</v>
+      </c>
+      <c r="M54">
+        <v>8.779684160000002</v>
+      </c>
+      <c r="N54">
+        <v>-1.389684160000002</v>
+      </c>
+      <c r="O54">
+        <v>-0.2640399904000004</v>
+      </c>
+      <c r="P54">
+        <v>-1.125644169600002</v>
+      </c>
+      <c r="Q54">
+        <v>1.244355830399998</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.188160425503763</v>
+      </c>
+      <c r="T54">
+        <v>2.025275775416373</v>
+      </c>
+      <c r="U54">
+        <v>0.1966</v>
+      </c>
+      <c r="V54">
+        <v>0.1599260263139123</v>
+      </c>
+      <c r="W54">
+        <v>0.1651585432266848</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>0.8417159279679598</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.1777774467196823</v>
+      </c>
+      <c r="C55">
+        <v>3.212582031440512</v>
+      </c>
+      <c r="D55">
+        <v>48.14098203144052</v>
+      </c>
+      <c r="E55">
+        <v>36.5364</v>
+      </c>
+      <c r="F55">
+        <v>45.5164</v>
+      </c>
+      <c r="G55">
+        <v>0.588</v>
+      </c>
+      <c r="H55">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>9.76</v>
+      </c>
+      <c r="K55">
+        <v>2.37</v>
+      </c>
+      <c r="L55">
+        <v>7.39</v>
+      </c>
+      <c r="M55">
+        <v>8.948524240000001</v>
+      </c>
+      <c r="N55">
+        <v>-1.558524240000001</v>
+      </c>
+      <c r="O55">
+        <v>-0.2961196056000002</v>
+      </c>
+      <c r="P55">
+        <v>-1.262404634400001</v>
+      </c>
+      <c r="Q55">
+        <v>1.107595365599999</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.1913383068974601</v>
+      </c>
+      <c r="T55">
+        <v>2.068366749361402</v>
+      </c>
+      <c r="U55">
+        <v>0.1966</v>
+      </c>
+      <c r="V55">
+        <v>0.1569085541193102</v>
+      </c>
+      <c r="W55">
+        <v>0.1657517782601436</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>0.8258344953647909</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.1793554467196823</v>
+      </c>
+      <c r="C56">
+        <v>1.81330870636819</v>
+      </c>
+      <c r="D56">
+        <v>47.6005087063682</v>
+      </c>
+      <c r="E56">
+        <v>37.3952</v>
+      </c>
+      <c r="F56">
+        <v>46.37520000000001</v>
+      </c>
+      <c r="G56">
+        <v>0.588</v>
+      </c>
+      <c r="H56">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>9.76</v>
+      </c>
+      <c r="K56">
+        <v>2.37</v>
+      </c>
+      <c r="L56">
+        <v>7.39</v>
+      </c>
+      <c r="M56">
+        <v>9.117364320000002</v>
+      </c>
+      <c r="N56">
+        <v>-1.727364320000002</v>
+      </c>
+      <c r="O56">
+        <v>-0.3281992208000003</v>
+      </c>
+      <c r="P56">
+        <v>-1.399165099200002</v>
+      </c>
+      <c r="Q56">
+        <v>0.9708349007999981</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.1946543570474049</v>
+      </c>
+      <c r="T56">
+        <v>2.113331243912736</v>
+      </c>
+      <c r="U56">
+        <v>0.1966</v>
+      </c>
+      <c r="V56">
+        <v>0.1540028401541378</v>
+      </c>
+      <c r="W56">
+        <v>0.1663230416256965</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>0.8105412639691465</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.1909165978761206</v>
+      </c>
+      <c r="C57">
+        <v>-2.66322061417474</v>
+      </c>
+      <c r="D57">
+        <v>43.98277938582527</v>
+      </c>
+      <c r="E57">
+        <v>38.254</v>
+      </c>
+      <c r="F57">
+        <v>47.23400000000001</v>
+      </c>
+      <c r="G57">
+        <v>0.588</v>
+      </c>
+      <c r="H57">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>9.76</v>
+      </c>
+      <c r="K57">
+        <v>2.37</v>
+      </c>
+      <c r="L57">
+        <v>7.39</v>
+      </c>
+      <c r="M57">
+        <v>10.0986292</v>
+      </c>
+      <c r="N57">
+        <v>-2.708629200000002</v>
+      </c>
+      <c r="O57">
+        <v>-0.5146395480000001</v>
+      </c>
+      <c r="P57">
+        <v>-2.193989652000002</v>
+      </c>
+      <c r="Q57">
+        <v>0.1760103479999984</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.1992803453294323</v>
+      </c>
+      <c r="T57">
+        <v>2.17605804703579</v>
+      </c>
+      <c r="U57">
+        <v>0.2138</v>
+      </c>
+      <c r="V57">
+        <v>0.1390386726943098</v>
+      </c>
+      <c r="W57">
+        <v>0.1840735317779565</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>0.7317824878647885</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.1926665978761206</v>
+      </c>
+      <c r="C58">
+        <v>-4.022258255011934</v>
+      </c>
+      <c r="D58">
+        <v>43.48254174498808</v>
+      </c>
+      <c r="E58">
+        <v>39.11280000000001</v>
+      </c>
+      <c r="F58">
+        <v>48.09280000000001</v>
+      </c>
+      <c r="G58">
+        <v>0.588</v>
+      </c>
+      <c r="H58">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>9.76</v>
+      </c>
+      <c r="K58">
+        <v>2.37</v>
+      </c>
+      <c r="L58">
+        <v>7.39</v>
+      </c>
+      <c r="M58">
+        <v>10.28224064</v>
+      </c>
+      <c r="N58">
+        <v>-2.892240640000002</v>
+      </c>
+      <c r="O58">
+        <v>-0.5495257216000001</v>
+      </c>
+      <c r="P58">
+        <v>-2.342714918400001</v>
+      </c>
+      <c r="Q58">
+        <v>0.02728508159999876</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.2029276259051012</v>
+      </c>
+      <c r="T58">
+        <v>2.225513911741149</v>
+      </c>
+      <c r="U58">
+        <v>0.2138</v>
+      </c>
+      <c r="V58">
+        <v>0.1365558392533399</v>
+      </c>
+      <c r="W58">
+        <v>0.1846043615676359</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>0.7187149434386315</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.1944165978761206</v>
+      </c>
+      <c r="C59">
+        <v>-5.370044963963799</v>
+      </c>
+      <c r="D59">
+        <v>42.99355503603621</v>
+      </c>
+      <c r="E59">
+        <v>39.97160000000001</v>
+      </c>
+      <c r="F59">
+        <v>48.95160000000001</v>
+      </c>
+      <c r="G59">
+        <v>0.588</v>
+      </c>
+      <c r="H59">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>9.76</v>
+      </c>
+      <c r="K59">
+        <v>2.37</v>
+      </c>
+      <c r="L59">
+        <v>7.39</v>
+      </c>
+      <c r="M59">
+        <v>10.46585208</v>
+      </c>
+      <c r="N59">
+        <v>-3.075852080000003</v>
+      </c>
+      <c r="O59">
+        <v>-0.5844118952000005</v>
+      </c>
+      <c r="P59">
+        <v>-2.491440184800003</v>
+      </c>
+      <c r="Q59">
+        <v>-0.1214401848000026</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.2067445474377779</v>
+      </c>
+      <c r="T59">
+        <v>2.277270049223501</v>
+      </c>
+      <c r="U59">
+        <v>0.2138</v>
+      </c>
+      <c r="V59">
+        <v>0.1341601227752112</v>
+      </c>
+      <c r="W59">
+        <v>0.1851165657506599</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>0.7061059093432169</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.1961665978761206</v>
+      </c>
+      <c r="C60">
+        <v>-6.706956090012845</v>
+      </c>
+      <c r="D60">
+        <v>42.51544390998716</v>
+      </c>
+      <c r="E60">
+        <v>40.8304</v>
+      </c>
+      <c r="F60">
+        <v>49.8104</v>
+      </c>
+      <c r="G60">
+        <v>0.588</v>
+      </c>
+      <c r="H60">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>9.76</v>
+      </c>
+      <c r="K60">
+        <v>2.37</v>
+      </c>
+      <c r="L60">
+        <v>7.39</v>
+      </c>
+      <c r="M60">
+        <v>10.64946352</v>
+      </c>
+      <c r="N60">
+        <v>-3.25946352</v>
+      </c>
+      <c r="O60">
+        <v>-0.6192980687999998</v>
+      </c>
+      <c r="P60">
+        <v>-2.6401654512</v>
+      </c>
+      <c r="Q60">
+        <v>-0.2701654511999996</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.2107432271386774</v>
+      </c>
+      <c r="T60">
+        <v>2.331490764681203</v>
+      </c>
+      <c r="U60">
+        <v>0.2138</v>
+      </c>
+      <c r="V60">
+        <v>0.1318470172101214</v>
+      </c>
+      <c r="W60">
+        <v>0.185611107720476</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>0.6939316695269547</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.1979165978761206</v>
+      </c>
+      <c r="C61">
+        <v>-8.03335046945277</v>
+      </c>
+      <c r="D61">
+        <v>42.04784953054723</v>
+      </c>
+      <c r="E61">
+        <v>41.6892</v>
+      </c>
+      <c r="F61">
+        <v>50.6692</v>
+      </c>
+      <c r="G61">
+        <v>0.588</v>
+      </c>
+      <c r="H61">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>9.76</v>
+      </c>
+      <c r="K61">
+        <v>2.37</v>
+      </c>
+      <c r="L61">
+        <v>7.39</v>
+      </c>
+      <c r="M61">
+        <v>10.83307496</v>
+      </c>
+      <c r="N61">
+        <v>-3.443074960000001</v>
+      </c>
+      <c r="O61">
+        <v>-0.6541842424000001</v>
+      </c>
+      <c r="P61">
+        <v>-2.788890717600002</v>
+      </c>
+      <c r="Q61">
+        <v>-0.4188907176000014</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.2149369643859622</v>
+      </c>
+      <c r="T61">
+        <v>2.388356393088062</v>
+      </c>
+      <c r="U61">
+        <v>0.2138</v>
+      </c>
+      <c r="V61">
+        <v>0.1296123220031701</v>
+      </c>
+      <c r="W61">
+        <v>0.1860888855557222</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>0.6821701158061588</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.1996665978761206</v>
+      </c>
+      <c r="C62">
+        <v>-9.349571324061287</v>
+      </c>
+      <c r="D62">
+        <v>41.59042867593872</v>
+      </c>
+      <c r="E62">
+        <v>42.548</v>
+      </c>
+      <c r="F62">
+        <v>51.52800000000001</v>
+      </c>
+      <c r="G62">
+        <v>0.588</v>
+      </c>
+      <c r="H62">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>9.76</v>
+      </c>
+      <c r="K62">
+        <v>2.37</v>
+      </c>
+      <c r="L62">
+        <v>7.39</v>
+      </c>
+      <c r="M62">
+        <v>11.0166864</v>
+      </c>
+      <c r="N62">
+        <v>-3.626686400000001</v>
+      </c>
+      <c r="O62">
+        <v>-0.6890704160000001</v>
+      </c>
+      <c r="P62">
+        <v>-2.937615984000002</v>
+      </c>
+      <c r="Q62">
+        <v>-0.5676159840000015</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.2193403884956112</v>
+      </c>
+      <c r="T62">
+        <v>2.448065302915263</v>
+      </c>
+      <c r="U62">
+        <v>0.2138</v>
+      </c>
+      <c r="V62">
+        <v>0.1274521166364506</v>
+      </c>
+      <c r="W62">
+        <v>0.1865507374631268</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>0.6708006138760562</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.2014165978761207</v>
+      </c>
+      <c r="C63">
+        <v>-10.65594710127893</v>
+      </c>
+      <c r="D63">
+        <v>41.14285289872107</v>
+      </c>
+      <c r="E63">
+        <v>43.4068</v>
+      </c>
+      <c r="F63">
+        <v>52.38680000000001</v>
+      </c>
+      <c r="G63">
+        <v>0.588</v>
+      </c>
+      <c r="H63">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>9.76</v>
+      </c>
+      <c r="K63">
+        <v>2.37</v>
+      </c>
+      <c r="L63">
+        <v>7.39</v>
+      </c>
+      <c r="M63">
+        <v>11.20029784</v>
+      </c>
+      <c r="N63">
+        <v>-3.810297840000001</v>
+      </c>
+      <c r="O63">
+        <v>-0.7239565896000001</v>
+      </c>
+      <c r="P63">
+        <v>-3.086341250400001</v>
+      </c>
+      <c r="Q63">
+        <v>-0.7163412504000011</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.223969629226268</v>
+      </c>
+      <c r="T63">
+        <v>2.510836208118219</v>
+      </c>
+      <c r="U63">
+        <v>0.2138</v>
+      </c>
+      <c r="V63">
+        <v>0.1253627376751973</v>
+      </c>
+      <c r="W63">
+        <v>0.1869974466850428</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>0.6598038825010388</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.2031665978761206</v>
+      </c>
+      <c r="C64">
+        <v>-11.95279226071592</v>
+      </c>
+      <c r="D64">
+        <v>40.70480773928409</v>
+      </c>
+      <c r="E64">
+        <v>44.26560000000001</v>
+      </c>
+      <c r="F64">
+        <v>53.2456</v>
+      </c>
+      <c r="G64">
+        <v>0.588</v>
+      </c>
+      <c r="H64">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>9.76</v>
+      </c>
+      <c r="K64">
+        <v>2.37</v>
+      </c>
+      <c r="L64">
+        <v>7.39</v>
+      </c>
+      <c r="M64">
+        <v>11.38390928</v>
+      </c>
+      <c r="N64">
+        <v>-3.993909280000001</v>
+      </c>
+      <c r="O64">
+        <v>-0.7588427632</v>
+      </c>
+      <c r="P64">
+        <v>-3.235066516800001</v>
+      </c>
+      <c r="Q64">
+        <v>-0.8650665168000011</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.2288425142059066</v>
+      </c>
+      <c r="T64">
+        <v>2.576910845173961</v>
+      </c>
+      <c r="U64">
+        <v>0.2138</v>
+      </c>
+      <c r="V64">
+        <v>0.1233407580352748</v>
+      </c>
+      <c r="W64">
+        <v>0.1874297459320582</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>0.6491618843961834</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.2049165978761206</v>
+      </c>
+      <c r="C65">
+        <v>-13.24040801094497</v>
+      </c>
+      <c r="D65">
+        <v>40.27599198905504</v>
+      </c>
+      <c r="E65">
+        <v>45.12440000000001</v>
+      </c>
+      <c r="F65">
+        <v>54.10440000000001</v>
+      </c>
+      <c r="G65">
+        <v>0.588</v>
+      </c>
+      <c r="H65">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>9.76</v>
+      </c>
+      <c r="K65">
+        <v>2.37</v>
+      </c>
+      <c r="L65">
+        <v>7.39</v>
+      </c>
+      <c r="M65">
+        <v>11.56752072</v>
+      </c>
+      <c r="N65">
+        <v>-4.177520720000001</v>
+      </c>
+      <c r="O65">
+        <v>-0.7937289368</v>
+      </c>
+      <c r="P65">
+        <v>-3.383791783200001</v>
+      </c>
+      <c r="Q65">
+        <v>-1.013791783200001</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.2339787983736338</v>
+      </c>
+      <c r="T65">
+        <v>2.646557084232716</v>
+      </c>
+      <c r="U65">
+        <v>0.2138</v>
+      </c>
+      <c r="V65">
+        <v>0.1213829682251911</v>
+      </c>
+      <c r="W65">
+        <v>0.1878483213934541</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>0.6388577275010059</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.2066665978761206</v>
+      </c>
+      <c r="C66">
+        <v>-14.51908300020794</v>
+      </c>
+      <c r="D66">
+        <v>39.85611699979207</v>
+      </c>
+      <c r="E66">
+        <v>45.98320000000001</v>
+      </c>
+      <c r="F66">
+        <v>54.96320000000001</v>
+      </c>
+      <c r="G66">
+        <v>0.588</v>
+      </c>
+      <c r="H66">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>9.76</v>
+      </c>
+      <c r="K66">
+        <v>2.37</v>
+      </c>
+      <c r="L66">
+        <v>7.39</v>
+      </c>
+      <c r="M66">
+        <v>11.75113216</v>
+      </c>
+      <c r="N66">
+        <v>-4.361132160000001</v>
+      </c>
+      <c r="O66">
+        <v>-0.8286151104</v>
+      </c>
+      <c r="P66">
+        <v>-3.532517049600001</v>
+      </c>
+      <c r="Q66">
+        <v>-1.162517049600001</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.2394004316617903</v>
+      </c>
+      <c r="T66">
+        <v>2.720072558794737</v>
+      </c>
+      <c r="U66">
+        <v>0.2138</v>
+      </c>
+      <c r="V66">
+        <v>0.1194863593466725</v>
+      </c>
+      <c r="W66">
+        <v>0.1882538163716814</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.6288755755088027</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.2084165978761206</v>
+      </c>
+      <c r="C67">
+        <v>-15.78909396436475</v>
+      </c>
+      <c r="D67">
+        <v>39.44490603563526</v>
+      </c>
+      <c r="E67">
+        <v>46.84200000000001</v>
+      </c>
+      <c r="F67">
+        <v>55.82200000000001</v>
+      </c>
+      <c r="G67">
+        <v>0.588</v>
+      </c>
+      <c r="H67">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>9.76</v>
+      </c>
+      <c r="K67">
+        <v>2.37</v>
+      </c>
+      <c r="L67">
+        <v>7.39</v>
+      </c>
+      <c r="M67">
+        <v>11.9347436</v>
+      </c>
+      <c r="N67">
+        <v>-4.544743600000001</v>
+      </c>
+      <c r="O67">
+        <v>-0.863501284</v>
+      </c>
+      <c r="P67">
+        <v>-3.681242316000001</v>
+      </c>
+      <c r="Q67">
+        <v>-1.311242316000001</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.2451318725664129</v>
+      </c>
+      <c r="T67">
+        <v>2.797788917617444</v>
+      </c>
+      <c r="U67">
+        <v>0.2138</v>
+      </c>
+      <c r="V67">
+        <v>0.117648107664416</v>
+      </c>
+      <c r="W67">
+        <v>0.1886468345813478</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.619200566654821</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.2101665978761206</v>
+      </c>
+      <c r="C68">
+        <v>-17.05070633514112</v>
+      </c>
+      <c r="D68">
+        <v>39.04209366485889</v>
+      </c>
+      <c r="E68">
+        <v>47.70080000000002</v>
+      </c>
+      <c r="F68">
+        <v>56.68080000000001</v>
+      </c>
+      <c r="G68">
+        <v>0.588</v>
+      </c>
+      <c r="H68">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>9.76</v>
+      </c>
+      <c r="K68">
+        <v>2.37</v>
+      </c>
+      <c r="L68">
+        <v>7.39</v>
+      </c>
+      <c r="M68">
+        <v>12.11835504</v>
+      </c>
+      <c r="N68">
+        <v>-4.728355040000003</v>
+      </c>
+      <c r="O68">
+        <v>-0.8983874576000003</v>
+      </c>
+      <c r="P68">
+        <v>-3.829967582400003</v>
+      </c>
+      <c r="Q68">
+        <v>-1.459967582400003</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.2512004570536603</v>
+      </c>
+      <c r="T68">
+        <v>2.880076826959133</v>
+      </c>
+      <c r="U68">
+        <v>0.2138</v>
+      </c>
+      <c r="V68">
+        <v>0.1158655605785915</v>
+      </c>
+      <c r="W68">
+        <v>0.1890279431482972</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.6098187398873237</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.2119165978761206</v>
+      </c>
+      <c r="C69">
+        <v>-18.30417481148441</v>
+      </c>
+      <c r="D69">
+        <v>38.6474251885156</v>
+      </c>
+      <c r="E69">
+        <v>48.5596</v>
+      </c>
+      <c r="F69">
+        <v>57.53960000000001</v>
+      </c>
+      <c r="G69">
+        <v>0.588</v>
+      </c>
+      <c r="H69">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>9.76</v>
+      </c>
+      <c r="K69">
+        <v>2.37</v>
+      </c>
+      <c r="L69">
+        <v>7.39</v>
+      </c>
+      <c r="M69">
+        <v>12.30196648</v>
+      </c>
+      <c r="N69">
+        <v>-4.911966480000001</v>
+      </c>
+      <c r="O69">
+        <v>-0.9332736312</v>
+      </c>
+      <c r="P69">
+        <v>-3.978692848800001</v>
+      </c>
+      <c r="Q69">
+        <v>-1.608692848800001</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.2576368345401349</v>
+      </c>
+      <c r="T69">
+        <v>2.967351882321531</v>
+      </c>
+      <c r="U69">
+        <v>0.2138</v>
+      </c>
+      <c r="V69">
+        <v>0.1141362238535379</v>
+      </c>
+      <c r="W69">
+        <v>0.1893976753401136</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.6007169676501996</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.2136665978761206</v>
+      </c>
+      <c r="C70">
+        <v>-19.54974389661189</v>
+      </c>
+      <c r="D70">
+        <v>38.26065610338811</v>
+      </c>
+      <c r="E70">
+        <v>49.41840000000001</v>
+      </c>
+      <c r="F70">
+        <v>58.39840000000001</v>
+      </c>
+      <c r="G70">
+        <v>0.588</v>
+      </c>
+      <c r="H70">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>9.76</v>
+      </c>
+      <c r="K70">
+        <v>2.37</v>
+      </c>
+      <c r="L70">
+        <v>7.39</v>
+      </c>
+      <c r="M70">
+        <v>12.48557792</v>
+      </c>
+      <c r="N70">
+        <v>-5.095577920000001</v>
+      </c>
+      <c r="O70">
+        <v>-0.9681598048</v>
+      </c>
+      <c r="P70">
+        <v>-4.127418115200001</v>
+      </c>
+      <c r="Q70">
+        <v>-1.757418115200001</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.2644754856195141</v>
+      </c>
+      <c r="T70">
+        <v>3.06008162864408</v>
+      </c>
+      <c r="U70">
+        <v>0.2138</v>
+      </c>
+      <c r="V70">
+        <v>0.1124577499733388</v>
+      </c>
+      <c r="W70">
+        <v>0.1897565330557001</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.5918828945965202</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.2154165978761206</v>
+      </c>
+      <c r="C71">
+        <v>-20.78764840313112</v>
+      </c>
+      <c r="D71">
+        <v>37.8815515968689</v>
+      </c>
+      <c r="E71">
+        <v>50.27720000000001</v>
+      </c>
+      <c r="F71">
+        <v>59.25720000000001</v>
+      </c>
+      <c r="G71">
+        <v>0.588</v>
+      </c>
+      <c r="H71">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>9.76</v>
+      </c>
+      <c r="K71">
+        <v>2.37</v>
+      </c>
+      <c r="L71">
+        <v>7.39</v>
+      </c>
+      <c r="M71">
+        <v>12.66918936</v>
+      </c>
+      <c r="N71">
+        <v>-5.279189360000003</v>
+      </c>
+      <c r="O71">
+        <v>-1.0030459784</v>
+      </c>
+      <c r="P71">
+        <v>-4.276143381600003</v>
+      </c>
+      <c r="Q71">
+        <v>-1.906143381600002</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.2717553399943372</v>
+      </c>
+      <c r="T71">
+        <v>3.158793939245502</v>
+      </c>
+      <c r="U71">
+        <v>0.2138</v>
+      </c>
+      <c r="V71">
+        <v>0.1108279275099571</v>
+      </c>
+      <c r="W71">
+        <v>0.1901049890983712</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.5833048816313531</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.2171665978761206</v>
+      </c>
+      <c r="C72">
+        <v>-22.01811392842504</v>
+      </c>
+      <c r="D72">
+        <v>37.50988607157498</v>
+      </c>
+      <c r="E72">
+        <v>51.13600000000001</v>
+      </c>
+      <c r="F72">
+        <v>60.11600000000001</v>
+      </c>
+      <c r="G72">
+        <v>0.588</v>
+      </c>
+      <c r="H72">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>9.76</v>
+      </c>
+      <c r="K72">
+        <v>2.37</v>
+      </c>
+      <c r="L72">
+        <v>7.39</v>
+      </c>
+      <c r="M72">
+        <v>12.8528008</v>
+      </c>
+      <c r="N72">
+        <v>-5.462800800000003</v>
+      </c>
+      <c r="O72">
+        <v>-1.037932152</v>
+      </c>
+      <c r="P72">
+        <v>-4.424868648000002</v>
+      </c>
+      <c r="Q72">
+        <v>-2.054868648000002</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.2795205179941484</v>
+      </c>
+      <c r="T72">
+        <v>3.264087070553685</v>
+      </c>
+      <c r="U72">
+        <v>0.2138</v>
+      </c>
+      <c r="V72">
+        <v>0.109244671402672</v>
+      </c>
+      <c r="W72">
+        <v>0.1904434892541087</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.5749719547509052</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.2189165978761206</v>
+      </c>
+      <c r="C73">
+        <v>-23.24135730232445</v>
+      </c>
+      <c r="D73">
+        <v>37.14544269767556</v>
+      </c>
+      <c r="E73">
+        <v>51.9948</v>
+      </c>
+      <c r="F73">
+        <v>60.9748</v>
+      </c>
+      <c r="G73">
+        <v>0.588</v>
+      </c>
+      <c r="H73">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>9.76</v>
+      </c>
+      <c r="K73">
+        <v>2.37</v>
+      </c>
+      <c r="L73">
+        <v>7.39</v>
+      </c>
+      <c r="M73">
+        <v>13.03641224</v>
+      </c>
+      <c r="N73">
+        <v>-5.646412240000001</v>
+      </c>
+      <c r="O73">
+        <v>-1.0728183256</v>
+      </c>
+      <c r="P73">
+        <v>-4.573593914400001</v>
+      </c>
+      <c r="Q73">
+        <v>-2.203593914400001</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.2878212255111879</v>
+      </c>
+      <c r="T73">
+        <v>3.3766417971245</v>
+      </c>
+      <c r="U73">
+        <v>0.2138</v>
+      </c>
+      <c r="V73">
+        <v>0.1077060140589724</v>
+      </c>
+      <c r="W73">
+        <v>0.1907724541941917</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.5668737582051179</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.2206665978761206</v>
+      </c>
+      <c r="C74">
+        <v>-24.45758700893395</v>
+      </c>
+      <c r="D74">
+        <v>36.78801299106605</v>
+      </c>
+      <c r="E74">
+        <v>52.8536</v>
+      </c>
+      <c r="F74">
+        <v>61.8336</v>
+      </c>
+      <c r="G74">
+        <v>0.588</v>
+      </c>
+      <c r="H74">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>9.76</v>
+      </c>
+      <c r="K74">
+        <v>2.37</v>
+      </c>
+      <c r="L74">
+        <v>7.39</v>
+      </c>
+      <c r="M74">
+        <v>13.22002368</v>
+      </c>
+      <c r="N74">
+        <v>-5.830023680000001</v>
+      </c>
+      <c r="O74">
+        <v>-1.1077044992</v>
+      </c>
+      <c r="P74">
+        <v>-4.722319180800001</v>
+      </c>
+      <c r="Q74">
+        <v>-2.352319180800001</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.2967148407080161</v>
+      </c>
+      <c r="T74">
+        <v>3.497236147021805</v>
+      </c>
+      <c r="U74">
+        <v>0.2138</v>
+      </c>
+      <c r="V74">
+        <v>0.1062100971970422</v>
+      </c>
+      <c r="W74">
+        <v>0.1910922812192724</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.5590005115633802</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.2224165978761206</v>
+      </c>
+      <c r="C75">
+        <v>-25.66700358433636</v>
+      </c>
+      <c r="D75">
+        <v>36.43739641566364</v>
+      </c>
+      <c r="E75">
+        <v>53.7124</v>
+      </c>
+      <c r="F75">
+        <v>62.69240000000001</v>
+      </c>
+      <c r="G75">
+        <v>0.588</v>
+      </c>
+      <c r="H75">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>9.76</v>
+      </c>
+      <c r="K75">
+        <v>2.37</v>
+      </c>
+      <c r="L75">
+        <v>7.39</v>
+      </c>
+      <c r="M75">
+        <v>13.40363512</v>
+      </c>
+      <c r="N75">
+        <v>-6.013635120000001</v>
+      </c>
+      <c r="O75">
+        <v>-1.1425906728</v>
+      </c>
+      <c r="P75">
+        <v>-4.871044447200001</v>
+      </c>
+      <c r="Q75">
+        <v>-2.501044447200001</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.3062672422157204</v>
+      </c>
+      <c r="T75">
+        <v>3.626763411726316</v>
+      </c>
+      <c r="U75">
+        <v>0.2138</v>
+      </c>
+      <c r="V75">
+        <v>0.1047551643587266</v>
+      </c>
+      <c r="W75">
+        <v>0.1914033458601042</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.5513429703090873</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.2241665978761206</v>
+      </c>
+      <c r="C76">
+        <v>-26.86979999176909</v>
+      </c>
+      <c r="D76">
+        <v>36.09340000823092</v>
+      </c>
+      <c r="E76">
+        <v>54.5712</v>
+      </c>
+      <c r="F76">
+        <v>63.55120000000001</v>
+      </c>
+      <c r="G76">
+        <v>0.588</v>
+      </c>
+      <c r="H76">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>9.76</v>
+      </c>
+      <c r="K76">
+        <v>2.37</v>
+      </c>
+      <c r="L76">
+        <v>7.39</v>
+      </c>
+      <c r="M76">
+        <v>13.58724656</v>
+      </c>
+      <c r="N76">
+        <v>-6.197246560000001</v>
+      </c>
+      <c r="O76">
+        <v>-1.1774768464</v>
+      </c>
+      <c r="P76">
+        <v>-5.019769713600001</v>
+      </c>
+      <c r="Q76">
+        <v>-2.6497697136</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.316554443839402</v>
+      </c>
+      <c r="T76">
+        <v>3.766254312177328</v>
+      </c>
+      <c r="U76">
+        <v>0.2138</v>
+      </c>
+      <c r="V76">
+        <v>0.1033395540295546</v>
+      </c>
+      <c r="W76">
+        <v>0.1917060033484812</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.5438923896292347</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.2259165978761206</v>
+      </c>
+      <c r="C77">
+        <v>-28.06616197574777</v>
+      </c>
+      <c r="D77">
+        <v>35.75583802425224</v>
+      </c>
+      <c r="E77">
+        <v>55.43000000000001</v>
+      </c>
+      <c r="F77">
+        <v>64.41000000000001</v>
+      </c>
+      <c r="G77">
+        <v>0.588</v>
+      </c>
+      <c r="H77">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>9.76</v>
+      </c>
+      <c r="K77">
+        <v>2.37</v>
+      </c>
+      <c r="L77">
+        <v>7.39</v>
+      </c>
+      <c r="M77">
+        <v>13.770858</v>
+      </c>
+      <c r="N77">
+        <v>-6.380858000000003</v>
+      </c>
+      <c r="O77">
+        <v>-1.21236302</v>
+      </c>
+      <c r="P77">
+        <v>-5.168494980000002</v>
+      </c>
+      <c r="Q77">
+        <v>-2.798494980000002</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.327664621592978</v>
+      </c>
+      <c r="T77">
+        <v>3.916904484664421</v>
+      </c>
+      <c r="U77">
+        <v>0.2138</v>
+      </c>
+      <c r="V77">
+        <v>0.1019616933091605</v>
+      </c>
+      <c r="W77">
+        <v>0.1920005899705015</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.5366404911008449</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.2276665978761206</v>
+      </c>
+      <c r="C78">
+        <v>-29.2562683965024</v>
+      </c>
+      <c r="D78">
+        <v>35.42453160349761</v>
+      </c>
+      <c r="E78">
+        <v>56.28880000000001</v>
+      </c>
+      <c r="F78">
+        <v>65.26880000000001</v>
+      </c>
+      <c r="G78">
+        <v>0.588</v>
+      </c>
+      <c r="H78">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>9.76</v>
+      </c>
+      <c r="K78">
+        <v>2.37</v>
+      </c>
+      <c r="L78">
+        <v>7.39</v>
+      </c>
+      <c r="M78">
+        <v>13.95446944</v>
+      </c>
+      <c r="N78">
+        <v>-6.564469440000003</v>
+      </c>
+      <c r="O78">
+        <v>-1.2472491936</v>
+      </c>
+      <c r="P78">
+        <v>-5.317220246400002</v>
+      </c>
+      <c r="Q78">
+        <v>-2.947220246400002</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.3397006474926855</v>
+      </c>
+      <c r="T78">
+        <v>4.080108838192106</v>
+      </c>
+      <c r="U78">
+        <v>0.2138</v>
+      </c>
+      <c r="V78">
+        <v>0.1006200920814084</v>
+      </c>
+      <c r="W78">
+        <v>0.1922874243129949</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.5295794320074128</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.2294165978761206</v>
+      </c>
+      <c r="C79">
+        <v>-30.44029154599125</v>
+      </c>
+      <c r="D79">
+        <v>35.09930845400876</v>
+      </c>
+      <c r="E79">
+        <v>57.14760000000001</v>
+      </c>
+      <c r="F79">
+        <v>66.12760000000002</v>
+      </c>
+      <c r="G79">
+        <v>0.588</v>
+      </c>
+      <c r="H79">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>9.76</v>
+      </c>
+      <c r="K79">
+        <v>2.37</v>
+      </c>
+      <c r="L79">
+        <v>7.39</v>
+      </c>
+      <c r="M79">
+        <v>14.13808088</v>
+      </c>
+      <c r="N79">
+        <v>-6.748080880000003</v>
+      </c>
+      <c r="O79">
+        <v>-1.2821353672</v>
+      </c>
+      <c r="P79">
+        <v>-5.465945512800002</v>
+      </c>
+      <c r="Q79">
+        <v>-3.095945512800002</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.3527832843401936</v>
+      </c>
+      <c r="T79">
+        <v>4.257504874635242</v>
+      </c>
+      <c r="U79">
+        <v>0.2138</v>
+      </c>
+      <c r="V79">
+        <v>0.0993133376387927</v>
+      </c>
+      <c r="W79">
+        <v>0.1925668084128261</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.5227017770462774</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.2311665978761206</v>
+      </c>
+      <c r="C80">
+        <v>-31.61839744666569</v>
+      </c>
+      <c r="D80">
+        <v>34.78000255333431</v>
+      </c>
+      <c r="E80">
+        <v>58.0064</v>
+      </c>
+      <c r="F80">
+        <v>66.9864</v>
+      </c>
+      <c r="G80">
+        <v>0.588</v>
+      </c>
+      <c r="H80">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>9.76</v>
+      </c>
+      <c r="K80">
+        <v>2.37</v>
+      </c>
+      <c r="L80">
+        <v>7.39</v>
+      </c>
+      <c r="M80">
+        <v>14.32169232</v>
+      </c>
+      <c r="N80">
+        <v>-6.931692320000001</v>
+      </c>
+      <c r="O80">
+        <v>-1.3170215408</v>
+      </c>
+      <c r="P80">
+        <v>-5.614670779200001</v>
+      </c>
+      <c r="Q80">
+        <v>-3.244670779200001</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.3670552518102023</v>
+      </c>
+      <c r="T80">
+        <v>4.451027823482297</v>
+      </c>
+      <c r="U80">
+        <v>0.2138</v>
+      </c>
+      <c r="V80">
+        <v>0.09804008972034664</v>
+      </c>
+      <c r="W80">
+        <v>0.1928390288177899</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.5160004722123509</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.2329165978761206</v>
+      </c>
+      <c r="C81">
+        <v>-32.79074613407457</v>
+      </c>
+      <c r="D81">
+        <v>34.46645386592543</v>
+      </c>
+      <c r="E81">
+        <v>58.8652</v>
+      </c>
+      <c r="F81">
+        <v>67.84520000000001</v>
+      </c>
+      <c r="G81">
+        <v>0.588</v>
+      </c>
+      <c r="H81">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>9.76</v>
+      </c>
+      <c r="K81">
+        <v>2.37</v>
+      </c>
+      <c r="L81">
+        <v>7.39</v>
+      </c>
+      <c r="M81">
+        <v>14.50530376</v>
+      </c>
+      <c r="N81">
+        <v>-7.115303760000001</v>
+      </c>
+      <c r="O81">
+        <v>-1.3519077144</v>
+      </c>
+      <c r="P81">
+        <v>-5.7633960456</v>
+      </c>
+      <c r="Q81">
+        <v>-3.3933960456</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.3826864542773548</v>
+      </c>
+      <c r="T81">
+        <v>4.662981529362407</v>
+      </c>
+      <c r="U81">
+        <v>0.2138</v>
+      </c>
+      <c r="V81">
+        <v>0.0967990759264182</v>
+      </c>
+      <c r="W81">
+        <v>0.1931043575669318</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.5094688206653591</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.2346665978761206</v>
+      </c>
+      <c r="C82">
+        <v>-33.95749192431859</v>
+      </c>
+      <c r="D82">
+        <v>34.15850807568142</v>
+      </c>
+      <c r="E82">
+        <v>59.724</v>
+      </c>
+      <c r="F82">
+        <v>68.70400000000001</v>
+      </c>
+      <c r="G82">
+        <v>0.588</v>
+      </c>
+      <c r="H82">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>9.76</v>
+      </c>
+      <c r="K82">
+        <v>2.37</v>
+      </c>
+      <c r="L82">
+        <v>7.39</v>
+      </c>
+      <c r="M82">
+        <v>14.6889152</v>
+      </c>
+      <c r="N82">
+        <v>-7.298915200000001</v>
+      </c>
+      <c r="O82">
+        <v>-1.386793888</v>
+      </c>
+      <c r="P82">
+        <v>-5.912121312000001</v>
+      </c>
+      <c r="Q82">
+        <v>-3.542121312000001</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.3998807769912226</v>
+      </c>
+      <c r="T82">
+        <v>4.896130605830527</v>
+      </c>
+      <c r="U82">
+        <v>0.2138</v>
+      </c>
+      <c r="V82">
+        <v>0.09558908747733798</v>
+      </c>
+      <c r="W82">
+        <v>0.1933630530973451</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.5031004604070421</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.2572926174930751</v>
+      </c>
+      <c r="C83">
+        <v>-38.35357882523991</v>
+      </c>
+      <c r="D83">
+        <v>30.6212211747601</v>
+      </c>
+      <c r="E83">
+        <v>60.58280000000001</v>
+      </c>
+      <c r="F83">
+        <v>69.56280000000001</v>
+      </c>
+      <c r="G83">
+        <v>0.588</v>
+      </c>
+      <c r="H83">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>9.76</v>
+      </c>
+      <c r="K83">
+        <v>2.37</v>
+      </c>
+      <c r="L83">
+        <v>7.39</v>
+      </c>
+      <c r="M83">
+        <v>16.61159664</v>
+      </c>
+      <c r="N83">
+        <v>-9.221596640000001</v>
+      </c>
+      <c r="O83">
+        <v>-1.7521033616</v>
+      </c>
+      <c r="P83">
+        <v>-7.469493278400002</v>
+      </c>
+      <c r="Q83">
+        <v>-5.099493278400002</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.4221798685010472</v>
+      </c>
+      <c r="T83">
+        <v>5.19849858380273</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>0.0845252885938121</v>
+      </c>
+      <c r="W83">
+        <v>0.2186153610837977</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.4448699399674323</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.2592926174930751</v>
+      </c>
+      <c r="C84">
+        <v>-39.4901316273329</v>
+      </c>
+      <c r="D84">
+        <v>30.34346837266711</v>
+      </c>
+      <c r="E84">
+        <v>61.44160000000001</v>
+      </c>
+      <c r="F84">
+        <v>70.42160000000001</v>
+      </c>
+      <c r="G84">
+        <v>0.588</v>
+      </c>
+      <c r="H84">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>9.76</v>
+      </c>
+      <c r="K84">
+        <v>2.37</v>
+      </c>
+      <c r="L84">
+        <v>7.39</v>
+      </c>
+      <c r="M84">
+        <v>16.81667808</v>
+      </c>
+      <c r="N84">
+        <v>-9.426678080000002</v>
+      </c>
+      <c r="O84">
+        <v>-1.7910688352</v>
+      </c>
+      <c r="P84">
+        <v>-7.635609244800002</v>
+      </c>
+      <c r="Q84">
+        <v>-5.265609244800002</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.4434787500844387</v>
+      </c>
+      <c r="T84">
+        <v>5.48730406068066</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>0.08349449239144854</v>
+      </c>
+      <c r="W84">
+        <v>0.2188615152169221</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.4394446967970977</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.2612926174930751</v>
+      </c>
+      <c r="C85">
+        <v>-40.62169095494171</v>
+      </c>
+      <c r="D85">
+        <v>30.0707090450583</v>
+      </c>
+      <c r="E85">
+        <v>62.30040000000001</v>
+      </c>
+      <c r="F85">
+        <v>71.28040000000001</v>
+      </c>
+      <c r="G85">
+        <v>0.588</v>
+      </c>
+      <c r="H85">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>9.76</v>
+      </c>
+      <c r="K85">
+        <v>2.37</v>
+      </c>
+      <c r="L85">
+        <v>7.39</v>
+      </c>
+      <c r="M85">
+        <v>17.02175952</v>
+      </c>
+      <c r="N85">
+        <v>-9.631759520000003</v>
+      </c>
+      <c r="O85">
+        <v>-1.8300343088</v>
+      </c>
+      <c r="P85">
+        <v>-7.801725211200003</v>
+      </c>
+      <c r="Q85">
+        <v>-5.431725211200003</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.467283382442347</v>
+      </c>
+      <c r="T85">
+        <v>5.810086652485406</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>0.08248853465179252</v>
+      </c>
+      <c r="W85">
+        <v>0.2191017379251519</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.4341501823778555</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.2632926174930751</v>
+      </c>
+      <c r="C86">
+        <v>-41.74839026834327</v>
+      </c>
+      <c r="D86">
+        <v>29.80280973165673</v>
+      </c>
+      <c r="E86">
+        <v>63.1592</v>
+      </c>
+      <c r="F86">
+        <v>72.1392</v>
+      </c>
+      <c r="G86">
+        <v>0.588</v>
+      </c>
+      <c r="H86">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>9.76</v>
+      </c>
+      <c r="K86">
+        <v>2.37</v>
+      </c>
+      <c r="L86">
+        <v>7.39</v>
+      </c>
+      <c r="M86">
+        <v>17.22684096</v>
+      </c>
+      <c r="N86">
+        <v>-9.83684096</v>
+      </c>
+      <c r="O86">
+        <v>-1.8689997824</v>
+      </c>
+      <c r="P86">
+        <v>-7.9678411776</v>
+      </c>
+      <c r="Q86">
+        <v>-5.5978411776</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.4940635938449934</v>
+      </c>
+      <c r="T86">
+        <v>6.17321706826574</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>0.08150652828689024</v>
+      </c>
+      <c r="W86">
+        <v>0.2193362410450906</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.4289817278257383</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.2652926174930751</v>
+      </c>
+      <c r="C87">
+        <v>-42.87035831383216</v>
+      </c>
+      <c r="D87">
+        <v>29.53964168616785</v>
+      </c>
+      <c r="E87">
+        <v>64.018</v>
+      </c>
+      <c r="F87">
+        <v>72.998</v>
+      </c>
+      <c r="G87">
+        <v>0.588</v>
+      </c>
+      <c r="H87">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>9.76</v>
+      </c>
+      <c r="K87">
+        <v>2.37</v>
+      </c>
+      <c r="L87">
+        <v>7.39</v>
+      </c>
+      <c r="M87">
+        <v>17.4319224</v>
+      </c>
+      <c r="N87">
+        <v>-10.0419224</v>
+      </c>
+      <c r="O87">
+        <v>-1.907965256</v>
+      </c>
+      <c r="P87">
+        <v>-8.133957144000002</v>
+      </c>
+      <c r="Q87">
+        <v>-5.763957144000002</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.5244145001013263</v>
+      </c>
+      <c r="T87">
+        <v>6.58476487281679</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>0.08054762795410329</v>
+      </c>
+      <c r="W87">
+        <v>0.2195652264445601</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.4239348839689649</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.2672926174930751</v>
+      </c>
+      <c r="C88">
+        <v>-43.98771933002834</v>
+      </c>
+      <c r="D88">
+        <v>29.28108066997167</v>
+      </c>
+      <c r="E88">
+        <v>64.8768</v>
+      </c>
+      <c r="F88">
+        <v>73.85680000000001</v>
+      </c>
+      <c r="G88">
+        <v>0.588</v>
+      </c>
+      <c r="H88">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>9.76</v>
+      </c>
+      <c r="K88">
+        <v>2.37</v>
+      </c>
+      <c r="L88">
+        <v>7.39</v>
+      </c>
+      <c r="M88">
+        <v>17.63700384</v>
+      </c>
+      <c r="N88">
+        <v>-10.24700384</v>
+      </c>
+      <c r="O88">
+        <v>-1.9469307296</v>
+      </c>
+      <c r="P88">
+        <v>-8.300073110400001</v>
+      </c>
+      <c r="Q88">
+        <v>-5.930073110400001</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.5591012501085639</v>
+      </c>
+      <c r="T88">
+        <v>7.055105220875133</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>0.07961102762905559</v>
+      </c>
+      <c r="W88">
+        <v>0.2197888866021815</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.4190054085739769</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.2692926174930751</v>
+      </c>
+      <c r="C89">
+        <v>-45.10059324344427</v>
+      </c>
+      <c r="D89">
+        <v>29.02700675655574</v>
+      </c>
+      <c r="E89">
+        <v>65.73560000000001</v>
+      </c>
+      <c r="F89">
+        <v>74.71560000000001</v>
+      </c>
+      <c r="G89">
+        <v>0.588</v>
+      </c>
+      <c r="H89">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>9.76</v>
+      </c>
+      <c r="K89">
+        <v>2.37</v>
+      </c>
+      <c r="L89">
+        <v>7.39</v>
+      </c>
+      <c r="M89">
+        <v>17.84208528</v>
+      </c>
+      <c r="N89">
+        <v>-10.45208528</v>
+      </c>
+      <c r="O89">
+        <v>-1.9858962032</v>
+      </c>
+      <c r="P89">
+        <v>-8.466189076800003</v>
+      </c>
+      <c r="Q89">
+        <v>-6.096189076800003</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.5991244231938382</v>
+      </c>
+      <c r="T89">
+        <v>7.597805622480912</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>0.07869595834596298</v>
+      </c>
+      <c r="W89">
+        <v>0.2200074051469841</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.4141892544524369</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.271292617493075</v>
+      </c>
+      <c r="C90">
+        <v>-46.20909585395765</v>
+      </c>
+      <c r="D90">
+        <v>28.77730414604236</v>
+      </c>
+      <c r="E90">
+        <v>66.59440000000001</v>
+      </c>
+      <c r="F90">
+        <v>75.57440000000001</v>
+      </c>
+      <c r="G90">
+        <v>0.588</v>
+      </c>
+      <c r="H90">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>9.76</v>
+      </c>
+      <c r="K90">
+        <v>2.37</v>
+      </c>
+      <c r="L90">
+        <v>7.39</v>
+      </c>
+      <c r="M90">
+        <v>18.04716672</v>
+      </c>
+      <c r="N90">
+        <v>-10.65716672</v>
+      </c>
+      <c r="O90">
+        <v>-2.0248616768</v>
+      </c>
+      <c r="P90">
+        <v>-8.632305043200002</v>
+      </c>
+      <c r="Q90">
+        <v>-6.262305043200002</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.6458181251266579</v>
+      </c>
+      <c r="T90">
+        <v>8.230956091020989</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>0.07780168609203159</v>
+      </c>
+      <c r="W90">
+        <v>0.2202209573612229</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.4094825583791137</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.2732926174930751</v>
+      </c>
+      <c r="C91">
+        <v>-47.31333901079302</v>
+      </c>
+      <c r="D91">
+        <v>28.531860989207</v>
+      </c>
+      <c r="E91">
+        <v>67.45320000000001</v>
+      </c>
+      <c r="F91">
+        <v>76.43320000000001</v>
+      </c>
+      <c r="G91">
+        <v>0.588</v>
+      </c>
+      <c r="H91">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>9.76</v>
+      </c>
+      <c r="K91">
+        <v>2.37</v>
+      </c>
+      <c r="L91">
+        <v>7.39</v>
+      </c>
+      <c r="M91">
+        <v>18.25224816</v>
+      </c>
+      <c r="N91">
+        <v>-10.86224816</v>
+      </c>
+      <c r="O91">
+        <v>-2.0638271504</v>
+      </c>
+      <c r="P91">
+        <v>-8.798421009600004</v>
+      </c>
+      <c r="Q91">
+        <v>-6.428421009600004</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.7010015910472633</v>
+      </c>
+      <c r="T91">
+        <v>8.979224826568354</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>0.07692750984380652</v>
+      </c>
+      <c r="W91">
+        <v>0.220429710649299</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.4048816307568766</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.2752926174930751</v>
+      </c>
+      <c r="C92">
+        <v>-48.41343077957342</v>
+      </c>
+      <c r="D92">
+        <v>28.29056922042659</v>
+      </c>
+      <c r="E92">
+        <v>68.31200000000001</v>
+      </c>
+      <c r="F92">
+        <v>77.29200000000002</v>
+      </c>
+      <c r="G92">
+        <v>0.588</v>
+      </c>
+      <c r="H92">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>9.76</v>
+      </c>
+      <c r="K92">
+        <v>2.37</v>
+      </c>
+      <c r="L92">
+        <v>7.39</v>
+      </c>
+      <c r="M92">
+        <v>18.4573296</v>
+      </c>
+      <c r="N92">
+        <v>-11.0673296</v>
+      </c>
+      <c r="O92">
+        <v>-2.102792624</v>
+      </c>
+      <c r="P92">
+        <v>-8.964536976000005</v>
+      </c>
+      <c r="Q92">
+        <v>-6.594536976000005</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.7672217501519896</v>
+      </c>
+      <c r="T92">
+        <v>9.877147309225187</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>0.07607275973443088</v>
+      </c>
+      <c r="W92">
+        <v>0.2206338249754179</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.400382945970689</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.2772926174930751</v>
+      </c>
+      <c r="C93">
+        <v>-49.50947560096709</v>
+      </c>
+      <c r="D93">
+        <v>28.05332439903292</v>
+      </c>
+      <c r="E93">
+        <v>69.17080000000001</v>
+      </c>
+      <c r="F93">
+        <v>78.15080000000002</v>
+      </c>
+      <c r="G93">
+        <v>0.588</v>
+      </c>
+      <c r="H93">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>9.76</v>
+      </c>
+      <c r="K93">
+        <v>2.37</v>
+      </c>
+      <c r="L93">
+        <v>7.39</v>
+      </c>
+      <c r="M93">
+        <v>18.66241104000001</v>
+      </c>
+      <c r="N93">
+        <v>-11.27241104000001</v>
+      </c>
+      <c r="O93">
+        <v>-2.1417580976</v>
+      </c>
+      <c r="P93">
+        <v>-9.130652942400005</v>
+      </c>
+      <c r="Q93">
+        <v>-6.760652942400005</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.8481575001688775</v>
+      </c>
+      <c r="T93">
+        <v>10.97460812136132</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>0.07523679534174482</v>
+      </c>
+      <c r="W93">
+        <v>0.2208334532723914</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.3959831333776045</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.2792926174930751</v>
+      </c>
+      <c r="C94">
+        <v>-50.6015744414177</v>
+      </c>
+      <c r="D94">
+        <v>27.82002555858231</v>
+      </c>
+      <c r="E94">
+        <v>70.0296</v>
+      </c>
+      <c r="F94">
+        <v>79.00960000000001</v>
+      </c>
+      <c r="G94">
+        <v>0.588</v>
+      </c>
+      <c r="H94">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>9.76</v>
+      </c>
+      <c r="K94">
+        <v>2.37</v>
+      </c>
+      <c r="L94">
+        <v>7.39</v>
+      </c>
+      <c r="M94">
+        <v>18.86749248</v>
+      </c>
+      <c r="N94">
+        <v>-11.47749248</v>
+      </c>
+      <c r="O94">
+        <v>-2.1807235712</v>
+      </c>
+      <c r="P94">
+        <v>-9.296768908800003</v>
+      </c>
+      <c r="Q94">
+        <v>-6.926768908800002</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.9493271876899874</v>
+      </c>
+      <c r="T94">
+        <v>12.34643413653149</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>0.07441900408803022</v>
+      </c>
+      <c r="W94">
+        <v>0.2210287418237784</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.3916789688843697</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.281292617493075</v>
+      </c>
+      <c r="C95">
+        <v>-51.68982493641576</v>
+      </c>
+      <c r="D95">
+        <v>27.59057506358425</v>
+      </c>
+      <c r="E95">
+        <v>70.8884</v>
+      </c>
+      <c r="F95">
+        <v>79.86840000000001</v>
+      </c>
+      <c r="G95">
+        <v>0.588</v>
+      </c>
+      <c r="H95">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>9.76</v>
+      </c>
+      <c r="K95">
+        <v>2.37</v>
+      </c>
+      <c r="L95">
+        <v>7.39</v>
+      </c>
+      <c r="M95">
+        <v>19.07257392</v>
+      </c>
+      <c r="N95">
+        <v>-11.68257392</v>
+      </c>
+      <c r="O95">
+        <v>-2.2196890448</v>
+      </c>
+      <c r="P95">
+        <v>-9.462884875200004</v>
+      </c>
+      <c r="Q95">
+        <v>-7.092884875200004</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>1.079402500217129</v>
+      </c>
+      <c r="T95">
+        <v>14.11021044175027</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>0.07361879974299763</v>
+      </c>
+      <c r="W95">
+        <v>0.2212198306213722</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.3874673670684088</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.2832926174930751</v>
+      </c>
+      <c r="C96">
+        <v>-52.7743215267381</v>
+      </c>
+      <c r="D96">
+        <v>27.36487847326191</v>
+      </c>
+      <c r="E96">
+        <v>71.74720000000001</v>
+      </c>
+      <c r="F96">
+        <v>80.72720000000001</v>
+      </c>
+      <c r="G96">
+        <v>0.588</v>
+      </c>
+      <c r="H96">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>9.76</v>
+      </c>
+      <c r="K96">
+        <v>2.37</v>
+      </c>
+      <c r="L96">
+        <v>7.39</v>
+      </c>
+      <c r="M96">
+        <v>19.27765536</v>
+      </c>
+      <c r="N96">
+        <v>-11.88765536</v>
+      </c>
+      <c r="O96">
+        <v>-2.2586545184</v>
+      </c>
+      <c r="P96">
+        <v>-9.629000841600003</v>
+      </c>
+      <c r="Q96">
+        <v>-7.259000841600003</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>1.252836250253317</v>
+      </c>
+      <c r="T96">
+        <v>16.46191218204199</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>0.07283562102232743</v>
+      </c>
+      <c r="W96">
+        <v>0.2214068536998682</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.3833453738017235</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.2852926174930751</v>
+      </c>
+      <c r="C97">
+        <v>-53.85515558805461</v>
+      </c>
+      <c r="D97">
+        <v>27.1428444119454</v>
+      </c>
+      <c r="E97">
+        <v>72.60600000000001</v>
+      </c>
+      <c r="F97">
+        <v>81.58600000000001</v>
+      </c>
+      <c r="G97">
+        <v>0.588</v>
+      </c>
+      <c r="H97">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>9.76</v>
+      </c>
+      <c r="K97">
+        <v>2.37</v>
+      </c>
+      <c r="L97">
+        <v>7.39</v>
+      </c>
+      <c r="M97">
+        <v>19.4827368</v>
+      </c>
+      <c r="N97">
+        <v>-12.0927368</v>
+      </c>
+      <c r="O97">
+        <v>-2.297619992</v>
+      </c>
+      <c r="P97">
+        <v>-9.795116808000005</v>
+      </c>
+      <c r="Q97">
+        <v>-7.425116808000005</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>1.495643500303981</v>
+      </c>
+      <c r="T97">
+        <v>19.7542946184504</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>0.072068930274724</v>
+      </c>
+      <c r="W97">
+        <v>0.2215899394503959</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.3793101593406527</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.2872926174930751</v>
+      </c>
+      <c r="C98">
+        <v>-54.93241555427635</v>
+      </c>
+      <c r="D98">
+        <v>26.92438444572366</v>
+      </c>
+      <c r="E98">
+        <v>73.4648</v>
+      </c>
+      <c r="F98">
+        <v>82.4448</v>
+      </c>
+      <c r="G98">
+        <v>0.588</v>
+      </c>
+      <c r="H98">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>9.76</v>
+      </c>
+      <c r="K98">
+        <v>2.37</v>
+      </c>
+      <c r="L98">
+        <v>7.39</v>
+      </c>
+      <c r="M98">
+        <v>19.68781824</v>
+      </c>
+      <c r="N98">
+        <v>-12.29781824</v>
+      </c>
+      <c r="O98">
+        <v>-2.3365854656</v>
+      </c>
+      <c r="P98">
+        <v>-9.961232774400003</v>
+      </c>
+      <c r="Q98">
+        <v>-7.591232774400003</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>1.859854375379972</v>
+      </c>
+      <c r="T98">
+        <v>24.69286827306294</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>0.07131821225102897</v>
+      </c>
+      <c r="W98">
+        <v>0.2217692109144543</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.375359011847521</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.2892926174930751</v>
+      </c>
+      <c r="C99">
+        <v>-56.00618703499447</v>
+      </c>
+      <c r="D99">
+        <v>26.70941296500553</v>
+      </c>
+      <c r="E99">
+        <v>74.3236</v>
+      </c>
+      <c r="F99">
+        <v>83.3036</v>
+      </c>
+      <c r="G99">
+        <v>0.588</v>
+      </c>
+      <c r="H99">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>9.76</v>
+      </c>
+      <c r="K99">
+        <v>2.37</v>
+      </c>
+      <c r="L99">
+        <v>7.39</v>
+      </c>
+      <c r="M99">
+        <v>19.89289968</v>
+      </c>
+      <c r="N99">
+        <v>-12.50289968</v>
+      </c>
+      <c r="O99">
+        <v>-2.3755509392</v>
+      </c>
+      <c r="P99">
+        <v>-10.1273487408</v>
+      </c>
+      <c r="Q99">
+        <v>-7.757348740800002</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>2.46687250050663</v>
+      </c>
+      <c r="T99">
+        <v>32.92382436408393</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>0.07058297294947197</v>
+      </c>
+      <c r="W99">
+        <v>0.2219447860596661</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.3714893313130104</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.2912926174930751</v>
+      </c>
+      <c r="C100">
+        <v>-57.07655292733776</v>
+      </c>
+      <c r="D100">
+        <v>26.49784707266225</v>
+      </c>
+      <c r="E100">
+        <v>75.1824</v>
+      </c>
+      <c r="F100">
+        <v>84.16240000000001</v>
+      </c>
+      <c r="G100">
+        <v>0.588</v>
+      </c>
+      <c r="H100">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>9.76</v>
+      </c>
+      <c r="K100">
+        <v>2.37</v>
+      </c>
+      <c r="L100">
+        <v>7.39</v>
+      </c>
+      <c r="M100">
+        <v>20.09798112</v>
+      </c>
+      <c r="N100">
+        <v>-12.70798112</v>
+      </c>
+      <c r="O100">
+        <v>-2.4145164128</v>
+      </c>
+      <c r="P100">
+        <v>-10.2934647072</v>
+      </c>
+      <c r="Q100">
+        <v>-7.923464707200004</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>3.680908750759945</v>
+      </c>
+      <c r="T100">
+        <v>49.38573654612589</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0.0698627385316202</v>
+      </c>
+      <c r="W100">
+        <v>0.2221167780386491</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.3676986238506328</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.2932926174930751</v>
+      </c>
+      <c r="C101">
+        <v>-58.14359352255568</v>
+      </c>
+      <c r="D101">
+        <v>26.28960647744433</v>
+      </c>
+      <c r="E101">
+        <v>76.0412</v>
+      </c>
+      <c r="F101">
+        <v>85.02120000000001</v>
+      </c>
+      <c r="G101">
+        <v>0.588</v>
+      </c>
+      <c r="H101">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>9.76</v>
+      </c>
+      <c r="K101">
+        <v>2.37</v>
+      </c>
+      <c r="L101">
+        <v>7.39</v>
+      </c>
+      <c r="M101">
+        <v>20.30306256</v>
+      </c>
+      <c r="N101">
+        <v>-12.91306256</v>
+      </c>
+      <c r="O101">
+        <v>-2.4534818864</v>
+      </c>
+      <c r="P101">
+        <v>-10.4595806736</v>
+      </c>
+      <c r="Q101">
+        <v>-8.089580673600004</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>7.32301750151989</v>
+      </c>
+      <c r="T101">
+        <v>98.77147309225178</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0.06915705430402808</v>
+      </c>
+      <c r="W101">
+        <v>0.2222852954321981</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.36398449633699</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/poland/poland_aerospace_defense.xlsx
+++ b/research/traditional_assets/database/data/poland/poland_aerospace_defense.xlsx
@@ -1397,7 +1397,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1534,22 +1534,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09443312991498173</v>
+        <v>0.09429015696814329</v>
       </c>
       <c r="C2">
-        <v>160.3110997037199</v>
+        <v>158.8187311116363</v>
       </c>
       <c r="D2">
-        <v>135.0110997037199</v>
+        <v>135.1220311116363</v>
       </c>
       <c r="E2">
-        <v>-1.13</v>
+        <v>0.4733000000000001</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1.6033</v>
       </c>
       <c r="G2">
         <v>25.3</v>
@@ -1570,28 +1570,28 @@
         <v>35.9</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.08064598999999999</v>
       </c>
       <c r="N2">
-        <v>35.9</v>
+        <v>35.81935401</v>
       </c>
       <c r="O2">
-        <v>6.821</v>
+        <v>6.8056772619</v>
       </c>
       <c r="P2">
-        <v>29.079</v>
+        <v>29.0136767481</v>
       </c>
       <c r="Q2">
-        <v>32.079</v>
+        <v>32.0136767481</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09443312991498173</v>
+        <v>0.09483103734155887</v>
       </c>
       <c r="T2">
-        <v>0.890732853642657</v>
+        <v>0.8980206678997333</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1608,7 +1608,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>445.1554255828468</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1616,22 +1616,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09429015696814329</v>
+        <v>0.09414718402130481</v>
       </c>
       <c r="C3">
-        <v>158.8187311116363</v>
+        <v>157.3265449622793</v>
       </c>
       <c r="D3">
-        <v>135.1220311116363</v>
+        <v>135.2331449622793</v>
       </c>
       <c r="E3">
-        <v>0.4733000000000001</v>
+        <v>2.0766</v>
       </c>
       <c r="F3">
-        <v>1.6033</v>
+        <v>3.2066</v>
       </c>
       <c r="G3">
         <v>25.3</v>
@@ -1652,28 +1652,28 @@
         <v>35.9</v>
       </c>
       <c r="M3">
-        <v>0.08064598999999999</v>
+        <v>0.16129198</v>
       </c>
       <c r="N3">
-        <v>35.81935401</v>
+        <v>35.73870802</v>
       </c>
       <c r="O3">
-        <v>6.8056772619</v>
+        <v>6.7903545238</v>
       </c>
       <c r="P3">
-        <v>29.0136767481</v>
+        <v>28.9483534962</v>
       </c>
       <c r="Q3">
-        <v>32.0136767481</v>
+        <v>31.9483534962</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09483103734155887</v>
+        <v>0.09523706532786205</v>
       </c>
       <c r="T3">
-        <v>0.8980206678997333</v>
+        <v>0.9054572130600153</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1690,7 +1690,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>445.1554255828468</v>
+        <v>222.5777127914234</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1698,22 +1698,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09414718402130481</v>
+        <v>0.09400421107446634</v>
       </c>
       <c r="C4">
-        <v>157.3265449622793</v>
+        <v>155.8345417060995</v>
       </c>
       <c r="D4">
-        <v>135.2331449622793</v>
+        <v>135.3444417060995</v>
       </c>
       <c r="E4">
-        <v>2.0766</v>
+        <v>3.679899999999999</v>
       </c>
       <c r="F4">
-        <v>3.2066</v>
+        <v>4.809899999999999</v>
       </c>
       <c r="G4">
         <v>25.3</v>
@@ -1734,28 +1734,28 @@
         <v>35.9</v>
       </c>
       <c r="M4">
-        <v>0.16129198</v>
+        <v>0.2419379699999999</v>
       </c>
       <c r="N4">
-        <v>35.73870802</v>
+        <v>35.65806203</v>
       </c>
       <c r="O4">
-        <v>6.7903545238</v>
+        <v>6.7750317857</v>
       </c>
       <c r="P4">
-        <v>28.9483534962</v>
+        <v>28.8830302443</v>
       </c>
       <c r="Q4">
-        <v>31.9483534962</v>
+        <v>31.8830302443</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09523706532786205</v>
+        <v>0.09565146502522304</v>
       </c>
       <c r="T4">
-        <v>0.9054572130600153</v>
+        <v>0.9130470890483442</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1772,7 +1772,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>222.5777127914234</v>
+        <v>148.3851418609489</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1780,22 +1780,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09400421107446634</v>
+        <v>0.09386123812762788</v>
       </c>
       <c r="C5">
-        <v>155.8345417060995</v>
+        <v>154.3427217950316</v>
       </c>
       <c r="D5">
-        <v>135.3444417060995</v>
+        <v>135.4559217950315</v>
       </c>
       <c r="E5">
-        <v>3.679899999999999</v>
+        <v>5.2832</v>
       </c>
       <c r="F5">
-        <v>4.809899999999999</v>
+        <v>6.4132</v>
       </c>
       <c r="G5">
         <v>25.3</v>
@@ -1816,28 +1816,28 @@
         <v>35.9</v>
       </c>
       <c r="M5">
-        <v>0.2419379699999999</v>
+        <v>0.3225839599999999</v>
       </c>
       <c r="N5">
-        <v>35.65806203</v>
+        <v>35.57741604</v>
       </c>
       <c r="O5">
-        <v>6.7750317857</v>
+        <v>6.759709047599999</v>
       </c>
       <c r="P5">
-        <v>28.8830302443</v>
+        <v>28.8177069924</v>
       </c>
       <c r="Q5">
-        <v>31.8830302443</v>
+        <v>31.8177069924</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09565146502522304</v>
+        <v>0.09607449804961238</v>
       </c>
       <c r="T5">
-        <v>0.9130470890483442</v>
+        <v>0.9207950874530966</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1854,7 +1854,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>148.3851418609489</v>
+        <v>111.2888563957117</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1862,22 +1862,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09386123812762788</v>
+        <v>0.09371826518078941</v>
       </c>
       <c r="C6">
-        <v>154.3427217950316</v>
+        <v>152.8510856825002</v>
       </c>
       <c r="D6">
-        <v>135.4559217950315</v>
+        <v>135.5675856825002</v>
       </c>
       <c r="E6">
-        <v>5.2832</v>
+        <v>6.886499999999999</v>
       </c>
       <c r="F6">
-        <v>6.4132</v>
+        <v>8.016499999999999</v>
       </c>
       <c r="G6">
         <v>25.3</v>
@@ -1898,28 +1898,28 @@
         <v>35.9</v>
       </c>
       <c r="M6">
-        <v>0.3225839599999999</v>
+        <v>0.4032299499999999</v>
       </c>
       <c r="N6">
-        <v>35.57741604</v>
+        <v>35.49677005</v>
       </c>
       <c r="O6">
-        <v>6.759709047599999</v>
+        <v>6.7443863095</v>
       </c>
       <c r="P6">
-        <v>28.8177069924</v>
+        <v>28.7523837405</v>
       </c>
       <c r="Q6">
-        <v>31.8177069924</v>
+        <v>31.7523837405</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09607449804961238</v>
+        <v>0.09650643703240991</v>
       </c>
       <c r="T6">
-        <v>0.9207950874530966</v>
+        <v>0.9287062016137386</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1936,7 +1936,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>111.2888563957117</v>
+        <v>89.03108511656936</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1944,22 +1944,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09371826518078941</v>
+        <v>0.09357529223395095</v>
       </c>
       <c r="C7">
-        <v>152.8510856825002</v>
+        <v>151.3596338234268</v>
       </c>
       <c r="D7">
-        <v>135.5675856825002</v>
+        <v>135.6794338234268</v>
       </c>
       <c r="E7">
-        <v>6.886499999999999</v>
+        <v>8.489799999999999</v>
       </c>
       <c r="F7">
-        <v>8.016499999999999</v>
+        <v>9.6198</v>
       </c>
       <c r="G7">
         <v>25.3</v>
@@ -1980,28 +1980,28 @@
         <v>35.9</v>
       </c>
       <c r="M7">
-        <v>0.4032299499999999</v>
+        <v>0.4838759399999999</v>
       </c>
       <c r="N7">
-        <v>35.49677005</v>
+        <v>35.41612406</v>
       </c>
       <c r="O7">
-        <v>6.7443863095</v>
+        <v>6.7290635714</v>
       </c>
       <c r="P7">
-        <v>28.7523837405</v>
+        <v>28.6870604886</v>
       </c>
       <c r="Q7">
-        <v>31.7523837405</v>
+        <v>31.6870604886</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09650643703240991</v>
+        <v>0.0969475662063308</v>
       </c>
       <c r="T7">
-        <v>0.9287062016137386</v>
+        <v>0.9367856373522666</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2018,7 +2018,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>89.03108511656936</v>
+        <v>74.19257093047446</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2026,22 +2026,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09357529223395095</v>
+        <v>0.09343231928711249</v>
       </c>
       <c r="C8">
-        <v>151.3596338234268</v>
+        <v>149.8683666742351</v>
       </c>
       <c r="D8">
-        <v>135.6794338234268</v>
+        <v>135.7914666742351</v>
       </c>
       <c r="E8">
-        <v>8.489799999999999</v>
+        <v>10.0931</v>
       </c>
       <c r="F8">
-        <v>9.619799999999998</v>
+        <v>11.2231</v>
       </c>
       <c r="G8">
         <v>25.3</v>
@@ -2062,28 +2062,28 @@
         <v>35.9</v>
       </c>
       <c r="M8">
-        <v>0.4838759399999999</v>
+        <v>0.5645219299999998</v>
       </c>
       <c r="N8">
-        <v>35.41612406</v>
+        <v>35.33547807</v>
       </c>
       <c r="O8">
-        <v>6.7290635714</v>
+        <v>6.7137408333</v>
       </c>
       <c r="P8">
-        <v>28.6870604886</v>
+        <v>28.6217372367</v>
       </c>
       <c r="Q8">
-        <v>31.6870604886</v>
+        <v>31.6217372367</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.0969475662063308</v>
+        <v>0.09739818202915321</v>
       </c>
       <c r="T8">
-        <v>0.9367856373522666</v>
+        <v>0.9450388243969997</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2100,7 +2100,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>74.19257093047447</v>
+        <v>63.59363222612098</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2108,22 +2108,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09343231928711247</v>
+        <v>0.09328934634027401</v>
       </c>
       <c r="C9">
-        <v>149.8683666742351</v>
+        <v>148.3772846928576</v>
       </c>
       <c r="D9">
-        <v>135.7914666742351</v>
+        <v>135.9036846928576</v>
       </c>
       <c r="E9">
-        <v>10.0931</v>
+        <v>11.6964</v>
       </c>
       <c r="F9">
-        <v>11.2231</v>
+        <v>12.8264</v>
       </c>
       <c r="G9">
         <v>25.3</v>
@@ -2144,28 +2144,28 @@
         <v>35.9</v>
       </c>
       <c r="M9">
-        <v>0.5645219299999999</v>
+        <v>0.6451679199999999</v>
       </c>
       <c r="N9">
-        <v>35.33547807</v>
+        <v>35.25483208</v>
       </c>
       <c r="O9">
-        <v>6.7137408333</v>
+        <v>6.6984180952</v>
       </c>
       <c r="P9">
-        <v>28.6217372367</v>
+        <v>28.5564139848</v>
       </c>
       <c r="Q9">
-        <v>31.6217372367</v>
+        <v>31.5564139848</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09739818202915321</v>
+        <v>0.09785859384812393</v>
       </c>
       <c r="T9">
-        <v>0.9450388243969997</v>
+        <v>0.9534714285514007</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2182,7 +2182,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>63.59363222612097</v>
+        <v>55.64442819785585</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2190,22 +2190,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09328934634027401</v>
+        <v>0.09314637339343555</v>
       </c>
       <c r="C10">
-        <v>148.3772846928576</v>
+        <v>146.8863883387419</v>
       </c>
       <c r="D10">
-        <v>135.9036846928576</v>
+        <v>136.0160883387419</v>
       </c>
       <c r="E10">
-        <v>11.6964</v>
+        <v>13.2997</v>
       </c>
       <c r="F10">
-        <v>12.8264</v>
+        <v>14.4297</v>
       </c>
       <c r="G10">
         <v>25.3</v>
@@ -2226,28 +2226,28 @@
         <v>35.9</v>
       </c>
       <c r="M10">
-        <v>0.6451679199999999</v>
+        <v>0.7258139099999998</v>
       </c>
       <c r="N10">
-        <v>35.25483208</v>
+        <v>35.17418609</v>
       </c>
       <c r="O10">
-        <v>6.6984180952</v>
+        <v>6.6830953571</v>
       </c>
       <c r="P10">
-        <v>28.5564139848</v>
+        <v>28.4910907329</v>
       </c>
       <c r="Q10">
-        <v>31.5564139848</v>
+        <v>31.4910907329</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09785859384812393</v>
+        <v>0.09832912460817093</v>
       </c>
       <c r="T10">
-        <v>0.9534714285514007</v>
+        <v>0.962089364665239</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2264,7 +2264,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>55.64442819785585</v>
+        <v>49.46171395364964</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2272,22 +2272,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09314637339343555</v>
+        <v>0.09300340044659711</v>
       </c>
       <c r="C11">
-        <v>146.8863883387419</v>
+        <v>145.3956780728568</v>
       </c>
       <c r="D11">
-        <v>136.0160883387419</v>
+        <v>136.1286780728568</v>
       </c>
       <c r="E11">
-        <v>13.2997</v>
+        <v>14.903</v>
       </c>
       <c r="F11">
-        <v>14.4297</v>
+        <v>16.033</v>
       </c>
       <c r="G11">
         <v>25.3</v>
@@ -2308,28 +2308,28 @@
         <v>35.9</v>
       </c>
       <c r="M11">
-        <v>0.7258139099999998</v>
+        <v>0.8064598999999999</v>
       </c>
       <c r="N11">
-        <v>35.17418609</v>
+        <v>35.0935401</v>
       </c>
       <c r="O11">
-        <v>6.6830953571</v>
+        <v>6.667772619</v>
       </c>
       <c r="P11">
-        <v>28.4910907329</v>
+        <v>28.425767481</v>
       </c>
       <c r="Q11">
-        <v>31.4910907329</v>
+        <v>31.425767481</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09832912460817093</v>
+        <v>0.09881011160733011</v>
       </c>
       <c r="T11">
-        <v>0.962089364665239</v>
+        <v>0.9708988104704962</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2346,7 +2346,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>49.46171395364964</v>
+        <v>44.51554255828467</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2354,22 +2354,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09300340044659711</v>
+        <v>0.09286042749975862</v>
       </c>
       <c r="C12">
-        <v>145.3956780728568</v>
+        <v>143.9051543576986</v>
       </c>
       <c r="D12">
-        <v>136.1286780728568</v>
+        <v>136.2414543576986</v>
       </c>
       <c r="E12">
-        <v>14.903</v>
+        <v>16.5063</v>
       </c>
       <c r="F12">
-        <v>16.033</v>
+        <v>17.6363</v>
       </c>
       <c r="G12">
         <v>25.3</v>
@@ -2390,28 +2390,28 @@
         <v>35.9</v>
       </c>
       <c r="M12">
-        <v>0.8064598999999999</v>
+        <v>0.8871058899999998</v>
       </c>
       <c r="N12">
-        <v>35.0935401</v>
+        <v>35.01289411</v>
       </c>
       <c r="O12">
-        <v>6.667772619</v>
+        <v>6.6524498809</v>
       </c>
       <c r="P12">
-        <v>28.425767481</v>
+        <v>28.3604442291</v>
       </c>
       <c r="Q12">
-        <v>31.425767481</v>
+        <v>31.3604442291</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09881011160733011</v>
+        <v>0.09930190730309957</v>
       </c>
       <c r="T12">
-        <v>0.9708988104704962</v>
+        <v>0.9799062213500286</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2428,7 +2428,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>44.51554255828467</v>
+        <v>40.46867505298607</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2436,22 +2436,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09286042749975862</v>
+        <v>0.09271745455292016</v>
       </c>
       <c r="C13">
-        <v>143.9051543576986</v>
+        <v>142.4148176572976</v>
       </c>
       <c r="D13">
-        <v>136.2414543576986</v>
+        <v>136.3544176572976</v>
       </c>
       <c r="E13">
-        <v>16.5063</v>
+        <v>18.1096</v>
       </c>
       <c r="F13">
-        <v>17.6363</v>
+        <v>19.2396</v>
       </c>
       <c r="G13">
         <v>25.3</v>
@@ -2472,28 +2472,28 @@
         <v>35.9</v>
       </c>
       <c r="M13">
-        <v>0.8871058899999998</v>
+        <v>0.9677518799999998</v>
       </c>
       <c r="N13">
-        <v>35.01289411</v>
+        <v>34.93224812</v>
       </c>
       <c r="O13">
-        <v>6.6524498809</v>
+        <v>6.6371271428</v>
       </c>
       <c r="P13">
-        <v>28.3604442291</v>
+        <v>28.2951209772</v>
       </c>
       <c r="Q13">
-        <v>31.3604442291</v>
+        <v>31.2951209772</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09930190730309957</v>
+        <v>0.0998048801737729</v>
       </c>
       <c r="T13">
-        <v>0.9799062213500286</v>
+        <v>0.9891183461131867</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2510,7 +2510,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>40.46867505298607</v>
+        <v>37.09628546523723</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2518,22 +2518,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09271745455292016</v>
+        <v>0.09257448160608168</v>
       </c>
       <c r="C14">
-        <v>142.4148176572976</v>
+        <v>140.9246684372243</v>
       </c>
       <c r="D14">
-        <v>136.3544176572976</v>
+        <v>136.4675684372243</v>
       </c>
       <c r="E14">
-        <v>18.1096</v>
+        <v>19.7129</v>
       </c>
       <c r="F14">
-        <v>19.2396</v>
+        <v>20.8429</v>
       </c>
       <c r="G14">
         <v>25.3</v>
@@ -2554,28 +2554,28 @@
         <v>35.9</v>
       </c>
       <c r="M14">
-        <v>0.9677518799999998</v>
+        <v>1.04839787</v>
       </c>
       <c r="N14">
-        <v>34.93224812</v>
+        <v>34.85160213</v>
       </c>
       <c r="O14">
-        <v>6.6371271428</v>
+        <v>6.6218044047</v>
       </c>
       <c r="P14">
-        <v>28.2951209772</v>
+        <v>28.2297977253</v>
       </c>
       <c r="Q14">
-        <v>31.2951209772</v>
+        <v>31.2297977253</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.0998048801737729</v>
+        <v>0.1003194156391743</v>
       </c>
       <c r="T14">
-        <v>0.9891183461131867</v>
+        <v>0.9985422438594062</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2592,7 +2592,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>37.09628546523723</v>
+        <v>34.24272504483436</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2600,22 +2600,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09257448160608168</v>
+        <v>0.09243150865924323</v>
       </c>
       <c r="C15">
-        <v>140.9246684372243</v>
+        <v>139.4347071645958</v>
       </c>
       <c r="D15">
-        <v>136.4675684372243</v>
+        <v>136.5809071645958</v>
       </c>
       <c r="E15">
-        <v>19.7129</v>
+        <v>21.3162</v>
       </c>
       <c r="F15">
-        <v>20.8429</v>
+        <v>22.4462</v>
       </c>
       <c r="G15">
         <v>25.3</v>
@@ -2636,28 +2636,28 @@
         <v>35.9</v>
       </c>
       <c r="M15">
-        <v>1.04839787</v>
+        <v>1.12904386</v>
       </c>
       <c r="N15">
-        <v>34.85160213</v>
+        <v>34.77095614</v>
       </c>
       <c r="O15">
-        <v>6.6218044047</v>
+        <v>6.606481666599999</v>
       </c>
       <c r="P15">
-        <v>28.2297977253</v>
+        <v>28.1644744734</v>
       </c>
       <c r="Q15">
-        <v>31.2297977253</v>
+        <v>31.1644744734</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1003194156391743</v>
+        <v>0.1008459170456317</v>
       </c>
       <c r="T15">
-        <v>0.9985422438594062</v>
+        <v>1.008185302018328</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2674,7 +2674,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>34.24272504483436</v>
+        <v>31.79681611306048</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2682,22 +2682,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09243150865924323</v>
+        <v>0.09228853571240477</v>
       </c>
       <c r="C16">
-        <v>139.4347071645958</v>
+        <v>137.9449343080825</v>
       </c>
       <c r="D16">
-        <v>136.5809071645958</v>
+        <v>136.6944343080825</v>
       </c>
       <c r="E16">
-        <v>21.3162</v>
+        <v>22.9195</v>
       </c>
       <c r="F16">
-        <v>22.4462</v>
+        <v>24.0495</v>
       </c>
       <c r="G16">
         <v>25.3</v>
@@ -2718,28 +2718,28 @@
         <v>35.9</v>
       </c>
       <c r="M16">
-        <v>1.12904386</v>
+        <v>1.20968985</v>
       </c>
       <c r="N16">
-        <v>34.77095614</v>
+        <v>34.69031015</v>
       </c>
       <c r="O16">
-        <v>6.606481666599999</v>
+        <v>6.591158928500001</v>
       </c>
       <c r="P16">
-        <v>28.1644744734</v>
+        <v>28.0991512215</v>
       </c>
       <c r="Q16">
-        <v>31.1644744734</v>
+        <v>31.0991512215</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1008459170456317</v>
+        <v>0.1013848067204762</v>
       </c>
       <c r="T16">
-        <v>1.008185302018328</v>
+        <v>1.018055255663343</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2756,7 +2756,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>31.79681611306048</v>
+        <v>29.67702837218978</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2764,22 +2764,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09228853571240477</v>
+        <v>0.09214556276556631</v>
       </c>
       <c r="C17">
-        <v>137.9449343080825</v>
+        <v>136.4553503379141</v>
       </c>
       <c r="D17">
-        <v>136.6944343080825</v>
+        <v>136.8081503379141</v>
       </c>
       <c r="E17">
-        <v>22.9195</v>
+        <v>24.5228</v>
       </c>
       <c r="F17">
-        <v>24.0495</v>
+        <v>25.6528</v>
       </c>
       <c r="G17">
         <v>25.3</v>
@@ -2800,28 +2800,28 @@
         <v>35.9</v>
       </c>
       <c r="M17">
-        <v>1.20968985</v>
+        <v>1.29033584</v>
       </c>
       <c r="N17">
-        <v>34.69031015</v>
+        <v>34.60966416</v>
       </c>
       <c r="O17">
-        <v>6.591158928500001</v>
+        <v>6.5758361904</v>
       </c>
       <c r="P17">
-        <v>28.0991512215</v>
+        <v>28.0338279696</v>
       </c>
       <c r="Q17">
-        <v>31.0991512215</v>
+        <v>31.0338279696</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1013848067204762</v>
+        <v>0.1019365271018646</v>
       </c>
       <c r="T17">
-        <v>1.018055255663343</v>
+        <v>1.028160208204667</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2838,7 +2838,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>29.67702837218978</v>
+        <v>27.82221409892793</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2846,22 +2846,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09214556276556631</v>
+        <v>0.09200258981872783</v>
       </c>
       <c r="C18">
-        <v>136.4553503379141</v>
+        <v>134.9659557258866</v>
       </c>
       <c r="D18">
-        <v>136.8081503379141</v>
+        <v>136.9220557258866</v>
       </c>
       <c r="E18">
-        <v>24.5228</v>
+        <v>26.1261</v>
       </c>
       <c r="F18">
-        <v>25.6528</v>
+        <v>27.2561</v>
       </c>
       <c r="G18">
         <v>25.3</v>
@@ -2882,28 +2882,28 @@
         <v>35.9</v>
       </c>
       <c r="M18">
-        <v>1.29033584</v>
+        <v>1.37098183</v>
       </c>
       <c r="N18">
-        <v>34.60966416</v>
+        <v>34.52901817</v>
       </c>
       <c r="O18">
-        <v>6.5758361904</v>
+        <v>6.5605134523</v>
       </c>
       <c r="P18">
-        <v>28.0338279696</v>
+        <v>27.9685047177</v>
       </c>
       <c r="Q18">
-        <v>31.0338279696</v>
+        <v>30.9685047177</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1019365271018646</v>
+        <v>0.1025015419502745</v>
       </c>
       <c r="T18">
-        <v>1.028160208204667</v>
+        <v>1.038508653578312</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2920,7 +2920,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>27.82221409892793</v>
+        <v>26.18561326957922</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2928,22 +2928,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09200258981872783</v>
+        <v>0.09185961687188934</v>
       </c>
       <c r="C19">
-        <v>134.9659557258866</v>
+        <v>133.4767509453682</v>
       </c>
       <c r="D19">
-        <v>136.9220557258866</v>
+        <v>137.0361509453682</v>
       </c>
       <c r="E19">
-        <v>26.1261</v>
+        <v>27.7294</v>
       </c>
       <c r="F19">
-        <v>27.2561</v>
+        <v>28.8594</v>
       </c>
       <c r="G19">
         <v>25.3</v>
@@ -2964,28 +2964,28 @@
         <v>35.9</v>
       </c>
       <c r="M19">
-        <v>1.37098183</v>
+        <v>1.45162782</v>
       </c>
       <c r="N19">
-        <v>34.52901817</v>
+        <v>34.44837218</v>
       </c>
       <c r="O19">
-        <v>6.5605134523</v>
+        <v>6.5451907142</v>
       </c>
       <c r="P19">
-        <v>27.9685047177</v>
+        <v>27.9031814658</v>
       </c>
       <c r="Q19">
-        <v>30.9685047177</v>
+        <v>30.9031814658</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1025015419502745</v>
+        <v>0.1030803376486455</v>
       </c>
       <c r="T19">
-        <v>1.038508653578312</v>
+        <v>1.049109500058632</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -3002,7 +3002,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>26.18561326957922</v>
+        <v>24.73085697682482</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3010,22 +3010,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09185961687188936</v>
+        <v>0.09171664392505091</v>
       </c>
       <c r="C20">
-        <v>133.4767509453682</v>
+        <v>131.9877364713066</v>
       </c>
       <c r="D20">
-        <v>137.0361509453682</v>
+        <v>137.1504364713066</v>
       </c>
       <c r="E20">
-        <v>27.7294</v>
+        <v>29.3327</v>
       </c>
       <c r="F20">
-        <v>28.8594</v>
+        <v>30.4627</v>
       </c>
       <c r="G20">
         <v>25.3</v>
@@ -3046,28 +3046,28 @@
         <v>35.9</v>
       </c>
       <c r="M20">
-        <v>1.45162782</v>
+        <v>1.53227381</v>
       </c>
       <c r="N20">
-        <v>34.44837218</v>
+        <v>34.36772619</v>
       </c>
       <c r="O20">
-        <v>6.5451907142</v>
+        <v>6.5298679761</v>
       </c>
       <c r="P20">
-        <v>27.9031814658</v>
+        <v>27.8378582139</v>
       </c>
       <c r="Q20">
-        <v>30.9031814658</v>
+        <v>30.8378582139</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1030803376486455</v>
+        <v>0.1036734245988283</v>
       </c>
       <c r="T20">
-        <v>1.049109500058632</v>
+        <v>1.059972095834762</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -3084,7 +3084,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>24.73085697682482</v>
+        <v>23.42923292541299</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3092,22 +3092,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09171664392505091</v>
+        <v>0.09157367097821245</v>
       </c>
       <c r="C21">
-        <v>131.9877364713066</v>
+        <v>130.4989127802349</v>
       </c>
       <c r="D21">
-        <v>137.1504364713066</v>
+        <v>137.2649127802349</v>
       </c>
       <c r="E21">
-        <v>29.3327</v>
+        <v>30.936</v>
       </c>
       <c r="F21">
-        <v>30.4627</v>
+        <v>32.066</v>
       </c>
       <c r="G21">
         <v>25.3</v>
@@ -3128,28 +3128,28 @@
         <v>35.9</v>
       </c>
       <c r="M21">
-        <v>1.53227381</v>
+        <v>1.6129198</v>
       </c>
       <c r="N21">
-        <v>34.36772619</v>
+        <v>34.2870802</v>
       </c>
       <c r="O21">
-        <v>6.5298679761</v>
+        <v>6.514545238</v>
       </c>
       <c r="P21">
-        <v>27.8378582139</v>
+        <v>27.772534962</v>
       </c>
       <c r="Q21">
-        <v>30.8378582139</v>
+        <v>30.772534962</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1036734245988283</v>
+        <v>0.1042813387227655</v>
       </c>
       <c r="T21">
-        <v>1.059972095834762</v>
+        <v>1.071106256505295</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3166,7 +3166,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>23.42923292541299</v>
+        <v>22.25777127914234</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3174,22 +3174,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09157367097821245</v>
+        <v>0.09143069803137398</v>
       </c>
       <c r="C22">
-        <v>130.4989127802349</v>
+        <v>129.0102803502788</v>
       </c>
       <c r="D22">
-        <v>137.2649127802349</v>
+        <v>137.3795803502788</v>
       </c>
       <c r="E22">
-        <v>30.936</v>
+        <v>32.5393</v>
       </c>
       <c r="F22">
-        <v>32.066</v>
+        <v>33.6693</v>
       </c>
       <c r="G22">
         <v>25.3</v>
@@ -3210,28 +3210,28 @@
         <v>35.9</v>
       </c>
       <c r="M22">
-        <v>1.6129198</v>
+        <v>1.69356579</v>
       </c>
       <c r="N22">
-        <v>34.2870802</v>
+        <v>34.20643421</v>
       </c>
       <c r="O22">
-        <v>6.514545238</v>
+        <v>6.499222499899999</v>
       </c>
       <c r="P22">
-        <v>27.772534962</v>
+        <v>27.7072117101</v>
       </c>
       <c r="Q22">
-        <v>30.772534962</v>
+        <v>30.7072117101</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1042813387227655</v>
+        <v>0.1049046430776886</v>
       </c>
       <c r="T22">
-        <v>1.071106256505295</v>
+        <v>1.082522294661158</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3248,7 +3248,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>22.25777127914234</v>
+        <v>21.19787740870699</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3256,22 +3256,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09143069803137396</v>
+        <v>0.0912877250845355</v>
       </c>
       <c r="C23">
-        <v>129.0102803502788</v>
+        <v>127.5218396611628</v>
       </c>
       <c r="D23">
-        <v>137.3795803502788</v>
+        <v>137.4944396611628</v>
       </c>
       <c r="E23">
-        <v>32.53929999999999</v>
+        <v>34.14259999999999</v>
       </c>
       <c r="F23">
-        <v>33.66929999999999</v>
+        <v>35.2726</v>
       </c>
       <c r="G23">
         <v>25.3</v>
@@ -3292,28 +3292,28 @@
         <v>35.9</v>
       </c>
       <c r="M23">
-        <v>1.69356579</v>
+        <v>1.77421178</v>
       </c>
       <c r="N23">
-        <v>34.20643421</v>
+        <v>34.12578822</v>
       </c>
       <c r="O23">
-        <v>6.499222499899999</v>
+        <v>6.483899761799999</v>
       </c>
       <c r="P23">
-        <v>27.7072117101</v>
+        <v>27.6418884582</v>
       </c>
       <c r="Q23">
-        <v>30.7072117101</v>
+        <v>30.6418884582</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1049046430776886</v>
+        <v>0.1055439295955583</v>
       </c>
       <c r="T23">
-        <v>1.082522294661158</v>
+        <v>1.094231051744095</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3330,7 +3330,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>21.19787740870699</v>
+        <v>20.23433752649303</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3338,22 +3338,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.0912877250845355</v>
+        <v>0.09114475213769703</v>
       </c>
       <c r="C24">
-        <v>127.5218396611628</v>
+        <v>126.0335911942173</v>
       </c>
       <c r="D24">
-        <v>137.4944396611628</v>
+        <v>137.6094911942172</v>
       </c>
       <c r="E24">
-        <v>34.14259999999999</v>
+        <v>35.7459</v>
       </c>
       <c r="F24">
-        <v>35.2726</v>
+        <v>36.8759</v>
       </c>
       <c r="G24">
         <v>25.3</v>
@@ -3374,28 +3374,28 @@
         <v>35.9</v>
       </c>
       <c r="M24">
-        <v>1.77421178</v>
+        <v>1.85485777</v>
       </c>
       <c r="N24">
-        <v>34.12578822</v>
+        <v>34.04514223</v>
       </c>
       <c r="O24">
-        <v>6.483899761799999</v>
+        <v>6.468577023699999</v>
       </c>
       <c r="P24">
-        <v>27.6418884582</v>
+        <v>27.5765652063</v>
       </c>
       <c r="Q24">
-        <v>30.6418884582</v>
+        <v>30.5765652063</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1055439295955583</v>
+        <v>0.1061998209580481</v>
       </c>
       <c r="T24">
-        <v>1.094231051744095</v>
+        <v>1.106243932387627</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3412,7 +3412,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>20.23433752649303</v>
+        <v>19.35458372099333</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3420,22 +3420,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09114475213769703</v>
+        <v>0.09100177919085858</v>
       </c>
       <c r="C25">
-        <v>126.0335911942173</v>
+        <v>124.5455354323846</v>
       </c>
       <c r="D25">
-        <v>137.6094911942172</v>
+        <v>137.7247354323846</v>
       </c>
       <c r="E25">
-        <v>35.7459</v>
+        <v>37.3492</v>
       </c>
       <c r="F25">
-        <v>36.8759</v>
+        <v>38.4792</v>
       </c>
       <c r="G25">
         <v>25.3</v>
@@ -3456,28 +3456,28 @@
         <v>35.9</v>
       </c>
       <c r="M25">
-        <v>1.85485777</v>
+        <v>1.93550376</v>
       </c>
       <c r="N25">
-        <v>34.04514223</v>
+        <v>33.96449624</v>
       </c>
       <c r="O25">
-        <v>6.468577023699999</v>
+        <v>6.453254285599999</v>
       </c>
       <c r="P25">
-        <v>27.5765652063</v>
+        <v>27.5112419544</v>
       </c>
       <c r="Q25">
-        <v>30.5765652063</v>
+        <v>30.5112419544</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1061998209580481</v>
+        <v>0.1068729726195508</v>
       </c>
       <c r="T25">
-        <v>1.106243932387627</v>
+        <v>1.118572941469147</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3494,7 +3494,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>19.35458372099333</v>
+        <v>18.54814273261861</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3502,22 +3502,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09100177919085858</v>
+        <v>0.0908588062440201</v>
       </c>
       <c r="C26">
-        <v>124.5455354323846</v>
+        <v>123.0576728602269</v>
       </c>
       <c r="D26">
-        <v>137.7247354323846</v>
+        <v>137.8401728602269</v>
       </c>
       <c r="E26">
-        <v>37.34919999999999</v>
+        <v>38.95249999999999</v>
       </c>
       <c r="F26">
-        <v>38.47919999999999</v>
+        <v>40.0825</v>
       </c>
       <c r="G26">
         <v>25.3</v>
@@ -3538,28 +3538,28 @@
         <v>35.9</v>
       </c>
       <c r="M26">
-        <v>1.93550376</v>
+        <v>2.01614975</v>
       </c>
       <c r="N26">
-        <v>33.96449624</v>
+        <v>33.88385025</v>
       </c>
       <c r="O26">
-        <v>6.453254285600001</v>
+        <v>6.437931547500001</v>
       </c>
       <c r="P26">
-        <v>27.5112419544</v>
+        <v>27.4459187025</v>
       </c>
       <c r="Q26">
-        <v>30.5112419544</v>
+        <v>30.4459187025</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1068729726195508</v>
+        <v>0.1075640749920268</v>
       </c>
       <c r="T26">
-        <v>1.118572941469147</v>
+        <v>1.131230724126174</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3576,7 +3576,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>18.54814273261862</v>
+        <v>17.80621702331387</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3584,22 +3584,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.0908588062440201</v>
+        <v>0.09071583329718164</v>
       </c>
       <c r="C27">
-        <v>123.0576728602269</v>
+        <v>121.5700039639318</v>
       </c>
       <c r="D27">
-        <v>137.8401728602269</v>
+        <v>137.9558039639317</v>
       </c>
       <c r="E27">
-        <v>38.95249999999999</v>
+        <v>40.5558</v>
       </c>
       <c r="F27">
-        <v>40.0825</v>
+        <v>41.6858</v>
       </c>
       <c r="G27">
         <v>25.3</v>
@@ -3620,28 +3620,28 @@
         <v>35.9</v>
       </c>
       <c r="M27">
-        <v>2.01614975</v>
+        <v>2.09679574</v>
       </c>
       <c r="N27">
-        <v>33.88385025</v>
+        <v>33.80320426</v>
       </c>
       <c r="O27">
-        <v>6.437931547500001</v>
+        <v>6.422608809400001</v>
       </c>
       <c r="P27">
-        <v>27.4459187025</v>
+        <v>27.3805954506</v>
       </c>
       <c r="Q27">
-        <v>30.4459187025</v>
+        <v>30.3805954506</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1075640749920268</v>
+        <v>0.1082738558070022</v>
       </c>
       <c r="T27">
-        <v>1.131230724126174</v>
+        <v>1.144230609017175</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3658,7 +3658,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>17.80621702331387</v>
+        <v>17.12136252241718</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3666,22 +3666,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09071583329718164</v>
+        <v>0.09057286035034318</v>
       </c>
       <c r="C28">
-        <v>121.5700039639318</v>
+        <v>120.0825292313198</v>
       </c>
       <c r="D28">
-        <v>137.9558039639317</v>
+        <v>138.0716292313197</v>
       </c>
       <c r="E28">
-        <v>40.5558</v>
+        <v>42.1591</v>
       </c>
       <c r="F28">
-        <v>41.6858</v>
+        <v>43.2891</v>
       </c>
       <c r="G28">
         <v>25.3</v>
@@ -3702,28 +3702,28 @@
         <v>35.9</v>
       </c>
       <c r="M28">
-        <v>2.09679574</v>
+        <v>2.17744173</v>
       </c>
       <c r="N28">
-        <v>33.80320426</v>
+        <v>33.72255827</v>
       </c>
       <c r="O28">
-        <v>6.422608809400001</v>
+        <v>6.4072860713</v>
       </c>
       <c r="P28">
-        <v>27.3805954506</v>
+        <v>27.3152721987</v>
       </c>
       <c r="Q28">
-        <v>30.3805954506</v>
+        <v>30.3152721987</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1082738558070022</v>
+        <v>0.109003082671703</v>
       </c>
       <c r="T28">
-        <v>1.144230609017175</v>
+        <v>1.157586655138067</v>
       </c>
       <c r="U28">
         <v>0.0503</v>
@@ -3740,7 +3740,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>17.12136252241718</v>
+        <v>16.48723798454988</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3748,22 +3748,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09057286035034318</v>
+        <v>0.09042988740350469</v>
       </c>
       <c r="C29">
-        <v>120.0825292313198</v>
+        <v>118.5952491518511</v>
       </c>
       <c r="D29">
-        <v>138.0716292313197</v>
+        <v>138.1876491518511</v>
       </c>
       <c r="E29">
-        <v>42.1591</v>
+        <v>43.7624</v>
       </c>
       <c r="F29">
-        <v>43.2891</v>
+        <v>44.8924</v>
       </c>
       <c r="G29">
         <v>25.3</v>
@@ -3784,28 +3784,28 @@
         <v>35.9</v>
       </c>
       <c r="M29">
-        <v>2.17744173</v>
+        <v>2.25808772</v>
       </c>
       <c r="N29">
-        <v>33.72255827</v>
+        <v>33.64191228</v>
       </c>
       <c r="O29">
-        <v>6.4072860713</v>
+        <v>6.3919633332</v>
       </c>
       <c r="P29">
-        <v>27.3152721987</v>
+        <v>27.2499489468</v>
       </c>
       <c r="Q29">
-        <v>30.3152721987</v>
+        <v>30.2499489468</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.109003082671703</v>
+        <v>0.109752565838201</v>
       </c>
       <c r="T29">
-        <v>1.157586655138067</v>
+        <v>1.171313702540094</v>
       </c>
       <c r="U29">
         <v>0.0503</v>
@@ -3822,7 +3822,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>16.48723798454988</v>
+        <v>15.89840805653024</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3830,22 +3830,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09042988740350469</v>
+        <v>0.09028691445666626</v>
       </c>
       <c r="C30">
-        <v>118.5952491518511</v>
+        <v>117.1081642166325</v>
       </c>
       <c r="D30">
-        <v>138.1876491518511</v>
+        <v>138.3038642166325</v>
       </c>
       <c r="E30">
-        <v>43.7624</v>
+        <v>45.3657</v>
       </c>
       <c r="F30">
-        <v>44.8924</v>
+        <v>46.4957</v>
       </c>
       <c r="G30">
         <v>25.3</v>
@@ -3866,28 +3866,28 @@
         <v>35.9</v>
       </c>
       <c r="M30">
-        <v>2.25808772</v>
+        <v>2.33873371</v>
       </c>
       <c r="N30">
-        <v>33.64191228</v>
+        <v>33.56126629</v>
       </c>
       <c r="O30">
-        <v>6.3919633332</v>
+        <v>6.3766405951</v>
       </c>
       <c r="P30">
-        <v>27.2499489468</v>
+        <v>27.1846256949</v>
       </c>
       <c r="Q30">
-        <v>30.2499489468</v>
+        <v>30.1846256949</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.109752565838201</v>
+        <v>0.1105231612065722</v>
       </c>
       <c r="T30">
-        <v>1.171313702540094</v>
+        <v>1.185427427333728</v>
       </c>
       <c r="U30">
         <v>0.0503</v>
@@ -3904,7 +3904,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>15.89840805653024</v>
+        <v>15.35018708906368</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3912,22 +3912,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09028691445666624</v>
+        <v>0.09014394150982777</v>
       </c>
       <c r="C31">
-        <v>117.1081642166325</v>
+        <v>115.6212749184242</v>
       </c>
       <c r="D31">
-        <v>138.3038642166325</v>
+        <v>138.4202749184242</v>
       </c>
       <c r="E31">
-        <v>45.36569999999999</v>
+        <v>46.96899999999999</v>
       </c>
       <c r="F31">
-        <v>46.49569999999999</v>
+        <v>48.099</v>
       </c>
       <c r="G31">
         <v>25.3</v>
@@ -3948,28 +3948,28 @@
         <v>35.9</v>
       </c>
       <c r="M31">
-        <v>2.33873371</v>
+        <v>2.4193797</v>
       </c>
       <c r="N31">
-        <v>33.56126629</v>
+        <v>33.4806203</v>
       </c>
       <c r="O31">
-        <v>6.3766405951</v>
+        <v>6.361317857</v>
       </c>
       <c r="P31">
-        <v>27.1846256949</v>
+        <v>27.119302443</v>
       </c>
       <c r="Q31">
-        <v>30.1846256949</v>
+        <v>30.119302443</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1105231612065722</v>
+        <v>0.1113157735854683</v>
       </c>
       <c r="T31">
-        <v>1.185427427333728</v>
+        <v>1.199944401407179</v>
       </c>
       <c r="U31">
         <v>0.0503</v>
@@ -3986,7 +3986,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>15.35018708906368</v>
+        <v>14.83851418609489</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3994,22 +3994,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09014394150982777</v>
+        <v>0.09000096856298929</v>
       </c>
       <c r="C32">
-        <v>115.6212749184242</v>
+        <v>114.1345817516467</v>
       </c>
       <c r="D32">
-        <v>138.4202749184242</v>
+        <v>138.5368817516467</v>
       </c>
       <c r="E32">
-        <v>46.96899999999999</v>
+        <v>48.57229999999999</v>
       </c>
       <c r="F32">
-        <v>48.099</v>
+        <v>49.70229999999999</v>
       </c>
       <c r="G32">
         <v>25.3</v>
@@ -4030,28 +4030,28 @@
         <v>35.9</v>
       </c>
       <c r="M32">
-        <v>2.4193797</v>
+        <v>2.50002569</v>
       </c>
       <c r="N32">
-        <v>33.4806203</v>
+        <v>33.39997431</v>
       </c>
       <c r="O32">
-        <v>6.361317857</v>
+        <v>6.345995118899999</v>
       </c>
       <c r="P32">
-        <v>27.119302443</v>
+        <v>27.0539791911</v>
       </c>
       <c r="Q32">
-        <v>30.119302443</v>
+        <v>30.0539791911</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1113157735854683</v>
+        <v>0.1121313602362164</v>
       </c>
       <c r="T32">
-        <v>1.199944401407179</v>
+        <v>1.214882157337833</v>
       </c>
       <c r="U32">
         <v>0.0503</v>
@@ -4068,7 +4068,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>14.83851418609489</v>
+        <v>14.35985243815635</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4076,22 +4076,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09000096856298929</v>
+        <v>0.08985799561615083</v>
       </c>
       <c r="C33">
-        <v>114.1345817516467</v>
+        <v>112.6480852123881</v>
       </c>
       <c r="D33">
-        <v>138.5368817516467</v>
+        <v>138.653685212388</v>
       </c>
       <c r="E33">
-        <v>48.57229999999999</v>
+        <v>50.1756</v>
       </c>
       <c r="F33">
-        <v>49.70229999999999</v>
+        <v>51.3056</v>
       </c>
       <c r="G33">
         <v>25.3</v>
@@ -4112,28 +4112,28 @@
         <v>35.9</v>
       </c>
       <c r="M33">
-        <v>2.50002569</v>
+        <v>2.58067168</v>
       </c>
       <c r="N33">
-        <v>33.39997431</v>
+        <v>33.31932832</v>
       </c>
       <c r="O33">
-        <v>6.345995118899999</v>
+        <v>6.330672380799999</v>
       </c>
       <c r="P33">
-        <v>27.0539791911</v>
+        <v>26.9886559392</v>
       </c>
       <c r="Q33">
-        <v>30.0539791911</v>
+        <v>29.9886559392</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1121313602362164</v>
+        <v>0.1129709347296336</v>
       </c>
       <c r="T33">
-        <v>1.214882157337833</v>
+        <v>1.230259259031152</v>
       </c>
       <c r="U33">
         <v>0.0503</v>
@@ -4150,7 +4150,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>14.35985243815635</v>
+        <v>13.91110704946396</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4158,22 +4158,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08985799561615083</v>
+        <v>0.08971502266931236</v>
       </c>
       <c r="C34">
-        <v>112.6480852123881</v>
+        <v>111.1617857984108</v>
       </c>
       <c r="D34">
-        <v>138.653685212388</v>
+        <v>138.7706857984108</v>
       </c>
       <c r="E34">
-        <v>50.1756</v>
+        <v>51.77889999999999</v>
       </c>
       <c r="F34">
-        <v>51.3056</v>
+        <v>52.9089</v>
       </c>
       <c r="G34">
         <v>25.3</v>
@@ -4194,28 +4194,28 @@
         <v>35.9</v>
       </c>
       <c r="M34">
-        <v>2.58067168</v>
+        <v>2.66131767</v>
       </c>
       <c r="N34">
-        <v>33.31932832</v>
+        <v>33.23868233</v>
       </c>
       <c r="O34">
-        <v>6.330672380799999</v>
+        <v>6.315349642699999</v>
       </c>
       <c r="P34">
-        <v>26.9886559392</v>
+        <v>26.9233326873</v>
       </c>
       <c r="Q34">
-        <v>29.9886559392</v>
+        <v>29.9233326873</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1129709347296336</v>
+        <v>0.1138355711482274</v>
       </c>
       <c r="T34">
-        <v>1.230259259031152</v>
+        <v>1.246095378685466</v>
       </c>
       <c r="U34">
         <v>0.0503</v>
@@ -4232,7 +4232,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>13.91110704946396</v>
+        <v>13.48955835099535</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4240,22 +4240,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08971502266931236</v>
+        <v>0.0895720497224739</v>
       </c>
       <c r="C35">
-        <v>111.1617857984108</v>
+        <v>109.675684009159</v>
       </c>
       <c r="D35">
-        <v>138.7706857984108</v>
+        <v>138.887884009159</v>
       </c>
       <c r="E35">
-        <v>51.77889999999999</v>
+        <v>53.3822</v>
       </c>
       <c r="F35">
-        <v>52.9089</v>
+        <v>54.5122</v>
       </c>
       <c r="G35">
         <v>25.3</v>
@@ -4276,28 +4276,28 @@
         <v>35.9</v>
       </c>
       <c r="M35">
-        <v>2.66131767</v>
+        <v>2.74196366</v>
       </c>
       <c r="N35">
-        <v>33.23868233</v>
+        <v>33.15803634</v>
       </c>
       <c r="O35">
-        <v>6.315349642699999</v>
+        <v>6.300026904599999</v>
       </c>
       <c r="P35">
-        <v>26.9233326873</v>
+        <v>26.8580094354</v>
       </c>
       <c r="Q35">
-        <v>29.9233326873</v>
+        <v>29.8580094354</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1138355711482274</v>
+        <v>0.114726408670415</v>
       </c>
       <c r="T35">
-        <v>1.246095378685466</v>
+        <v>1.262411380753548</v>
       </c>
       <c r="U35">
         <v>0.0503</v>
@@ -4314,7 +4314,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>13.48955835099535</v>
+        <v>13.09280663478961</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4322,22 +4322,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.0895720497224739</v>
+        <v>0.08985432677563543</v>
       </c>
       <c r="C36">
-        <v>109.675684009159</v>
+        <v>107.8411851075699</v>
       </c>
       <c r="D36">
-        <v>138.887884009159</v>
+        <v>138.6566851075699</v>
       </c>
       <c r="E36">
-        <v>53.3822</v>
+        <v>54.98549999999999</v>
       </c>
       <c r="F36">
-        <v>54.5122</v>
+        <v>56.1155</v>
       </c>
       <c r="G36">
         <v>25.3</v>
@@ -4358,45 +4358,45 @@
         <v>35.9</v>
       </c>
       <c r="M36">
-        <v>2.74196366</v>
+        <v>2.9067829</v>
       </c>
       <c r="N36">
-        <v>33.15803634</v>
+        <v>32.9932171</v>
       </c>
       <c r="O36">
-        <v>6.300026904599999</v>
+        <v>6.268711248999999</v>
       </c>
       <c r="P36">
-        <v>26.8580094354</v>
+        <v>26.724505851</v>
       </c>
       <c r="Q36">
-        <v>29.8580094354</v>
+        <v>29.724505851</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.114726408670415</v>
+        <v>0.1156446565779007</v>
       </c>
       <c r="T36">
-        <v>1.262411380753548</v>
+        <v>1.279229413654493</v>
       </c>
       <c r="U36">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V36">
         <v>0.19</v>
       </c>
       <c r="W36">
-        <v>0.040743</v>
+        <v>0.041958</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y36">
-        <v>13.09280663478961</v>
+        <v>12.35042355588372</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4404,22 +4404,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08985432677563543</v>
+        <v>0.08972350382879699</v>
       </c>
       <c r="C37">
-        <v>107.8411851075699</v>
+        <v>106.3449398112306</v>
       </c>
       <c r="D37">
-        <v>138.6566851075699</v>
+        <v>138.7637398112306</v>
       </c>
       <c r="E37">
-        <v>54.98549999999999</v>
+        <v>56.5888</v>
       </c>
       <c r="F37">
-        <v>56.1155</v>
+        <v>57.7188</v>
       </c>
       <c r="G37">
         <v>25.3</v>
@@ -4440,28 +4440,28 @@
         <v>35.9</v>
       </c>
       <c r="M37">
-        <v>2.9067829</v>
+        <v>2.98983384</v>
       </c>
       <c r="N37">
-        <v>32.9932171</v>
+        <v>32.91016616</v>
       </c>
       <c r="O37">
-        <v>6.268711248999999</v>
+        <v>6.252931570399999</v>
       </c>
       <c r="P37">
-        <v>26.724505851</v>
+        <v>26.65723458959999</v>
       </c>
       <c r="Q37">
-        <v>29.724505851</v>
+        <v>29.65723458959999</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1156446565779007</v>
+        <v>0.1165915997324953</v>
       </c>
       <c r="T37">
-        <v>1.279229413654493</v>
+        <v>1.296573010083593</v>
       </c>
       <c r="U37">
         <v>0.0518</v>
@@ -4478,7 +4478,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>12.35042355588372</v>
+        <v>12.00735623488695</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4486,22 +4486,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.089723503828797</v>
+        <v>0.08959268088195854</v>
       </c>
       <c r="C38">
-        <v>106.3449398112306</v>
+        <v>104.8488599532191</v>
       </c>
       <c r="D38">
-        <v>138.7637398112306</v>
+        <v>138.8709599532191</v>
       </c>
       <c r="E38">
-        <v>56.58879999999999</v>
+        <v>58.19209999999999</v>
       </c>
       <c r="F38">
-        <v>57.71879999999999</v>
+        <v>59.32209999999999</v>
       </c>
       <c r="G38">
         <v>25.3</v>
@@ -4522,28 +4522,28 @@
         <v>35.9</v>
       </c>
       <c r="M38">
-        <v>2.98983384</v>
+        <v>3.072884779999999</v>
       </c>
       <c r="N38">
-        <v>32.91016616</v>
+        <v>32.82711522</v>
       </c>
       <c r="O38">
-        <v>6.252931570399999</v>
+        <v>6.237151891799999</v>
       </c>
       <c r="P38">
-        <v>26.65723458959999</v>
+        <v>26.5899633282</v>
       </c>
       <c r="Q38">
-        <v>29.65723458959999</v>
+        <v>29.5899633282</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1165915997324953</v>
+        <v>0.1175686045745374</v>
       </c>
       <c r="T38">
-        <v>1.296573010083593</v>
+        <v>1.314467196875521</v>
       </c>
       <c r="U38">
         <v>0.0518</v>
@@ -4560,7 +4560,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>12.00735623488695</v>
+        <v>11.68283309340352</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4568,22 +4568,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08959268088195854</v>
+        <v>0.08946185793512007</v>
       </c>
       <c r="C39">
-        <v>104.8488599532191</v>
+        <v>103.352945917325</v>
       </c>
       <c r="D39">
-        <v>138.8709599532191</v>
+        <v>138.978345917325</v>
       </c>
       <c r="E39">
-        <v>58.19209999999999</v>
+        <v>59.79539999999999</v>
       </c>
       <c r="F39">
-        <v>59.32209999999999</v>
+        <v>60.9254</v>
       </c>
       <c r="G39">
         <v>25.3</v>
@@ -4604,28 +4604,28 @@
         <v>35.9</v>
       </c>
       <c r="M39">
-        <v>3.072884779999999</v>
+        <v>3.15593572</v>
       </c>
       <c r="N39">
-        <v>32.82711522</v>
+        <v>32.74406428</v>
       </c>
       <c r="O39">
-        <v>6.237151891799999</v>
+        <v>6.2213722132</v>
       </c>
       <c r="P39">
-        <v>26.5899633282</v>
+        <v>26.5226920668</v>
       </c>
       <c r="Q39">
-        <v>29.5899633282</v>
+        <v>29.5226920668</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1175686045745374</v>
+        <v>0.1185771257018066</v>
       </c>
       <c r="T39">
-        <v>1.314467196875521</v>
+        <v>1.332938615499447</v>
       </c>
       <c r="U39">
         <v>0.0518</v>
@@ -4642,7 +4642,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>11.68283309340352</v>
+        <v>11.37539011726132</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4650,22 +4650,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08946185793512007</v>
+        <v>0.0893310349882816</v>
       </c>
       <c r="C40">
-        <v>103.352945917325</v>
+        <v>101.8571980885263</v>
       </c>
       <c r="D40">
-        <v>138.978345917325</v>
+        <v>139.0858980885263</v>
       </c>
       <c r="E40">
-        <v>59.79539999999999</v>
+        <v>61.39869999999999</v>
       </c>
       <c r="F40">
-        <v>60.9254</v>
+        <v>62.52869999999999</v>
       </c>
       <c r="G40">
         <v>25.3</v>
@@ -4686,28 +4686,28 @@
         <v>35.9</v>
       </c>
       <c r="M40">
-        <v>3.15593572</v>
+        <v>3.23898666</v>
       </c>
       <c r="N40">
-        <v>32.74406428</v>
+        <v>32.66101334</v>
       </c>
       <c r="O40">
-        <v>6.2213722132</v>
+        <v>6.205592534599999</v>
       </c>
       <c r="P40">
-        <v>26.5226920668</v>
+        <v>26.4554208054</v>
       </c>
       <c r="Q40">
-        <v>29.5226920668</v>
+        <v>29.4554208054</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1185771257018066</v>
+        <v>0.1196187130955436</v>
       </c>
       <c r="T40">
-        <v>1.332938615499447</v>
+        <v>1.352015654406125</v>
       </c>
       <c r="U40">
         <v>0.0518</v>
@@ -4724,7 +4724,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>11.37539011726132</v>
+        <v>11.08371344758796</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4732,22 +4732,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.0893310349882816</v>
+        <v>0.08920021204144311</v>
       </c>
       <c r="C41">
-        <v>101.8571980885263</v>
+        <v>100.3616168529935</v>
       </c>
       <c r="D41">
-        <v>139.0858980885263</v>
+        <v>139.1936168529934</v>
       </c>
       <c r="E41">
-        <v>61.39869999999999</v>
+        <v>63.00199999999999</v>
       </c>
       <c r="F41">
-        <v>62.52869999999999</v>
+        <v>64.13199999999999</v>
       </c>
       <c r="G41">
         <v>25.3</v>
@@ -4768,28 +4768,28 @@
         <v>35.9</v>
       </c>
       <c r="M41">
-        <v>3.23898666</v>
+        <v>3.322037599999999</v>
       </c>
       <c r="N41">
-        <v>32.66101334</v>
+        <v>32.5779624</v>
       </c>
       <c r="O41">
-        <v>6.205592534599999</v>
+        <v>6.189812856</v>
       </c>
       <c r="P41">
-        <v>26.4554208054</v>
+        <v>26.388149544</v>
       </c>
       <c r="Q41">
-        <v>29.4554208054</v>
+        <v>29.388149544</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1196187130955436</v>
+        <v>0.1206950200690719</v>
       </c>
       <c r="T41">
-        <v>1.352015654406125</v>
+        <v>1.371728594609692</v>
       </c>
       <c r="U41">
         <v>0.0518</v>
@@ -4806,7 +4806,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>11.08371344758796</v>
+        <v>10.80662061139826</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4814,22 +4814,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08920021204144311</v>
+        <v>0.08906938909460466</v>
       </c>
       <c r="C42">
-        <v>100.3616168529935</v>
+        <v>98.86620259809416</v>
       </c>
       <c r="D42">
-        <v>139.1936168529934</v>
+        <v>139.3015025980941</v>
       </c>
       <c r="E42">
-        <v>63.00199999999999</v>
+        <v>64.6053</v>
       </c>
       <c r="F42">
-        <v>64.13199999999999</v>
+        <v>65.7353</v>
       </c>
       <c r="G42">
         <v>25.3</v>
@@ -4850,28 +4850,28 @@
         <v>35.9</v>
       </c>
       <c r="M42">
-        <v>3.322037599999999</v>
+        <v>3.405088539999999</v>
       </c>
       <c r="N42">
-        <v>32.5779624</v>
+        <v>32.49491146</v>
       </c>
       <c r="O42">
-        <v>6.189812856</v>
+        <v>6.174033177399999</v>
       </c>
       <c r="P42">
-        <v>26.388149544</v>
+        <v>26.3208782826</v>
       </c>
       <c r="Q42">
-        <v>29.388149544</v>
+        <v>29.3208782826</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1206950200690719</v>
+        <v>0.1218078120247537</v>
       </c>
       <c r="T42">
-        <v>1.371728594609692</v>
+        <v>1.392109770074397</v>
       </c>
       <c r="U42">
         <v>0.0518</v>
@@ -4888,7 +4888,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>10.80662061139826</v>
+        <v>10.54304449892513</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4896,22 +4896,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08906938909460466</v>
+        <v>0.0889385661477662</v>
       </c>
       <c r="C43">
-        <v>98.86620259809416</v>
+        <v>97.37095571239804</v>
       </c>
       <c r="D43">
-        <v>139.3015025980941</v>
+        <v>139.409555712398</v>
       </c>
       <c r="E43">
-        <v>64.6053</v>
+        <v>66.2086</v>
       </c>
       <c r="F43">
-        <v>65.7353</v>
+        <v>67.3386</v>
       </c>
       <c r="G43">
         <v>25.3</v>
@@ -4932,28 +4932,28 @@
         <v>35.9</v>
       </c>
       <c r="M43">
-        <v>3.405088539999999</v>
+        <v>3.48813948</v>
       </c>
       <c r="N43">
-        <v>32.49491146</v>
+        <v>32.41186052</v>
       </c>
       <c r="O43">
-        <v>6.174033177399999</v>
+        <v>6.1582534988</v>
       </c>
       <c r="P43">
-        <v>26.3208782826</v>
+        <v>26.2536070212</v>
       </c>
       <c r="Q43">
-        <v>29.3208782826</v>
+        <v>29.2536070212</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1218078120247537</v>
+        <v>0.1229589761168383</v>
       </c>
       <c r="T43">
-        <v>1.392109770074397</v>
+        <v>1.413193744693057</v>
       </c>
       <c r="U43">
         <v>0.0518</v>
@@ -4970,7 +4970,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>10.54304449892513</v>
+        <v>10.2920196299031</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4978,22 +4978,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.0889385661477662</v>
+        <v>0.08880774320092774</v>
       </c>
       <c r="C44">
-        <v>97.37095571239806</v>
+        <v>95.87587658568135</v>
       </c>
       <c r="D44">
-        <v>139.409555712398</v>
+        <v>139.5177765856813</v>
       </c>
       <c r="E44">
-        <v>66.20859999999999</v>
+        <v>67.81189999999999</v>
       </c>
       <c r="F44">
-        <v>67.33859999999999</v>
+        <v>68.94189999999999</v>
       </c>
       <c r="G44">
         <v>25.3</v>
@@ -5014,28 +5014,28 @@
         <v>35.9</v>
       </c>
       <c r="M44">
-        <v>3.488139479999999</v>
+        <v>3.571190419999999</v>
       </c>
       <c r="N44">
-        <v>32.41186052</v>
+        <v>32.32880958</v>
       </c>
       <c r="O44">
-        <v>6.1582534988</v>
+        <v>6.142473820199999</v>
       </c>
       <c r="P44">
-        <v>26.2536070212</v>
+        <v>26.1863357598</v>
       </c>
       <c r="Q44">
-        <v>29.2536070212</v>
+        <v>29.1863357598</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1229589761168383</v>
+        <v>0.1241505319314521</v>
       </c>
       <c r="T44">
-        <v>1.413193744693057</v>
+        <v>1.435017507894828</v>
       </c>
       <c r="U44">
         <v>0.0518</v>
@@ -5052,7 +5052,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>10.2920196299031</v>
+        <v>10.05267033618443</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5060,22 +5060,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08880774320092774</v>
+        <v>0.0886769202540893</v>
       </c>
       <c r="C45">
-        <v>95.87587658568135</v>
+        <v>94.3809656089314</v>
       </c>
       <c r="D45">
-        <v>139.5177765856813</v>
+        <v>139.6261656089314</v>
       </c>
       <c r="E45">
-        <v>67.81189999999999</v>
+        <v>69.4152</v>
       </c>
       <c r="F45">
-        <v>68.94189999999999</v>
+        <v>70.54519999999999</v>
       </c>
       <c r="G45">
         <v>25.3</v>
@@ -5096,28 +5096,28 @@
         <v>35.9</v>
       </c>
       <c r="M45">
-        <v>3.571190419999999</v>
+        <v>3.654241359999999</v>
       </c>
       <c r="N45">
-        <v>32.32880958</v>
+        <v>32.24575864</v>
       </c>
       <c r="O45">
-        <v>6.142473820199999</v>
+        <v>6.1266941416</v>
       </c>
       <c r="P45">
-        <v>26.1863357598</v>
+        <v>26.1190644984</v>
       </c>
       <c r="Q45">
-        <v>29.1863357598</v>
+        <v>29.1190644984</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1241505319314521</v>
+        <v>0.1253846433108737</v>
       </c>
       <c r="T45">
-        <v>1.435017507894828</v>
+        <v>1.457620691210948</v>
       </c>
       <c r="U45">
         <v>0.0518</v>
@@ -5134,7 +5134,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>10.05267033618443</v>
+        <v>9.824200555816599</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5142,22 +5142,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.0886769202540893</v>
+        <v>0.0891657473072508</v>
       </c>
       <c r="C46">
-        <v>94.3809656089314</v>
+        <v>92.37352266504173</v>
       </c>
       <c r="D46">
-        <v>139.6261656089314</v>
+        <v>139.2220226650417</v>
       </c>
       <c r="E46">
-        <v>69.4152</v>
+        <v>71.0185</v>
       </c>
       <c r="F46">
-        <v>70.54519999999999</v>
+        <v>72.1485</v>
       </c>
       <c r="G46">
         <v>25.3</v>
@@ -5178,45 +5178,45 @@
         <v>35.9</v>
       </c>
       <c r="M46">
-        <v>3.654241359999999</v>
+        <v>3.85994475</v>
       </c>
       <c r="N46">
-        <v>32.24575864</v>
+        <v>32.04005525</v>
       </c>
       <c r="O46">
-        <v>6.1266941416</v>
+        <v>6.0876104975</v>
       </c>
       <c r="P46">
-        <v>26.1190644984</v>
+        <v>25.9524447525</v>
       </c>
       <c r="Q46">
-        <v>29.1190644984</v>
+        <v>28.9524447525</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1253846433108737</v>
+        <v>0.1266636314677287</v>
       </c>
       <c r="T46">
-        <v>1.457620691210948</v>
+        <v>1.481045808465836</v>
       </c>
       <c r="U46">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V46">
         <v>0.19</v>
       </c>
       <c r="W46">
-        <v>0.041958</v>
+        <v>0.04333500000000001</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y46">
-        <v>9.824200555816599</v>
+        <v>9.300651259321782</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5224,22 +5224,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.0891657473072508</v>
+        <v>0.08904869436041235</v>
       </c>
       <c r="C47">
-        <v>92.37352266504173</v>
+        <v>90.86678424431938</v>
       </c>
       <c r="D47">
-        <v>139.2220226650417</v>
+        <v>139.3185842443194</v>
       </c>
       <c r="E47">
-        <v>71.0185</v>
+        <v>72.62180000000001</v>
       </c>
       <c r="F47">
-        <v>72.1485</v>
+        <v>73.7518</v>
       </c>
       <c r="G47">
         <v>25.3</v>
@@ -5260,28 +5260,28 @@
         <v>35.9</v>
       </c>
       <c r="M47">
-        <v>3.85994475</v>
+        <v>3.9457213</v>
       </c>
       <c r="N47">
-        <v>32.04005525</v>
+        <v>31.9542787</v>
       </c>
       <c r="O47">
-        <v>6.0876104975</v>
+        <v>6.071312953</v>
       </c>
       <c r="P47">
-        <v>25.9524447525</v>
+        <v>25.882965747</v>
       </c>
       <c r="Q47">
-        <v>28.9524447525</v>
+        <v>28.882965747</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1266636314677287</v>
+        <v>0.1279899895563191</v>
       </c>
       <c r="T47">
-        <v>1.481045808465836</v>
+        <v>1.50533852265609</v>
       </c>
       <c r="U47">
         <v>0.0535</v>
@@ -5298,7 +5298,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>9.300651259321782</v>
+        <v>9.09846318846696</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5306,22 +5306,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08904869436041235</v>
+        <v>0.08893164141357388</v>
       </c>
       <c r="C48">
-        <v>90.86678424431938</v>
+        <v>89.36017986288104</v>
       </c>
       <c r="D48">
-        <v>139.3185842443194</v>
+        <v>139.415279862881</v>
       </c>
       <c r="E48">
-        <v>72.62180000000001</v>
+        <v>74.2251</v>
       </c>
       <c r="F48">
-        <v>73.7518</v>
+        <v>75.35509999999999</v>
       </c>
       <c r="G48">
         <v>25.3</v>
@@ -5342,28 +5342,28 @@
         <v>35.9</v>
       </c>
       <c r="M48">
-        <v>3.9457213</v>
+        <v>4.031497849999999</v>
       </c>
       <c r="N48">
-        <v>31.9542787</v>
+        <v>31.86850215</v>
       </c>
       <c r="O48">
-        <v>6.071312953</v>
+        <v>6.055015408499999</v>
       </c>
       <c r="P48">
-        <v>25.882965747</v>
+        <v>25.8134867415</v>
       </c>
       <c r="Q48">
-        <v>28.882965747</v>
+        <v>28.8134867415</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1279899895563191</v>
+        <v>0.1293663988935356</v>
       </c>
       <c r="T48">
-        <v>1.50533852265609</v>
+        <v>1.530547943042203</v>
       </c>
       <c r="U48">
         <v>0.0535</v>
@@ -5380,7 +5380,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>9.09846318846696</v>
+        <v>8.90487886530809</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5388,22 +5388,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08893164141357388</v>
+        <v>0.08881458846673543</v>
       </c>
       <c r="C49">
-        <v>89.36017986288104</v>
+        <v>87.85370980001481</v>
       </c>
       <c r="D49">
-        <v>139.415279862881</v>
+        <v>139.5121098000148</v>
       </c>
       <c r="E49">
-        <v>74.2251</v>
+        <v>75.8284</v>
       </c>
       <c r="F49">
-        <v>75.35509999999999</v>
+        <v>76.9584</v>
       </c>
       <c r="G49">
         <v>25.3</v>
@@ -5424,28 +5424,28 @@
         <v>35.9</v>
       </c>
       <c r="M49">
-        <v>4.031497849999999</v>
+        <v>4.117274399999999</v>
       </c>
       <c r="N49">
-        <v>31.86850215</v>
+        <v>31.7827256</v>
       </c>
       <c r="O49">
-        <v>6.055015408499999</v>
+        <v>6.038717864</v>
       </c>
       <c r="P49">
-        <v>25.8134867415</v>
+        <v>25.744007736</v>
       </c>
       <c r="Q49">
-        <v>28.8134867415</v>
+        <v>28.744007736</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1293663988935356</v>
+        <v>0.1307957470514143</v>
       </c>
       <c r="T49">
-        <v>1.530547943042203</v>
+        <v>1.55672695652009</v>
       </c>
       <c r="U49">
         <v>0.0535</v>
@@ -5462,7 +5462,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>8.90487886530809</v>
+        <v>8.719360555614172</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5470,22 +5470,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.0888145884667354</v>
+        <v>0.08869753551989695</v>
       </c>
       <c r="C50">
-        <v>87.85370980001485</v>
+        <v>86.34737433578555</v>
       </c>
       <c r="D50">
-        <v>139.5121098000148</v>
+        <v>139.6090743357855</v>
       </c>
       <c r="E50">
-        <v>75.82839999999999</v>
+        <v>77.43169999999999</v>
       </c>
       <c r="F50">
-        <v>76.95839999999998</v>
+        <v>78.56169999999999</v>
       </c>
       <c r="G50">
         <v>25.3</v>
@@ -5506,28 +5506,28 @@
         <v>35.9</v>
       </c>
       <c r="M50">
-        <v>4.117274399999999</v>
+        <v>4.203050949999999</v>
       </c>
       <c r="N50">
-        <v>31.7827256</v>
+        <v>31.69694905</v>
       </c>
       <c r="O50">
-        <v>6.038717864</v>
+        <v>6.0224203195</v>
       </c>
       <c r="P50">
-        <v>25.744007736</v>
+        <v>25.6745287305</v>
       </c>
       <c r="Q50">
-        <v>28.744007736</v>
+        <v>28.6745287305</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1307957470514142</v>
+        <v>0.1322811480782293</v>
       </c>
       <c r="T50">
-        <v>1.55672695652009</v>
+        <v>1.583932597977501</v>
       </c>
       <c r="U50">
         <v>0.0535</v>
@@ -5544,7 +5544,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>8.719360555614172</v>
+        <v>8.541414421826129</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5552,22 +5552,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08869753551989695</v>
+        <v>0.08858048257305848</v>
       </c>
       <c r="C51">
-        <v>86.34737433578555</v>
+        <v>84.84117375103693</v>
       </c>
       <c r="D51">
-        <v>139.6090743357855</v>
+        <v>139.7061737510369</v>
       </c>
       <c r="E51">
-        <v>77.43169999999999</v>
+        <v>79.035</v>
       </c>
       <c r="F51">
-        <v>78.56169999999999</v>
+        <v>80.16499999999999</v>
       </c>
       <c r="G51">
         <v>25.3</v>
@@ -5588,28 +5588,28 @@
         <v>35.9</v>
       </c>
       <c r="M51">
-        <v>4.203050949999999</v>
+        <v>4.288827499999999</v>
       </c>
       <c r="N51">
-        <v>31.69694905</v>
+        <v>31.6111725</v>
       </c>
       <c r="O51">
-        <v>6.0224203195</v>
+        <v>6.006122775</v>
       </c>
       <c r="P51">
-        <v>25.6745287305</v>
+        <v>25.605049725</v>
       </c>
       <c r="Q51">
-        <v>28.6745287305</v>
+        <v>28.605049725</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1322811480782293</v>
+        <v>0.1338259651461169</v>
       </c>
       <c r="T51">
-        <v>1.583932597977501</v>
+        <v>1.612226465093209</v>
       </c>
       <c r="U51">
         <v>0.0535</v>
@@ -5626,7 +5626,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>8.541414421826129</v>
+        <v>8.370586133389605</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5634,22 +5634,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08858048257305848</v>
+        <v>0.08846342962622002</v>
       </c>
       <c r="C52">
-        <v>84.84117375103693</v>
+        <v>83.33510832739468</v>
       </c>
       <c r="D52">
-        <v>139.7061737510369</v>
+        <v>139.8034083273947</v>
       </c>
       <c r="E52">
-        <v>79.035</v>
+        <v>80.6383</v>
       </c>
       <c r="F52">
-        <v>80.16499999999999</v>
+        <v>81.7683</v>
       </c>
       <c r="G52">
         <v>25.3</v>
@@ -5670,28 +5670,28 @@
         <v>35.9</v>
       </c>
       <c r="M52">
-        <v>4.288827499999999</v>
+        <v>4.374604049999999</v>
       </c>
       <c r="N52">
-        <v>31.6111725</v>
+        <v>31.52539595</v>
       </c>
       <c r="O52">
-        <v>6.006122775</v>
+        <v>5.9898252305</v>
       </c>
       <c r="P52">
-        <v>25.605049725</v>
+        <v>25.5355707195</v>
       </c>
       <c r="Q52">
-        <v>28.605049725</v>
+        <v>28.5355707195</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1338259651461169</v>
+        <v>0.1354338359718776</v>
       </c>
       <c r="T52">
-        <v>1.612226465093209</v>
+        <v>1.641675183927926</v>
       </c>
       <c r="U52">
         <v>0.0535</v>
@@ -5708,7 +5708,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>8.370586133389605</v>
+        <v>8.20645699351922</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5716,22 +5716,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08846342962622002</v>
+        <v>0.08834637667938156</v>
       </c>
       <c r="C53">
-        <v>83.33510832739468</v>
+        <v>81.82917834726911</v>
       </c>
       <c r="D53">
-        <v>139.8034083273947</v>
+        <v>139.9007783472691</v>
       </c>
       <c r="E53">
-        <v>80.6383</v>
+        <v>82.24160000000001</v>
       </c>
       <c r="F53">
-        <v>81.7683</v>
+        <v>83.3716</v>
       </c>
       <c r="G53">
         <v>25.3</v>
@@ -5752,28 +5752,28 @@
         <v>35.9</v>
       </c>
       <c r="M53">
-        <v>4.374604049999999</v>
+        <v>4.4603806</v>
       </c>
       <c r="N53">
-        <v>31.52539595</v>
+        <v>31.4396194</v>
       </c>
       <c r="O53">
-        <v>5.9898252305</v>
+        <v>5.973527686</v>
       </c>
       <c r="P53">
-        <v>25.5355707195</v>
+        <v>25.466091714</v>
       </c>
       <c r="Q53">
-        <v>28.5355707195</v>
+        <v>28.466091714</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1354338359718776</v>
+        <v>0.1371087014153782</v>
       </c>
       <c r="T53">
-        <v>1.641675183927926</v>
+        <v>1.672350932714089</v>
       </c>
       <c r="U53">
         <v>0.0535</v>
@@ -5790,7 +5790,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>8.20645699351922</v>
+        <v>8.04864051287462</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5798,22 +5798,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.08834637667938156</v>
+        <v>0.08822932373254308</v>
       </c>
       <c r="C54">
-        <v>81.82917834726911</v>
+        <v>80.32338409385781</v>
       </c>
       <c r="D54">
-        <v>139.9007783472691</v>
+        <v>139.9982840938578</v>
       </c>
       <c r="E54">
-        <v>82.24160000000001</v>
+        <v>83.8449</v>
       </c>
       <c r="F54">
-        <v>83.3716</v>
+        <v>84.97489999999999</v>
       </c>
       <c r="G54">
         <v>25.3</v>
@@ -5834,28 +5834,28 @@
         <v>35.9</v>
       </c>
       <c r="M54">
-        <v>4.4603806</v>
+        <v>4.546157149999999</v>
       </c>
       <c r="N54">
-        <v>31.4396194</v>
+        <v>31.35384285</v>
       </c>
       <c r="O54">
-        <v>5.973527686</v>
+        <v>5.9572301415</v>
       </c>
       <c r="P54">
-        <v>25.466091714</v>
+        <v>25.3966127085</v>
       </c>
       <c r="Q54">
-        <v>28.466091714</v>
+        <v>28.3966127085</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1371087014153782</v>
+        <v>0.1388548377288151</v>
       </c>
       <c r="T54">
-        <v>1.672350932714089</v>
+        <v>1.704332032512429</v>
       </c>
       <c r="U54">
         <v>0.0535</v>
@@ -5872,7 +5872,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>8.04864051287462</v>
+        <v>7.896779371122268</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5880,22 +5880,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.08822932373254308</v>
+        <v>0.08811227078570461</v>
       </c>
       <c r="C55">
-        <v>80.32338409385781</v>
+        <v>78.81772585114841</v>
       </c>
       <c r="D55">
-        <v>139.9982840938578</v>
+        <v>140.0959258511484</v>
       </c>
       <c r="E55">
-        <v>83.8449</v>
+        <v>85.4482</v>
       </c>
       <c r="F55">
-        <v>84.97489999999999</v>
+        <v>86.5782</v>
       </c>
       <c r="G55">
         <v>25.3</v>
@@ -5916,28 +5916,28 @@
         <v>35.9</v>
       </c>
       <c r="M55">
-        <v>4.546157149999999</v>
+        <v>4.631933699999999</v>
       </c>
       <c r="N55">
-        <v>31.35384285</v>
+        <v>31.2680663</v>
       </c>
       <c r="O55">
-        <v>5.9572301415</v>
+        <v>5.940932597000001</v>
       </c>
       <c r="P55">
-        <v>25.3966127085</v>
+        <v>25.327133703</v>
       </c>
       <c r="Q55">
-        <v>28.3966127085</v>
+        <v>28.327133703</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1388548377288151</v>
+        <v>0.1406768930124013</v>
       </c>
       <c r="T55">
-        <v>1.704332032512429</v>
+        <v>1.737703614910697</v>
       </c>
       <c r="U55">
         <v>0.0535</v>
@@ -5954,7 +5954,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>7.896779371122268</v>
+        <v>7.750542716101486</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5962,22 +5962,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.08811227078570461</v>
+        <v>0.08835161783886614</v>
       </c>
       <c r="C56">
-        <v>78.81772585114841</v>
+        <v>77.01491560949623</v>
       </c>
       <c r="D56">
-        <v>140.0959258511484</v>
+        <v>139.8964156094962</v>
       </c>
       <c r="E56">
-        <v>85.4482</v>
+        <v>87.0515</v>
       </c>
       <c r="F56">
-        <v>86.5782</v>
+        <v>88.1815</v>
       </c>
       <c r="G56">
         <v>25.3</v>
@@ -5998,45 +5998,45 @@
         <v>35.9</v>
       </c>
       <c r="M56">
-        <v>4.631933699999999</v>
+        <v>4.78825545</v>
       </c>
       <c r="N56">
-        <v>31.2680663</v>
+        <v>31.11174455</v>
       </c>
       <c r="O56">
-        <v>5.940932597000001</v>
+        <v>5.911231464499999</v>
       </c>
       <c r="P56">
-        <v>25.327133703</v>
+        <v>25.2005130855</v>
       </c>
       <c r="Q56">
-        <v>28.327133703</v>
+        <v>28.2005130855</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1406768930124013</v>
+        <v>0.1425799285308137</v>
       </c>
       <c r="T56">
-        <v>1.737703614910697</v>
+        <v>1.772558378748888</v>
       </c>
       <c r="U56">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V56">
         <v>0.19</v>
       </c>
       <c r="W56">
-        <v>0.04333500000000001</v>
+        <v>0.043983</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y56">
-        <v>7.750542716101486</v>
+        <v>7.497511437072555</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6044,22 +6044,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.08835161783886614</v>
+        <v>0.08824104489202769</v>
       </c>
       <c r="C57">
-        <v>77.01491560949623</v>
+        <v>75.50371418057709</v>
       </c>
       <c r="D57">
-        <v>139.8964156094962</v>
+        <v>139.9885141805771</v>
       </c>
       <c r="E57">
-        <v>87.0515</v>
+        <v>88.65480000000001</v>
       </c>
       <c r="F57">
-        <v>88.1815</v>
+        <v>89.7848</v>
       </c>
       <c r="G57">
         <v>25.3</v>
@@ -6080,28 +6080,28 @@
         <v>35.9</v>
       </c>
       <c r="M57">
-        <v>4.78825545</v>
+        <v>4.87531464</v>
       </c>
       <c r="N57">
-        <v>31.11174455</v>
+        <v>31.02468536</v>
       </c>
       <c r="O57">
-        <v>5.911231464499999</v>
+        <v>5.8946902184</v>
       </c>
       <c r="P57">
-        <v>25.2005130855</v>
+        <v>25.1299951416</v>
       </c>
       <c r="Q57">
-        <v>28.2005130855</v>
+        <v>28.1299951416</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1425799285308137</v>
+        <v>0.1445694656636993</v>
       </c>
       <c r="T57">
-        <v>1.772558378748888</v>
+        <v>1.808997450034269</v>
       </c>
       <c r="U57">
         <v>0.0543</v>
@@ -6118,7 +6118,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>7.497511437072555</v>
+        <v>7.363627304267689</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6126,22 +6126,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08824104489202769</v>
+        <v>0.08813047194518921</v>
       </c>
       <c r="C58">
-        <v>75.50371418057709</v>
+        <v>73.99263409478924</v>
       </c>
       <c r="D58">
-        <v>139.9885141805771</v>
+        <v>140.0807340947892</v>
       </c>
       <c r="E58">
-        <v>88.65480000000001</v>
+        <v>90.2581</v>
       </c>
       <c r="F58">
-        <v>89.7848</v>
+        <v>91.38809999999999</v>
       </c>
       <c r="G58">
         <v>25.3</v>
@@ -6162,28 +6162,28 @@
         <v>35.9</v>
       </c>
       <c r="M58">
-        <v>4.87531464</v>
+        <v>4.96237383</v>
       </c>
       <c r="N58">
-        <v>31.02468536</v>
+        <v>30.93762617</v>
       </c>
       <c r="O58">
-        <v>5.8946902184</v>
+        <v>5.8781489723</v>
       </c>
       <c r="P58">
-        <v>25.1299951416</v>
+        <v>25.0594771977</v>
       </c>
       <c r="Q58">
-        <v>28.1299951416</v>
+        <v>28.0594771977</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1445694656636993</v>
+        <v>0.1466515394074168</v>
       </c>
       <c r="T58">
-        <v>1.808997450034269</v>
+        <v>1.847131361844552</v>
       </c>
       <c r="U58">
         <v>0.0543</v>
@@ -6200,7 +6200,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>7.363627304267689</v>
+        <v>7.234440860333168</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6208,22 +6208,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08813047194518921</v>
+        <v>0.08801989899835075</v>
       </c>
       <c r="C59">
-        <v>73.99263409478924</v>
+        <v>72.48167559210148</v>
       </c>
       <c r="D59">
-        <v>140.0807340947892</v>
+        <v>140.1730755921015</v>
       </c>
       <c r="E59">
-        <v>90.2581</v>
+        <v>91.8614</v>
       </c>
       <c r="F59">
-        <v>91.38809999999999</v>
+        <v>92.9914</v>
       </c>
       <c r="G59">
         <v>25.3</v>
@@ -6244,28 +6244,28 @@
         <v>35.9</v>
       </c>
       <c r="M59">
-        <v>4.96237383</v>
+        <v>5.04943302</v>
       </c>
       <c r="N59">
-        <v>30.93762617</v>
+        <v>30.85056698</v>
       </c>
       <c r="O59">
-        <v>5.8781489723</v>
+        <v>5.861607726199999</v>
       </c>
       <c r="P59">
-        <v>25.0594771977</v>
+        <v>24.9889592538</v>
       </c>
       <c r="Q59">
-        <v>28.0594771977</v>
+        <v>27.9889592538</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1466515394074168</v>
+        <v>0.1488327595198828</v>
       </c>
       <c r="T59">
-        <v>1.847131361844552</v>
+        <v>1.88708117421723</v>
       </c>
       <c r="U59">
         <v>0.0543</v>
@@ -6282,7 +6282,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>7.234440860333168</v>
+        <v>7.109709121361906</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6290,22 +6290,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.08801989899835075</v>
+        <v>0.08790932605151229</v>
       </c>
       <c r="C60">
-        <v>72.4816755921015</v>
+        <v>70.97083891311595</v>
       </c>
       <c r="D60">
-        <v>140.1730755921015</v>
+        <v>140.2655389131159</v>
       </c>
       <c r="E60">
-        <v>91.86139999999999</v>
+        <v>93.46469999999999</v>
       </c>
       <c r="F60">
-        <v>92.99139999999998</v>
+        <v>94.59469999999999</v>
       </c>
       <c r="G60">
         <v>25.3</v>
@@ -6326,28 +6326,28 @@
         <v>35.9</v>
       </c>
       <c r="M60">
-        <v>5.049433019999999</v>
+        <v>5.136492209999999</v>
       </c>
       <c r="N60">
-        <v>30.85056698</v>
+        <v>30.76350779</v>
       </c>
       <c r="O60">
-        <v>5.8616077262</v>
+        <v>5.8450664801</v>
       </c>
       <c r="P60">
-        <v>24.9889592538</v>
+        <v>24.9184413099</v>
       </c>
       <c r="Q60">
-        <v>27.9889592538</v>
+        <v>27.9184413099</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1488327595198827</v>
+        <v>0.1511203806134446</v>
       </c>
       <c r="T60">
-        <v>1.887081174217229</v>
+        <v>1.928979757925159</v>
       </c>
       <c r="U60">
         <v>0.0543</v>
@@ -6364,7 +6364,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>7.109709121361908</v>
+        <v>6.989205576932044</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6372,22 +6372,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.08790932605151229</v>
+        <v>0.08779875310467382</v>
       </c>
       <c r="C61">
-        <v>70.97083891311595</v>
+        <v>69.46012429906993</v>
       </c>
       <c r="D61">
-        <v>140.2655389131159</v>
+        <v>140.3581242990699</v>
       </c>
       <c r="E61">
-        <v>93.46469999999999</v>
+        <v>95.068</v>
       </c>
       <c r="F61">
-        <v>94.59469999999999</v>
+        <v>96.19799999999999</v>
       </c>
       <c r="G61">
         <v>25.3</v>
@@ -6408,28 +6408,28 @@
         <v>35.9</v>
       </c>
       <c r="M61">
-        <v>5.136492209999999</v>
+        <v>5.2235514</v>
       </c>
       <c r="N61">
-        <v>30.76350779</v>
+        <v>30.6764486</v>
       </c>
       <c r="O61">
-        <v>5.8450664801</v>
+        <v>5.828525234</v>
       </c>
       <c r="P61">
-        <v>24.9184413099</v>
+        <v>24.847923366</v>
       </c>
       <c r="Q61">
-        <v>27.9184413099</v>
+        <v>27.847923366</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1511203806134446</v>
+        <v>0.1535223827616845</v>
       </c>
       <c r="T61">
-        <v>1.928979757925159</v>
+        <v>1.972973270818485</v>
       </c>
       <c r="U61">
         <v>0.0543</v>
@@ -6446,7 +6446,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>6.989205576932044</v>
+        <v>6.87271881731651</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6454,22 +6454,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.08779875310467382</v>
+        <v>0.08768818015783536</v>
       </c>
       <c r="C62">
-        <v>69.46012429906993</v>
+        <v>67.9495319918381</v>
       </c>
       <c r="D62">
-        <v>140.3581242990699</v>
+        <v>140.4508319918381</v>
       </c>
       <c r="E62">
-        <v>95.068</v>
+        <v>96.67129999999999</v>
       </c>
       <c r="F62">
-        <v>96.19799999999999</v>
+        <v>97.80129999999998</v>
       </c>
       <c r="G62">
         <v>25.3</v>
@@ -6490,28 +6490,28 @@
         <v>35.9</v>
       </c>
       <c r="M62">
-        <v>5.2235514</v>
+        <v>5.31061059</v>
       </c>
       <c r="N62">
-        <v>30.6764486</v>
+        <v>30.58938941</v>
       </c>
       <c r="O62">
-        <v>5.828525234</v>
+        <v>5.8119839879</v>
       </c>
       <c r="P62">
-        <v>24.847923366</v>
+        <v>24.7774054221</v>
       </c>
       <c r="Q62">
-        <v>27.847923366</v>
+        <v>27.7774054221</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1535223827616845</v>
+        <v>0.1560475645072701</v>
       </c>
       <c r="T62">
-        <v>1.972973270818485</v>
+        <v>2.019222861296085</v>
       </c>
       <c r="U62">
         <v>0.0543</v>
@@ -6528,7 +6528,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>6.87271881731651</v>
+        <v>6.760051295721158</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6536,22 +6536,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.08768818015783536</v>
+        <v>0.08757760721099689</v>
       </c>
       <c r="C63">
-        <v>67.9495319918381</v>
+        <v>66.43906223393469</v>
       </c>
       <c r="D63">
-        <v>140.4508319918381</v>
+        <v>140.5436622339347</v>
       </c>
       <c r="E63">
-        <v>96.67129999999999</v>
+        <v>98.27459999999999</v>
       </c>
       <c r="F63">
-        <v>97.80129999999998</v>
+        <v>99.40459999999999</v>
       </c>
       <c r="G63">
         <v>25.3</v>
@@ -6572,28 +6572,28 @@
         <v>35.9</v>
       </c>
       <c r="M63">
-        <v>5.31061059</v>
+        <v>5.397669779999999</v>
       </c>
       <c r="N63">
-        <v>30.58938941</v>
+        <v>30.50233022</v>
       </c>
       <c r="O63">
-        <v>5.8119839879</v>
+        <v>5.7954427418</v>
       </c>
       <c r="P63">
-        <v>24.7774054221</v>
+        <v>24.7068874782</v>
       </c>
       <c r="Q63">
-        <v>27.7774054221</v>
+        <v>27.7068874782</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1560475645072701</v>
+        <v>0.158705650555255</v>
       </c>
       <c r="T63">
-        <v>2.019222861296085</v>
+        <v>2.06790664074619</v>
       </c>
       <c r="U63">
         <v>0.0543</v>
@@ -6610,7 +6610,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>6.760051295721158</v>
+        <v>6.6510182103063</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6618,22 +6618,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.08757760721099689</v>
+        <v>0.08746703426415843</v>
       </c>
       <c r="C64">
-        <v>66.43906223393469</v>
+        <v>64.92871526851532</v>
       </c>
       <c r="D64">
-        <v>140.5436622339347</v>
+        <v>140.6366152685153</v>
       </c>
       <c r="E64">
-        <v>98.27459999999999</v>
+        <v>99.8779</v>
       </c>
       <c r="F64">
-        <v>99.40459999999999</v>
+        <v>101.0079</v>
       </c>
       <c r="G64">
         <v>25.3</v>
@@ -6654,28 +6654,28 @@
         <v>35.9</v>
       </c>
       <c r="M64">
-        <v>5.397669779999999</v>
+        <v>5.48472897</v>
       </c>
       <c r="N64">
-        <v>30.50233022</v>
+        <v>30.41527103</v>
       </c>
       <c r="O64">
-        <v>5.7954427418</v>
+        <v>5.7789014957</v>
       </c>
       <c r="P64">
-        <v>24.7068874782</v>
+        <v>24.6363695343</v>
       </c>
       <c r="Q64">
-        <v>27.7068874782</v>
+        <v>27.6363695343</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.158705650555255</v>
+        <v>0.1615074169301579</v>
       </c>
       <c r="T64">
-        <v>2.06790664074619</v>
+        <v>2.119221975842246</v>
       </c>
       <c r="U64">
         <v>0.0543</v>
@@ -6692,7 +6692,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>6.6510182103063</v>
+        <v>6.54544649268239</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6700,22 +6700,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.08746703426415843</v>
+        <v>0.08735646131731997</v>
       </c>
       <c r="C65">
-        <v>64.92871526851532</v>
+        <v>63.41849133937944</v>
       </c>
       <c r="D65">
-        <v>140.6366152685153</v>
+        <v>140.7296913393794</v>
       </c>
       <c r="E65">
-        <v>99.8779</v>
+        <v>101.4812</v>
       </c>
       <c r="F65">
-        <v>101.0079</v>
+        <v>102.6112</v>
       </c>
       <c r="G65">
         <v>25.3</v>
@@ -6736,28 +6736,28 @@
         <v>35.9</v>
       </c>
       <c r="M65">
-        <v>5.48472897</v>
+        <v>5.57178816</v>
       </c>
       <c r="N65">
-        <v>30.41527103</v>
+        <v>30.32821184</v>
       </c>
       <c r="O65">
-        <v>5.7789014957</v>
+        <v>5.762360249599999</v>
       </c>
       <c r="P65">
-        <v>24.6363695343</v>
+        <v>24.5658515904</v>
       </c>
       <c r="Q65">
-        <v>27.6363695343</v>
+        <v>27.5658515904</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1615074169301579</v>
+        <v>0.1644648369925555</v>
       </c>
       <c r="T65">
-        <v>2.119221975842246</v>
+        <v>2.173388162888084</v>
       </c>
       <c r="U65">
         <v>0.0543</v>
@@ -6774,7 +6774,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>6.54544649268239</v>
+        <v>6.443173891234228</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6782,22 +6782,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.08735646131731997</v>
+        <v>0.0872458883704815</v>
       </c>
       <c r="C66">
-        <v>63.41849133937944</v>
+        <v>61.90839069097234</v>
       </c>
       <c r="D66">
-        <v>140.7296913393794</v>
+        <v>140.8228906909723</v>
       </c>
       <c r="E66">
-        <v>101.4812</v>
+        <v>103.0845</v>
       </c>
       <c r="F66">
-        <v>102.6112</v>
+        <v>104.2145</v>
       </c>
       <c r="G66">
         <v>25.3</v>
@@ -6818,28 +6818,28 @@
         <v>35.9</v>
       </c>
       <c r="M66">
-        <v>5.57178816</v>
+        <v>5.658847349999999</v>
       </c>
       <c r="N66">
-        <v>30.32821184</v>
+        <v>30.24115265</v>
       </c>
       <c r="O66">
-        <v>5.762360249599999</v>
+        <v>5.7458190035</v>
       </c>
       <c r="P66">
-        <v>24.5658515904</v>
+        <v>24.4953336465</v>
       </c>
       <c r="Q66">
-        <v>27.5658515904</v>
+        <v>27.4953336465</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1644648369925555</v>
+        <v>0.16759125248709</v>
       </c>
       <c r="T66">
-        <v>2.173388162888084</v>
+        <v>2.230649560622254</v>
       </c>
       <c r="U66">
         <v>0.0543</v>
@@ -6856,7 +6856,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>6.443173891234228</v>
+        <v>6.344048139061394</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6864,22 +6864,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.0872458883704815</v>
+        <v>0.08713531542364303</v>
       </c>
       <c r="C67">
-        <v>61.90839069097234</v>
+        <v>60.39841356838723</v>
       </c>
       <c r="D67">
-        <v>140.8228906909723</v>
+        <v>140.9162135683872</v>
       </c>
       <c r="E67">
-        <v>103.0845</v>
+        <v>104.6878</v>
       </c>
       <c r="F67">
-        <v>104.2145</v>
+        <v>105.8178</v>
       </c>
       <c r="G67">
         <v>25.3</v>
@@ -6900,28 +6900,28 @@
         <v>35.9</v>
       </c>
       <c r="M67">
-        <v>5.658847349999999</v>
+        <v>5.74590654</v>
       </c>
       <c r="N67">
-        <v>30.24115265</v>
+        <v>30.15409346</v>
       </c>
       <c r="O67">
-        <v>5.7458190035</v>
+        <v>5.7292777574</v>
       </c>
       <c r="P67">
-        <v>24.4953336465</v>
+        <v>24.4248157026</v>
       </c>
       <c r="Q67">
-        <v>27.4953336465</v>
+        <v>27.4248157026</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.16759125248709</v>
+        <v>0.1709015747754207</v>
       </c>
       <c r="T67">
-        <v>2.230649560622254</v>
+        <v>2.2912792758702</v>
       </c>
       <c r="U67">
         <v>0.0543</v>
@@ -6938,7 +6938,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>6.344048139061394</v>
+        <v>6.247926197560464</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6946,22 +6946,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.08713531542364303</v>
+        <v>0.08702474247680456</v>
       </c>
       <c r="C68">
-        <v>60.39841356838723</v>
+        <v>58.88856021736748</v>
       </c>
       <c r="D68">
-        <v>140.9162135683872</v>
+        <v>141.0096602173675</v>
       </c>
       <c r="E68">
-        <v>104.6878</v>
+        <v>106.2911</v>
       </c>
       <c r="F68">
-        <v>105.8178</v>
+        <v>107.4211</v>
       </c>
       <c r="G68">
         <v>25.3</v>
@@ -6982,28 +6982,28 @@
         <v>35.9</v>
       </c>
       <c r="M68">
-        <v>5.74590654</v>
+        <v>5.83296573</v>
       </c>
       <c r="N68">
-        <v>30.15409346</v>
+        <v>30.06703427</v>
       </c>
       <c r="O68">
-        <v>5.7292777574</v>
+        <v>5.7127365113</v>
       </c>
       <c r="P68">
-        <v>24.4248157026</v>
+        <v>24.3542977587</v>
       </c>
       <c r="Q68">
-        <v>27.4248157026</v>
+        <v>27.3542977587</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1709015747754207</v>
+        <v>0.1744125226569835</v>
       </c>
       <c r="T68">
-        <v>2.2912792758702</v>
+        <v>2.35558351931499</v>
       </c>
       <c r="U68">
         <v>0.0543</v>
@@ -7020,7 +7020,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>6.247926197560464</v>
+        <v>6.154673567746129</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7028,22 +7028,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.08702474247680456</v>
+        <v>0.0874649695299661</v>
       </c>
       <c r="C69">
-        <v>58.88856021736748</v>
+        <v>56.91395215462286</v>
       </c>
       <c r="D69">
-        <v>141.0096602173675</v>
+        <v>140.6383521546229</v>
       </c>
       <c r="E69">
-        <v>106.2911</v>
+        <v>107.8944</v>
       </c>
       <c r="F69">
-        <v>107.4211</v>
+        <v>109.0244</v>
       </c>
       <c r="G69">
         <v>25.3</v>
@@ -7064,45 +7064,45 @@
         <v>35.9</v>
       </c>
       <c r="M69">
-        <v>5.83296573</v>
+        <v>6.02904932</v>
       </c>
       <c r="N69">
-        <v>30.06703427</v>
+        <v>29.87095068</v>
       </c>
       <c r="O69">
-        <v>5.7127365113</v>
+        <v>5.6754806292</v>
       </c>
       <c r="P69">
-        <v>24.3542977587</v>
+        <v>24.1954700508</v>
       </c>
       <c r="Q69">
-        <v>27.3542977587</v>
+        <v>27.1954700508</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1744125226569835</v>
+        <v>0.1781429047811441</v>
       </c>
       <c r="T69">
-        <v>2.35558351931499</v>
+        <v>2.42390677797508</v>
       </c>
       <c r="U69">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V69">
         <v>0.19</v>
       </c>
       <c r="W69">
-        <v>0.043983</v>
+        <v>0.04479300000000001</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y69">
-        <v>6.154673567746129</v>
+        <v>5.954504283272309</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7110,22 +7110,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.0874649695299661</v>
+        <v>0.08736249658312764</v>
       </c>
       <c r="C70">
-        <v>56.91395215462286</v>
+        <v>55.39690790523662</v>
       </c>
       <c r="D70">
-        <v>140.6383521546229</v>
+        <v>140.7246079052366</v>
       </c>
       <c r="E70">
-        <v>107.8944</v>
+        <v>109.4977</v>
       </c>
       <c r="F70">
-        <v>109.0244</v>
+        <v>110.6277</v>
       </c>
       <c r="G70">
         <v>25.3</v>
@@ -7146,28 +7146,28 @@
         <v>35.9</v>
       </c>
       <c r="M70">
-        <v>6.02904932</v>
+        <v>6.11771181</v>
       </c>
       <c r="N70">
-        <v>29.87095068</v>
+        <v>29.78228819</v>
       </c>
       <c r="O70">
-        <v>5.6754806292</v>
+        <v>5.6586347561</v>
       </c>
       <c r="P70">
-        <v>24.1954700508</v>
+        <v>24.1236534339</v>
       </c>
       <c r="Q70">
-        <v>27.1954700508</v>
+        <v>27.1236534339</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1781429047811441</v>
+        <v>0.1821139567197666</v>
       </c>
       <c r="T70">
-        <v>2.42390677797508</v>
+        <v>2.49663798880679</v>
       </c>
       <c r="U70">
         <v>0.0553</v>
@@ -7184,7 +7184,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>5.954504283272309</v>
+        <v>5.868207119746622</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7192,22 +7192,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.08736249658312764</v>
+        <v>0.08726002363628918</v>
       </c>
       <c r="C71">
-        <v>55.39690790523662</v>
+        <v>53.87996952484423</v>
       </c>
       <c r="D71">
-        <v>140.7246079052366</v>
+        <v>140.8109695248442</v>
       </c>
       <c r="E71">
-        <v>109.4977</v>
+        <v>111.101</v>
       </c>
       <c r="F71">
-        <v>110.6277</v>
+        <v>112.231</v>
       </c>
       <c r="G71">
         <v>25.3</v>
@@ -7228,28 +7228,28 @@
         <v>35.9</v>
       </c>
       <c r="M71">
-        <v>6.11771181</v>
+        <v>6.2063743</v>
       </c>
       <c r="N71">
-        <v>29.78228819</v>
+        <v>29.6936257</v>
       </c>
       <c r="O71">
-        <v>5.6586347561</v>
+        <v>5.641788882999999</v>
       </c>
       <c r="P71">
-        <v>24.1236534339</v>
+        <v>24.051836817</v>
       </c>
       <c r="Q71">
-        <v>27.1236534339</v>
+        <v>27.051836817</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1821139567197666</v>
+        <v>0.1863497454542972</v>
       </c>
       <c r="T71">
-        <v>2.49663798880679</v>
+        <v>2.574217947027279</v>
       </c>
       <c r="U71">
         <v>0.0553</v>
@@ -7266,7 +7266,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>5.868207119746622</v>
+        <v>5.784375589464528</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7274,22 +7274,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.08726002363628918</v>
+        <v>0.08715755068945072</v>
       </c>
       <c r="C72">
-        <v>53.87996952484423</v>
+        <v>52.36313720847831</v>
       </c>
       <c r="D72">
-        <v>140.8109695248442</v>
+        <v>140.8974372084783</v>
       </c>
       <c r="E72">
-        <v>111.101</v>
+        <v>112.7043</v>
       </c>
       <c r="F72">
-        <v>112.231</v>
+        <v>113.8343</v>
       </c>
       <c r="G72">
         <v>25.3</v>
@@ -7310,28 +7310,28 @@
         <v>35.9</v>
       </c>
       <c r="M72">
-        <v>6.2063743</v>
+        <v>6.29503679</v>
       </c>
       <c r="N72">
-        <v>29.6936257</v>
+        <v>29.60496321</v>
       </c>
       <c r="O72">
-        <v>5.641788882999999</v>
+        <v>5.6249430099</v>
       </c>
       <c r="P72">
-        <v>24.051836817</v>
+        <v>23.9800202001</v>
       </c>
       <c r="Q72">
-        <v>27.051836817</v>
+        <v>26.9800202001</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1863497454542972</v>
+        <v>0.1908776575498301</v>
       </c>
       <c r="T72">
-        <v>2.574217947027279</v>
+        <v>2.65714824719401</v>
       </c>
       <c r="U72">
         <v>0.0553</v>
@@ -7348,7 +7348,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>5.784375589464528</v>
+        <v>5.702905510739676</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7356,22 +7356,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.08715755068945071</v>
+        <v>0.08705507774261226</v>
       </c>
       <c r="C73">
-        <v>52.36313720847835</v>
+        <v>50.84641115165097</v>
       </c>
       <c r="D73">
-        <v>140.8974372084783</v>
+        <v>140.9840111516509</v>
       </c>
       <c r="E73">
-        <v>112.7043</v>
+        <v>114.3076</v>
       </c>
       <c r="F73">
-        <v>113.8343</v>
+        <v>115.4376</v>
       </c>
       <c r="G73">
         <v>25.3</v>
@@ -7392,28 +7392,28 @@
         <v>35.9</v>
       </c>
       <c r="M73">
-        <v>6.295036789999999</v>
+        <v>6.383699279999999</v>
       </c>
       <c r="N73">
-        <v>29.60496321</v>
+        <v>29.51630072</v>
       </c>
       <c r="O73">
-        <v>5.6249430099</v>
+        <v>5.608097136800001</v>
       </c>
       <c r="P73">
-        <v>23.9800202001</v>
+        <v>23.9082035832</v>
       </c>
       <c r="Q73">
-        <v>26.9800202001</v>
+        <v>26.9082035832</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.19087765754983</v>
+        <v>0.1957289919379009</v>
       </c>
       <c r="T73">
-        <v>2.657148247194009</v>
+        <v>2.746002140229791</v>
       </c>
       <c r="U73">
         <v>0.0553</v>
@@ -7430,7 +7430,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>5.702905510739677</v>
+        <v>5.623698489757181</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7438,22 +7438,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.08705507774261226</v>
+        <v>0.08695260479577378</v>
       </c>
       <c r="C74">
-        <v>50.84641115165097</v>
+        <v>49.32979155035501</v>
       </c>
       <c r="D74">
-        <v>140.9840111516509</v>
+        <v>141.070691550355</v>
       </c>
       <c r="E74">
-        <v>114.3076</v>
+        <v>115.9109</v>
       </c>
       <c r="F74">
-        <v>115.4376</v>
+        <v>117.0409</v>
       </c>
       <c r="G74">
         <v>25.3</v>
@@ -7474,28 +7474,28 @@
         <v>35.9</v>
       </c>
       <c r="M74">
-        <v>6.383699279999999</v>
+        <v>6.472361769999999</v>
       </c>
       <c r="N74">
-        <v>29.51630072</v>
+        <v>29.42763823</v>
       </c>
       <c r="O74">
-        <v>5.608097136800001</v>
+        <v>5.5912512637</v>
       </c>
       <c r="P74">
-        <v>23.9082035832</v>
+        <v>23.8363869663</v>
       </c>
       <c r="Q74">
-        <v>26.9082035832</v>
+        <v>26.8363869663</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1957289919379009</v>
+        <v>0.2009396844287918</v>
       </c>
       <c r="T74">
-        <v>2.746002140229791</v>
+        <v>2.841437803120076</v>
       </c>
       <c r="U74">
         <v>0.0553</v>
@@ -7512,7 +7512,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>5.623698489757181</v>
+        <v>5.546661524144069</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7520,22 +7520,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.08695260479577378</v>
+        <v>0.08685013184893531</v>
       </c>
       <c r="C75">
-        <v>49.32979155035501</v>
+        <v>47.81327860106555</v>
       </c>
       <c r="D75">
-        <v>141.070691550355</v>
+        <v>141.1574786010655</v>
       </c>
       <c r="E75">
-        <v>115.9109</v>
+        <v>117.5142</v>
       </c>
       <c r="F75">
-        <v>117.0409</v>
+        <v>118.6442</v>
       </c>
       <c r="G75">
         <v>25.3</v>
@@ -7556,28 +7556,28 @@
         <v>35.9</v>
       </c>
       <c r="M75">
-        <v>6.472361769999999</v>
+        <v>6.561024259999999</v>
       </c>
       <c r="N75">
-        <v>29.42763823</v>
+        <v>29.33897574</v>
       </c>
       <c r="O75">
-        <v>5.5912512637</v>
+        <v>5.5744053906</v>
       </c>
       <c r="P75">
-        <v>23.8363869663</v>
+        <v>23.7645703494</v>
       </c>
       <c r="Q75">
-        <v>26.8363869663</v>
+        <v>26.7645703494</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2009396844287918</v>
+        <v>0.206551199418982</v>
       </c>
       <c r="T75">
-        <v>2.841437803120076</v>
+        <v>2.944214670848075</v>
       </c>
       <c r="U75">
         <v>0.0553</v>
@@ -7594,7 +7594,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>5.546661524144069</v>
+        <v>5.471706638682662</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7602,22 +7602,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.08685013184893531</v>
+        <v>0.08674765890209685</v>
       </c>
       <c r="C76">
-        <v>47.81327860106555</v>
+        <v>46.29687250074154</v>
       </c>
       <c r="D76">
-        <v>141.1574786010655</v>
+        <v>141.2443725007415</v>
       </c>
       <c r="E76">
-        <v>117.5142</v>
+        <v>119.1175</v>
       </c>
       <c r="F76">
-        <v>118.6442</v>
+        <v>120.2475</v>
       </c>
       <c r="G76">
         <v>25.3</v>
@@ -7638,28 +7638,28 @@
         <v>35.9</v>
       </c>
       <c r="M76">
-        <v>6.561024259999999</v>
+        <v>6.64968675</v>
       </c>
       <c r="N76">
-        <v>29.33897574</v>
+        <v>29.25031325</v>
       </c>
       <c r="O76">
-        <v>5.5744053906</v>
+        <v>5.5575595175</v>
       </c>
       <c r="P76">
-        <v>23.7645703494</v>
+        <v>23.6927537325</v>
       </c>
       <c r="Q76">
-        <v>26.7645703494</v>
+        <v>26.6927537325</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.206551199418982</v>
+        <v>0.2126116356083874</v>
       </c>
       <c r="T76">
-        <v>2.944214670848075</v>
+        <v>3.055213687994314</v>
       </c>
       <c r="U76">
         <v>0.0553</v>
@@ -7676,7 +7676,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>5.471706638682662</v>
+        <v>5.398750550166893</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7684,22 +7684,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.08674765890209685</v>
+        <v>0.08664518595525839</v>
       </c>
       <c r="C77">
-        <v>46.29687250074154</v>
+        <v>44.78057344682722</v>
       </c>
       <c r="D77">
-        <v>141.2443725007415</v>
+        <v>141.3313734468272</v>
       </c>
       <c r="E77">
-        <v>119.1175</v>
+        <v>120.7208</v>
       </c>
       <c r="F77">
-        <v>120.2475</v>
+        <v>121.8508</v>
       </c>
       <c r="G77">
         <v>25.3</v>
@@ -7720,28 +7720,28 @@
         <v>35.9</v>
       </c>
       <c r="M77">
-        <v>6.64968675</v>
+        <v>6.73834924</v>
       </c>
       <c r="N77">
-        <v>29.25031325</v>
+        <v>29.16165076</v>
       </c>
       <c r="O77">
-        <v>5.5575595175</v>
+        <v>5.5407136444</v>
       </c>
       <c r="P77">
-        <v>23.6927537325</v>
+        <v>23.6209371156</v>
       </c>
       <c r="Q77">
-        <v>26.6927537325</v>
+        <v>26.6209371156</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2126116356083874</v>
+        <v>0.2191771081469099</v>
       </c>
       <c r="T77">
-        <v>3.055213687994314</v>
+        <v>3.175462623236073</v>
       </c>
       <c r="U77">
         <v>0.0553</v>
@@ -7758,7 +7758,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>5.398750550166893</v>
+        <v>5.327714358717329</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7766,22 +7766,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.08664518595525839</v>
+        <v>0.08654271300841992</v>
       </c>
       <c r="C78">
-        <v>44.78057344682722</v>
+        <v>43.26438163725352</v>
       </c>
       <c r="D78">
-        <v>141.3313734468272</v>
+        <v>141.4184816372535</v>
       </c>
       <c r="E78">
-        <v>120.7208</v>
+        <v>122.3241</v>
       </c>
       <c r="F78">
-        <v>121.8508</v>
+        <v>123.4541</v>
       </c>
       <c r="G78">
         <v>25.3</v>
@@ -7802,28 +7802,28 @@
         <v>35.9</v>
       </c>
       <c r="M78">
-        <v>6.73834924</v>
+        <v>6.82701173</v>
       </c>
       <c r="N78">
-        <v>29.16165076</v>
+        <v>29.07298827</v>
       </c>
       <c r="O78">
-        <v>5.5407136444</v>
+        <v>5.5238677713</v>
       </c>
       <c r="P78">
-        <v>23.6209371156</v>
+        <v>23.5491204987</v>
       </c>
       <c r="Q78">
-        <v>26.6209371156</v>
+        <v>26.5491204987</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2191771081469099</v>
+        <v>0.2263134913409562</v>
       </c>
       <c r="T78">
-        <v>3.175462623236073</v>
+        <v>3.306167987629288</v>
       </c>
       <c r="U78">
         <v>0.0553</v>
@@ -7840,7 +7840,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>5.327714358717329</v>
+        <v>5.258523263149572</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7848,22 +7848,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.08654271300841992</v>
+        <v>0.08644024006158146</v>
       </c>
       <c r="C79">
-        <v>43.26438163725352</v>
+        <v>41.74829727043975</v>
       </c>
       <c r="D79">
-        <v>141.4184816372535</v>
+        <v>141.5056972704397</v>
       </c>
       <c r="E79">
-        <v>122.3241</v>
+        <v>123.9274</v>
       </c>
       <c r="F79">
-        <v>123.4541</v>
+        <v>125.0574</v>
       </c>
       <c r="G79">
         <v>25.3</v>
@@ -7884,28 +7884,28 @@
         <v>35.9</v>
       </c>
       <c r="M79">
-        <v>6.82701173</v>
+        <v>6.91567422</v>
       </c>
       <c r="N79">
-        <v>29.07298827</v>
+        <v>28.98432578</v>
       </c>
       <c r="O79">
-        <v>5.5238677713</v>
+        <v>5.5070218982</v>
       </c>
       <c r="P79">
-        <v>23.5491204987</v>
+        <v>23.4773038818</v>
       </c>
       <c r="Q79">
-        <v>26.5491204987</v>
+        <v>26.4773038818</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2263134913409562</v>
+        <v>0.2340986366435521</v>
       </c>
       <c r="T79">
-        <v>3.306167987629288</v>
+        <v>3.448755657876434</v>
       </c>
       <c r="U79">
         <v>0.0553</v>
@@ -7922,7 +7922,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>5.258523263149572</v>
+        <v>5.191106298237397</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7930,22 +7930,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.08644024006158146</v>
+        <v>0.08633776711474297</v>
       </c>
       <c r="C80">
-        <v>41.74829727043975</v>
+        <v>40.23232054529493</v>
       </c>
       <c r="D80">
-        <v>141.5056972704397</v>
+        <v>141.5930205452949</v>
       </c>
       <c r="E80">
-        <v>123.9274</v>
+        <v>125.5307</v>
       </c>
       <c r="F80">
-        <v>125.0574</v>
+        <v>126.6607</v>
       </c>
       <c r="G80">
         <v>25.3</v>
@@ -7966,28 +7966,28 @@
         <v>35.9</v>
       </c>
       <c r="M80">
-        <v>6.91567422</v>
+        <v>7.00433671</v>
       </c>
       <c r="N80">
-        <v>28.98432578</v>
+        <v>28.89566329</v>
       </c>
       <c r="O80">
-        <v>5.5070218982</v>
+        <v>5.490176025099999</v>
       </c>
       <c r="P80">
-        <v>23.4773038818</v>
+        <v>23.4054872649</v>
       </c>
       <c r="Q80">
-        <v>26.4773038818</v>
+        <v>26.4054872649</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2340986366435521</v>
+        <v>0.242625224355919</v>
       </c>
       <c r="T80">
-        <v>3.448755657876434</v>
+        <v>3.604923106242354</v>
       </c>
       <c r="U80">
         <v>0.0553</v>
@@ -8004,7 +8004,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>5.191106298237397</v>
+        <v>5.125396091930595</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8012,22 +8012,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.08633776711474297</v>
+        <v>0.08623529416790451</v>
       </c>
       <c r="C81">
-        <v>40.23232054529493</v>
+        <v>38.71645166121931</v>
       </c>
       <c r="D81">
-        <v>141.5930205452949</v>
+        <v>141.6804516612193</v>
       </c>
       <c r="E81">
-        <v>125.5307</v>
+        <v>127.134</v>
       </c>
       <c r="F81">
-        <v>126.6607</v>
+        <v>128.264</v>
       </c>
       <c r="G81">
         <v>25.3</v>
@@ -8048,28 +8048,28 @@
         <v>35.9</v>
       </c>
       <c r="M81">
-        <v>7.00433671</v>
+        <v>7.0929992</v>
       </c>
       <c r="N81">
-        <v>28.89566329</v>
+        <v>28.8070008</v>
       </c>
       <c r="O81">
-        <v>5.490176025099999</v>
+        <v>5.473330152</v>
       </c>
       <c r="P81">
-        <v>23.4054872649</v>
+        <v>23.333670648</v>
       </c>
       <c r="Q81">
-        <v>26.4054872649</v>
+        <v>26.333670648</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.242625224355919</v>
+        <v>0.2520044708395226</v>
       </c>
       <c r="T81">
-        <v>3.604923106242354</v>
+        <v>3.776707299444867</v>
       </c>
       <c r="U81">
         <v>0.0553</v>
@@ -8086,7 +8086,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>5.125396091930595</v>
+        <v>5.061328640781462</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8094,22 +8094,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.08623529416790451</v>
+        <v>0.08613282122106605</v>
       </c>
       <c r="C82">
-        <v>38.71645166121931</v>
+        <v>37.20069081810604</v>
       </c>
       <c r="D82">
-        <v>141.6804516612193</v>
+        <v>141.767990818106</v>
       </c>
       <c r="E82">
-        <v>127.134</v>
+        <v>128.7373</v>
       </c>
       <c r="F82">
-        <v>128.264</v>
+        <v>129.8673</v>
       </c>
       <c r="G82">
         <v>25.3</v>
@@ -8130,28 +8130,28 @@
         <v>35.9</v>
       </c>
       <c r="M82">
-        <v>7.0929992</v>
+        <v>7.18166169</v>
       </c>
       <c r="N82">
-        <v>28.8070008</v>
+        <v>28.71833831</v>
       </c>
       <c r="O82">
-        <v>5.473330152</v>
+        <v>5.4564842789</v>
       </c>
       <c r="P82">
-        <v>23.333670648</v>
+        <v>23.2618540311</v>
       </c>
       <c r="Q82">
-        <v>26.333670648</v>
+        <v>26.2618540311</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2520044708395226</v>
+        <v>0.2623710064266635</v>
       </c>
       <c r="T82">
-        <v>3.776707299444867</v>
+        <v>3.966574039300276</v>
       </c>
       <c r="U82">
         <v>0.0553</v>
@@ -8168,7 +8168,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>5.061328640781462</v>
+        <v>4.998843102006383</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8176,22 +8176,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.08613282122106605</v>
+        <v>0.08603034827422758</v>
       </c>
       <c r="C83">
-        <v>37.20069081810604</v>
+        <v>35.68503821634266</v>
       </c>
       <c r="D83">
-        <v>141.767990818106</v>
+        <v>141.8556382163426</v>
       </c>
       <c r="E83">
-        <v>128.7373</v>
+        <v>130.3406</v>
       </c>
       <c r="F83">
-        <v>129.8673</v>
+        <v>131.4706</v>
       </c>
       <c r="G83">
         <v>25.3</v>
@@ -8212,28 +8212,28 @@
         <v>35.9</v>
       </c>
       <c r="M83">
-        <v>7.18166169</v>
+        <v>7.270324179999999</v>
       </c>
       <c r="N83">
-        <v>28.71833831</v>
+        <v>28.62967582</v>
       </c>
       <c r="O83">
-        <v>5.4564842789</v>
+        <v>5.4396384058</v>
       </c>
       <c r="P83">
-        <v>23.2618540311</v>
+        <v>23.1900374142</v>
       </c>
       <c r="Q83">
-        <v>26.2618540311</v>
+        <v>26.1900374142</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2623710064266635</v>
+        <v>0.2738893793012644</v>
       </c>
       <c r="T83">
-        <v>3.966574039300276</v>
+        <v>4.177537083584062</v>
       </c>
       <c r="U83">
         <v>0.0553</v>
@@ -8250,7 +8250,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>4.998843102006383</v>
+        <v>4.937881600762402</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8258,22 +8258,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.08603034827422758</v>
+        <v>0.08592787532738913</v>
       </c>
       <c r="C84">
-        <v>35.68503821634266</v>
+        <v>34.1694940568124</v>
       </c>
       <c r="D84">
-        <v>141.8556382163426</v>
+        <v>141.9433940568124</v>
       </c>
       <c r="E84">
-        <v>130.3406</v>
+        <v>131.9439</v>
       </c>
       <c r="F84">
-        <v>131.4706</v>
+        <v>133.0739</v>
       </c>
       <c r="G84">
         <v>25.3</v>
@@ -8294,28 +8294,28 @@
         <v>35.9</v>
       </c>
       <c r="M84">
-        <v>7.270324179999999</v>
+        <v>7.358986670000001</v>
       </c>
       <c r="N84">
-        <v>28.62967582</v>
+        <v>28.54101333</v>
       </c>
       <c r="O84">
-        <v>5.4396384058</v>
+        <v>5.4227925327</v>
       </c>
       <c r="P84">
-        <v>23.1900374142</v>
+        <v>23.1182207973</v>
       </c>
       <c r="Q84">
-        <v>26.1900374142</v>
+        <v>26.1182207973</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2738893793012644</v>
+        <v>0.2867628548669949</v>
       </c>
       <c r="T84">
-        <v>4.177537083584062</v>
+        <v>4.413319309548296</v>
       </c>
       <c r="U84">
         <v>0.0553</v>
@@ -8332,7 +8332,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>4.937881600762402</v>
+        <v>4.878389051355626</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8340,22 +8340,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.08592787532738913</v>
+        <v>0.08582540238055067</v>
       </c>
       <c r="C85">
-        <v>34.1694940568124</v>
+        <v>32.65405854089602</v>
       </c>
       <c r="D85">
-        <v>141.9433940568124</v>
+        <v>142.031258540896</v>
       </c>
       <c r="E85">
-        <v>131.9439</v>
+        <v>133.5472</v>
       </c>
       <c r="F85">
-        <v>133.0739</v>
+        <v>134.6772</v>
       </c>
       <c r="G85">
         <v>25.3</v>
@@ -8376,28 +8376,28 @@
         <v>35.9</v>
       </c>
       <c r="M85">
-        <v>7.358986670000001</v>
+        <v>7.44764916</v>
       </c>
       <c r="N85">
-        <v>28.54101333</v>
+        <v>28.45235084</v>
       </c>
       <c r="O85">
-        <v>5.4227925327</v>
+        <v>5.4059466596</v>
       </c>
       <c r="P85">
-        <v>23.1182207973</v>
+        <v>23.0464041804</v>
       </c>
       <c r="Q85">
-        <v>26.1182207973</v>
+        <v>26.0464041804</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2867628548669949</v>
+        <v>0.3012455148784418</v>
       </c>
       <c r="T85">
-        <v>4.413319309548296</v>
+        <v>4.678574313758059</v>
       </c>
       <c r="U85">
         <v>0.0553</v>
@@ -8414,7 +8414,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>4.878389051355626</v>
+        <v>4.82031299122044</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8422,22 +8422,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.08582540238055067</v>
+        <v>0.08572292943371221</v>
       </c>
       <c r="C86">
-        <v>32.65405854089605</v>
+        <v>31.13873187047321</v>
       </c>
       <c r="D86">
-        <v>142.031258540896</v>
+        <v>142.1192318704732</v>
       </c>
       <c r="E86">
-        <v>133.5472</v>
+        <v>135.1505</v>
       </c>
       <c r="F86">
-        <v>134.6772</v>
+        <v>136.2805</v>
       </c>
       <c r="G86">
         <v>25.3</v>
@@ -8458,28 +8458,28 @@
         <v>35.9</v>
       </c>
       <c r="M86">
-        <v>7.447649159999998</v>
+        <v>7.53631165</v>
       </c>
       <c r="N86">
-        <v>28.45235084</v>
+        <v>28.36368835</v>
       </c>
       <c r="O86">
-        <v>5.405946659600001</v>
+        <v>5.389100786499999</v>
       </c>
       <c r="P86">
-        <v>23.0464041804</v>
+        <v>22.9745875635</v>
       </c>
       <c r="Q86">
-        <v>26.0464041804</v>
+        <v>25.9745875635</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3012455148784416</v>
+        <v>0.3176591962247479</v>
       </c>
       <c r="T86">
-        <v>4.678574313758055</v>
+        <v>4.979196651862452</v>
       </c>
       <c r="U86">
         <v>0.0553</v>
@@ -8496,7 +8496,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>4.820312991220441</v>
+        <v>4.763603426617847</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8504,22 +8504,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.08572292943371221</v>
+        <v>0.08562045648687373</v>
       </c>
       <c r="C87">
-        <v>31.13873187047321</v>
+        <v>29.62351424792408</v>
       </c>
       <c r="D87">
-        <v>142.1192318704732</v>
+        <v>142.207314247924</v>
       </c>
       <c r="E87">
-        <v>135.1505</v>
+        <v>136.7538</v>
       </c>
       <c r="F87">
-        <v>136.2805</v>
+        <v>137.8838</v>
       </c>
       <c r="G87">
         <v>25.3</v>
@@ -8540,28 +8540,28 @@
         <v>35.9</v>
       </c>
       <c r="M87">
-        <v>7.53631165</v>
+        <v>7.624974139999999</v>
       </c>
       <c r="N87">
-        <v>28.36368835</v>
+        <v>28.27502586</v>
       </c>
       <c r="O87">
-        <v>5.389100786499999</v>
+        <v>5.3722549134</v>
       </c>
       <c r="P87">
-        <v>22.9745875635</v>
+        <v>22.9027709466</v>
       </c>
       <c r="Q87">
-        <v>25.9745875635</v>
+        <v>25.9027709466</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3176591962247479</v>
+        <v>0.3364176891919552</v>
       </c>
       <c r="T87">
-        <v>4.979196651862452</v>
+        <v>5.322765038267478</v>
       </c>
       <c r="U87">
         <v>0.0553</v>
@@ -8578,7 +8578,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>4.763603426617847</v>
+        <v>4.708212689099035</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8586,22 +8586,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.08562045648687373</v>
+        <v>0.08551798354003526</v>
       </c>
       <c r="C88">
-        <v>29.62351424792408</v>
+        <v>28.10840587613072</v>
       </c>
       <c r="D88">
-        <v>142.207314247924</v>
+        <v>142.2955058761307</v>
       </c>
       <c r="E88">
-        <v>136.7538</v>
+        <v>138.3571</v>
       </c>
       <c r="F88">
-        <v>137.8838</v>
+        <v>139.4871</v>
       </c>
       <c r="G88">
         <v>25.3</v>
@@ -8622,28 +8622,28 @@
         <v>35.9</v>
       </c>
       <c r="M88">
-        <v>7.624974139999999</v>
+        <v>7.71363663</v>
       </c>
       <c r="N88">
-        <v>28.27502586</v>
+        <v>28.18636337</v>
       </c>
       <c r="O88">
-        <v>5.3722549134</v>
+        <v>5.3554090403</v>
       </c>
       <c r="P88">
-        <v>22.9027709466</v>
+        <v>22.8309543297</v>
       </c>
       <c r="Q88">
-        <v>25.9027709466</v>
+        <v>25.8309543297</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3364176891919552</v>
+        <v>0.3580621041541174</v>
       </c>
       <c r="T88">
-        <v>5.322765038267478</v>
+        <v>5.719190099504044</v>
       </c>
       <c r="U88">
         <v>0.0553</v>
@@ -8660,7 +8660,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>4.708212689099035</v>
+        <v>4.654095301868011</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8668,22 +8668,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.08551798354003526</v>
+        <v>0.0854155105931968</v>
       </c>
       <c r="C89">
-        <v>28.10840587613072</v>
+        <v>26.59340695847902</v>
       </c>
       <c r="D89">
-        <v>142.2955058761307</v>
+        <v>142.383806958479</v>
       </c>
       <c r="E89">
-        <v>138.3571</v>
+        <v>139.9604</v>
       </c>
       <c r="F89">
-        <v>139.4871</v>
+        <v>141.0904</v>
       </c>
       <c r="G89">
         <v>25.3</v>
@@ -8704,28 +8704,28 @@
         <v>35.9</v>
       </c>
       <c r="M89">
-        <v>7.71363663</v>
+        <v>7.80229912</v>
       </c>
       <c r="N89">
-        <v>28.18636337</v>
+        <v>28.09770088</v>
       </c>
       <c r="O89">
-        <v>5.3554090403</v>
+        <v>5.338563167199999</v>
       </c>
       <c r="P89">
-        <v>22.8309543297</v>
+        <v>22.7591377128</v>
       </c>
       <c r="Q89">
-        <v>25.8309543297</v>
+        <v>25.7591377128</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3580621041541174</v>
+        <v>0.3833139216099733</v>
       </c>
       <c r="T89">
-        <v>5.719190099504044</v>
+        <v>6.18168600428004</v>
       </c>
       <c r="U89">
         <v>0.0553</v>
@@ -8742,7 +8742,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>4.654095301868011</v>
+        <v>4.601207855255875</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8750,22 +8750,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.0854155105931968</v>
+        <v>0.08531303764635834</v>
       </c>
       <c r="C90">
-        <v>26.59340695847902</v>
+        <v>25.07851769885983</v>
       </c>
       <c r="D90">
-        <v>142.383806958479</v>
+        <v>142.4722176988598</v>
       </c>
       <c r="E90">
-        <v>139.9604</v>
+        <v>141.5637</v>
       </c>
       <c r="F90">
-        <v>141.0904</v>
+        <v>142.6937</v>
       </c>
       <c r="G90">
         <v>25.3</v>
@@ -8786,28 +8786,28 @@
         <v>35.9</v>
       </c>
       <c r="M90">
-        <v>7.80229912</v>
+        <v>7.890961609999999</v>
       </c>
       <c r="N90">
-        <v>28.09770088</v>
+        <v>28.00903839</v>
       </c>
       <c r="O90">
-        <v>5.338563167199999</v>
+        <v>5.3217172941</v>
       </c>
       <c r="P90">
-        <v>22.7591377128</v>
+        <v>22.6873210959</v>
       </c>
       <c r="Q90">
-        <v>25.7591377128</v>
+        <v>25.6873210959</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3833139216099733</v>
+        <v>0.4131569786032576</v>
       </c>
       <c r="T90">
-        <v>6.18168600428004</v>
+        <v>6.728272073560762</v>
       </c>
       <c r="U90">
         <v>0.0553</v>
@@ -8824,7 +8824,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>4.601207855255875</v>
+        <v>4.549508890590079</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8832,22 +8832,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.08531303764635834</v>
+        <v>0.08703306469951987</v>
       </c>
       <c r="C91">
-        <v>25.07851769885983</v>
+        <v>22.00562268496114</v>
       </c>
       <c r="D91">
-        <v>142.4722176988598</v>
+        <v>141.0026226849611</v>
       </c>
       <c r="E91">
-        <v>141.5637</v>
+        <v>143.167</v>
       </c>
       <c r="F91">
-        <v>142.6937</v>
+        <v>144.297</v>
       </c>
       <c r="G91">
         <v>25.3</v>
@@ -8868,45 +8868,45 @@
         <v>35.9</v>
       </c>
       <c r="M91">
-        <v>7.890961609999999</v>
+        <v>8.340366600000001</v>
       </c>
       <c r="N91">
-        <v>28.00903839</v>
+        <v>27.5596334</v>
       </c>
       <c r="O91">
-        <v>5.3217172941</v>
+        <v>5.236330345999999</v>
       </c>
       <c r="P91">
-        <v>22.6873210959</v>
+        <v>22.323303054</v>
       </c>
       <c r="Q91">
-        <v>25.6873210959</v>
+        <v>25.323303054</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4131569786032576</v>
+        <v>0.4489686469951987</v>
       </c>
       <c r="T91">
-        <v>6.728272073560762</v>
+        <v>7.384175356697629</v>
       </c>
       <c r="U91">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V91">
         <v>0.19</v>
       </c>
       <c r="W91">
-        <v>0.04479300000000001</v>
+        <v>0.04681800000000001</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y91">
-        <v>4.549508890590079</v>
+        <v>4.30436714856155</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8914,22 +8914,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.08703306469951987</v>
+        <v>0.0869508417526814</v>
       </c>
       <c r="C92">
-        <v>22.00562268496114</v>
+        <v>20.47188381595967</v>
       </c>
       <c r="D92">
-        <v>141.0026226849611</v>
+        <v>141.0721838159596</v>
       </c>
       <c r="E92">
-        <v>143.167</v>
+        <v>144.7703</v>
       </c>
       <c r="F92">
-        <v>144.297</v>
+        <v>145.9003</v>
       </c>
       <c r="G92">
         <v>25.3</v>
@@ -8950,28 +8950,28 @@
         <v>35.9</v>
       </c>
       <c r="M92">
-        <v>8.340366600000001</v>
+        <v>8.43303734</v>
       </c>
       <c r="N92">
-        <v>27.5596334</v>
+        <v>27.46696266</v>
       </c>
       <c r="O92">
-        <v>5.236330345999999</v>
+        <v>5.2187229054</v>
       </c>
       <c r="P92">
-        <v>22.323303054</v>
+        <v>22.2482397546</v>
       </c>
       <c r="Q92">
-        <v>25.323303054</v>
+        <v>25.2482397546</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4489686469951987</v>
+        <v>0.4927384639186824</v>
       </c>
       <c r="T92">
-        <v>7.384175356697629</v>
+        <v>8.185834924976021</v>
       </c>
       <c r="U92">
         <v>0.0578</v>
@@ -8988,7 +8988,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>4.30436714856155</v>
+        <v>4.257066410665271</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8996,22 +8996,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.0869508417526814</v>
+        <v>0.08686861880584293</v>
       </c>
       <c r="C93">
-        <v>20.47188381595967</v>
+        <v>18.93821361432259</v>
       </c>
       <c r="D93">
-        <v>141.0721838159596</v>
+        <v>141.1418136143226</v>
       </c>
       <c r="E93">
-        <v>144.7703</v>
+        <v>146.3736</v>
       </c>
       <c r="F93">
-        <v>145.9003</v>
+        <v>147.5036</v>
       </c>
       <c r="G93">
         <v>25.3</v>
@@ -9032,28 +9032,28 @@
         <v>35.9</v>
       </c>
       <c r="M93">
-        <v>8.43303734</v>
+        <v>8.525708080000001</v>
       </c>
       <c r="N93">
-        <v>27.46696266</v>
+        <v>27.37429192</v>
       </c>
       <c r="O93">
-        <v>5.2187229054</v>
+        <v>5.2011154648</v>
       </c>
       <c r="P93">
-        <v>22.2482397546</v>
+        <v>22.1731764552</v>
       </c>
       <c r="Q93">
-        <v>25.2482397546</v>
+        <v>25.1731764552</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4927384639186824</v>
+        <v>0.5474507350730369</v>
       </c>
       <c r="T93">
-        <v>8.185834924976021</v>
+        <v>9.187909385324012</v>
       </c>
       <c r="U93">
         <v>0.0578</v>
@@ -9070,7 +9070,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>4.257066410665271</v>
+        <v>4.210793949679777</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9078,22 +9078,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.08686861880584293</v>
+        <v>0.08678639585900447</v>
       </c>
       <c r="C94">
-        <v>18.93821361432259</v>
+        <v>17.40461218177771</v>
       </c>
       <c r="D94">
-        <v>141.1418136143226</v>
+        <v>141.2115121817777</v>
       </c>
       <c r="E94">
-        <v>146.3736</v>
+        <v>147.9769</v>
       </c>
       <c r="F94">
-        <v>147.5036</v>
+        <v>149.1069</v>
       </c>
       <c r="G94">
         <v>25.3</v>
@@ -9114,28 +9114,28 @@
         <v>35.9</v>
       </c>
       <c r="M94">
-        <v>8.525708080000001</v>
+        <v>8.61837882</v>
       </c>
       <c r="N94">
-        <v>27.37429192</v>
+        <v>27.28162118</v>
       </c>
       <c r="O94">
-        <v>5.2011154648</v>
+        <v>5.1835080242</v>
       </c>
       <c r="P94">
-        <v>22.1731764552</v>
+        <v>22.0981131558</v>
       </c>
       <c r="Q94">
-        <v>25.1731764552</v>
+        <v>25.0981131558</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5474507350730369</v>
+        <v>0.6177950837000641</v>
       </c>
       <c r="T94">
-        <v>9.187909385324012</v>
+        <v>10.47629083434286</v>
       </c>
       <c r="U94">
         <v>0.0578</v>
@@ -9152,7 +9152,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>4.210793949679777</v>
+        <v>4.165516595382146</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9160,22 +9160,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.08678639585900447</v>
+        <v>0.08670417291216601</v>
       </c>
       <c r="C95">
-        <v>17.40461218177771</v>
+        <v>15.87107962025394</v>
       </c>
       <c r="D95">
-        <v>141.2115121817777</v>
+        <v>141.2812796202539</v>
       </c>
       <c r="E95">
-        <v>147.9769</v>
+        <v>149.5802</v>
       </c>
       <c r="F95">
-        <v>149.1069</v>
+        <v>150.7102</v>
       </c>
       <c r="G95">
         <v>25.3</v>
@@ -9196,28 +9196,28 @@
         <v>35.9</v>
       </c>
       <c r="M95">
-        <v>8.61837882</v>
+        <v>8.711049559999999</v>
       </c>
       <c r="N95">
-        <v>27.28162118</v>
+        <v>27.18895044</v>
       </c>
       <c r="O95">
-        <v>5.1835080242</v>
+        <v>5.1659005836</v>
       </c>
       <c r="P95">
-        <v>22.0981131558</v>
+        <v>22.0230498564</v>
       </c>
       <c r="Q95">
-        <v>25.0981131558</v>
+        <v>25.0230498564</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6177950837000641</v>
+        <v>0.7115875485361006</v>
       </c>
       <c r="T95">
-        <v>10.47629083434286</v>
+        <v>12.19413276636799</v>
       </c>
       <c r="U95">
         <v>0.0578</v>
@@ -9234,7 +9234,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>4.165516595382146</v>
+        <v>4.121202589048294</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9242,22 +9242,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.08670417291216601</v>
+        <v>0.08662194996532754</v>
       </c>
       <c r="C96">
-        <v>15.87107962025394</v>
+        <v>14.33761603188165</v>
       </c>
       <c r="D96">
-        <v>141.2812796202539</v>
+        <v>141.3511160318816</v>
       </c>
       <c r="E96">
-        <v>149.5802</v>
+        <v>151.1835</v>
       </c>
       <c r="F96">
-        <v>150.7102</v>
+        <v>152.3135</v>
       </c>
       <c r="G96">
         <v>25.3</v>
@@ -9278,28 +9278,28 @@
         <v>35.9</v>
       </c>
       <c r="M96">
-        <v>8.711049559999999</v>
+        <v>8.8037203</v>
       </c>
       <c r="N96">
-        <v>27.18895044</v>
+        <v>27.0962797</v>
       </c>
       <c r="O96">
-        <v>5.1659005836</v>
+        <v>5.148293142999999</v>
       </c>
       <c r="P96">
-        <v>22.0230498564</v>
+        <v>21.947986557</v>
       </c>
       <c r="Q96">
-        <v>25.0230498564</v>
+        <v>24.947986557</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.7115875485361006</v>
+        <v>0.8428969993065517</v>
       </c>
       <c r="T96">
-        <v>12.19413276636799</v>
+        <v>14.59911147120317</v>
       </c>
       <c r="U96">
         <v>0.0578</v>
@@ -9316,7 +9316,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>4.121202589048294</v>
+        <v>4.077821509163575</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9324,22 +9324,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.08662194996532754</v>
+        <v>0.08653972701848908</v>
       </c>
       <c r="C97">
-        <v>14.33761603188165</v>
+        <v>12.80422151899336</v>
       </c>
       <c r="D97">
-        <v>141.3511160318816</v>
+        <v>141.4210215189933</v>
       </c>
       <c r="E97">
-        <v>151.1835</v>
+        <v>152.7868</v>
       </c>
       <c r="F97">
-        <v>152.3135</v>
+        <v>153.9168</v>
       </c>
       <c r="G97">
         <v>25.3</v>
@@ -9360,28 +9360,28 @@
         <v>35.9</v>
       </c>
       <c r="M97">
-        <v>8.8037203</v>
+        <v>8.896391040000001</v>
       </c>
       <c r="N97">
-        <v>27.0962797</v>
+        <v>27.00360896</v>
       </c>
       <c r="O97">
-        <v>5.148293142999999</v>
+        <v>5.130685702399999</v>
       </c>
       <c r="P97">
-        <v>21.947986557</v>
+        <v>21.8729232576</v>
       </c>
       <c r="Q97">
-        <v>24.947986557</v>
+        <v>24.8729232576</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.8428969993065517</v>
+        <v>1.039861175462229</v>
       </c>
       <c r="T97">
-        <v>14.59911147120317</v>
+        <v>18.20657952845594</v>
       </c>
       <c r="U97">
         <v>0.0578</v>
@@ -9398,7 +9398,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>4.077821509163575</v>
+        <v>4.035344201776454</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9406,22 +9406,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.08653972701848908</v>
+        <v>0.08920745407165062</v>
       </c>
       <c r="C98">
-        <v>12.80422151899339</v>
+        <v>8.967549449978122</v>
       </c>
       <c r="D98">
-        <v>141.4210215189933</v>
+        <v>139.1876494499781</v>
       </c>
       <c r="E98">
-        <v>152.7868</v>
+        <v>154.3901</v>
       </c>
       <c r="F98">
-        <v>153.9168</v>
+        <v>155.5201</v>
       </c>
       <c r="G98">
         <v>25.3</v>
@@ -9442,45 +9442,45 @@
         <v>35.9</v>
       </c>
       <c r="M98">
-        <v>8.896391039999999</v>
+        <v>9.53338213</v>
       </c>
       <c r="N98">
-        <v>27.00360896</v>
+        <v>26.36661787</v>
       </c>
       <c r="O98">
-        <v>5.1306857024</v>
+        <v>5.0096573953</v>
       </c>
       <c r="P98">
-        <v>21.8729232576</v>
+        <v>21.3569604747</v>
       </c>
       <c r="Q98">
-        <v>24.8729232576</v>
+        <v>24.3569604747</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.039861175462226</v>
+        <v>1.368134802388353</v>
       </c>
       <c r="T98">
-        <v>18.20657952845589</v>
+        <v>24.21902629054383</v>
       </c>
       <c r="U98">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V98">
         <v>0.19</v>
       </c>
       <c r="W98">
-        <v>0.04681800000000001</v>
+        <v>0.049653</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y98">
-        <v>4.035344201776454</v>
+        <v>3.765714990803584</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9488,22 +9488,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.08920745407165062</v>
+        <v>0.08915358112481214</v>
       </c>
       <c r="C99">
-        <v>8.967549449978122</v>
+        <v>7.408652793770642</v>
       </c>
       <c r="D99">
-        <v>139.1876494499781</v>
+        <v>139.2320527937706</v>
       </c>
       <c r="E99">
-        <v>154.3901</v>
+        <v>155.9934</v>
       </c>
       <c r="F99">
-        <v>155.5201</v>
+        <v>157.1234</v>
       </c>
       <c r="G99">
         <v>25.3</v>
@@ -9524,28 +9524,28 @@
         <v>35.9</v>
       </c>
       <c r="M99">
-        <v>9.53338213</v>
+        <v>9.631664419999998</v>
       </c>
       <c r="N99">
-        <v>26.36661787</v>
+        <v>26.26833558</v>
       </c>
       <c r="O99">
-        <v>5.0096573953</v>
+        <v>4.9909837602</v>
       </c>
       <c r="P99">
-        <v>21.3569604747</v>
+        <v>21.2773518198</v>
       </c>
       <c r="Q99">
-        <v>24.3569604747</v>
+        <v>24.2773518198</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.368134802388353</v>
+        <v>2.024682056240605</v>
       </c>
       <c r="T99">
-        <v>24.21902629054383</v>
+        <v>36.24391981471968</v>
       </c>
       <c r="U99">
         <v>0.0613</v>
@@ -9562,7 +9562,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>3.765714990803584</v>
+        <v>3.727289327632119</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9570,22 +9570,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.08915358112481214</v>
+        <v>0.08909970817797369</v>
       </c>
       <c r="C100">
-        <v>7.408652793770642</v>
+        <v>5.849784477522064</v>
       </c>
       <c r="D100">
-        <v>139.2320527937706</v>
+        <v>139.276484477522</v>
       </c>
       <c r="E100">
-        <v>155.9934</v>
+        <v>157.5967</v>
       </c>
       <c r="F100">
-        <v>157.1234</v>
+        <v>158.7267</v>
       </c>
       <c r="G100">
         <v>25.3</v>
@@ -9606,28 +9606,28 @@
         <v>35.9</v>
       </c>
       <c r="M100">
-        <v>9.631664419999998</v>
+        <v>9.72994671</v>
       </c>
       <c r="N100">
-        <v>26.26833558</v>
+        <v>26.17005329</v>
       </c>
       <c r="O100">
-        <v>4.9909837602</v>
+        <v>4.9723101251</v>
       </c>
       <c r="P100">
-        <v>21.2773518198</v>
+        <v>21.1977431649</v>
       </c>
       <c r="Q100">
-        <v>24.2773518198</v>
+        <v>24.1977431649</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.024682056240605</v>
+        <v>3.994323817797365</v>
       </c>
       <c r="T100">
-        <v>36.24391981471968</v>
+        <v>72.31860038724727</v>
       </c>
       <c r="U100">
         <v>0.0613</v>
@@ -9644,91 +9644,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>3.727289327632119</v>
+        <v>3.689639940484319</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.08909970817797369</v>
-      </c>
-      <c r="C101">
-        <v>5.849784477522064</v>
-      </c>
-      <c r="D101">
-        <v>139.276484477522</v>
-      </c>
-      <c r="E101">
-        <v>157.5967</v>
-      </c>
-      <c r="F101">
-        <v>158.7267</v>
-      </c>
-      <c r="G101">
-        <v>25.3</v>
-      </c>
-      <c r="H101">
-        <v>159.2</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>38.9</v>
-      </c>
-      <c r="K101">
-        <v>3</v>
-      </c>
-      <c r="L101">
-        <v>35.9</v>
-      </c>
-      <c r="M101">
-        <v>9.72994671</v>
-      </c>
-      <c r="N101">
-        <v>26.17005329</v>
-      </c>
-      <c r="O101">
-        <v>4.9723101251</v>
-      </c>
-      <c r="P101">
-        <v>21.1977431649</v>
-      </c>
-      <c r="Q101">
-        <v>24.1977431649</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.994323817797365</v>
-      </c>
-      <c r="T101">
-        <v>72.31860038724727</v>
-      </c>
-      <c r="U101">
-        <v>0.0613</v>
-      </c>
-      <c r="V101">
-        <v>0.19</v>
-      </c>
-      <c r="W101">
-        <v>0.049653</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Ba1/BB+</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>3.689639940484319</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
